--- a/data/import/ANNEX_FORMATIONS.xlsx
+++ b/data/import/ANNEX_FORMATIONS.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30430"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DD8DC84-DC22-4EB9-9A7D-2C88CF8A9CFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E9036CE-2F93-4209-919A-BB982F825CD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Let's Go" sheetId="2" r:id="rId1"/>
@@ -85,9 +85,6 @@
   </si>
   <si>
     <t>Formation Français - Project 12  [ANNEX]  (مستحقات الدورة: 4000 دج  |  سعر الكتاب: 500 دج)</t>
-  </si>
-  <si>
-    <t>Let's Go  [ANNEX]  (مستحقات الدورة: 4000 دج  |  سعر الكتاب: 500 دج)</t>
   </si>
   <si>
     <t>Formation Anglais - Let's Go 02  [ANNEX]  (مستحقات الدورة: 4000 دج  |  سعر الكتاب: 500 دج)</t>
@@ -566,6 +563,9 @@
   <si>
     <t>06 70 10 46 18</t>
   </si>
+  <si>
+    <t>Formation Anglais - Let's Go 01  [ANNEX]  (مستحقات الدورة: 4000 دج  |  سعر الكتاب: 500 دج)</t>
+  </si>
 </sst>
 </file>
 
@@ -735,8 +735,8 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -750,8 +750,8 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
@@ -1116,17 +1116,17 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:9" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="B2" s="9"/>
-      <c r="C2" s="9"/>
-      <c r="D2" s="9"/>
-      <c r="E2" s="9"/>
-      <c r="F2" s="9"/>
-      <c r="G2" s="9"/>
-      <c r="H2" s="9"/>
-      <c r="I2" s="9"/>
+      <c r="A2" s="14" t="s">
+        <v>181</v>
+      </c>
+      <c r="B2" s="14"/>
+      <c r="C2" s="14"/>
+      <c r="D2" s="14"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="14"/>
+      <c r="G2" s="14"/>
+      <c r="H2" s="14"/>
+      <c r="I2" s="14"/>
     </row>
     <row r="3" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
@@ -1162,10 +1162,10 @@
         <v>1</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D4" s="3">
         <v>300</v>
@@ -1191,13 +1191,13 @@
       <c r="B5" s="11"/>
       <c r="C5" s="2"/>
       <c r="D5" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G5" s="4" t="s">
         <v>10</v>
@@ -1214,7 +1214,7 @@
         <v>2</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C6" s="5"/>
       <c r="D6" s="6">
@@ -1241,13 +1241,13 @@
       <c r="B7" s="13"/>
       <c r="C7" s="5"/>
       <c r="D7" s="7" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G7" s="7" t="s">
         <v>10</v>
@@ -1264,10 +1264,10 @@
         <v>3</v>
       </c>
       <c r="B8" s="11" t="s">
+        <v>76</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>77</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>78</v>
       </c>
       <c r="D8" s="3">
         <v>300</v>
@@ -1293,13 +1293,13 @@
       <c r="B9" s="11"/>
       <c r="C9" s="2"/>
       <c r="D9" s="4" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G9" s="4" t="s">
         <v>10</v>
@@ -1316,17 +1316,17 @@
         <v>4</v>
       </c>
       <c r="B10" s="13" t="s">
+        <v>79</v>
+      </c>
+      <c r="C10" s="5" t="s">
         <v>80</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>81</v>
       </c>
       <c r="D10" s="6">
         <v>300</v>
       </c>
       <c r="E10" s="6"/>
       <c r="F10" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G10" s="6" t="s">
         <v>10</v>
@@ -1343,11 +1343,11 @@
       <c r="B11" s="13"/>
       <c r="C11" s="5"/>
       <c r="D11" s="7" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E11" s="7"/>
       <c r="F11" s="7" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G11" s="7" t="s">
         <v>10</v>
@@ -1364,10 +1364,10 @@
         <v>5</v>
       </c>
       <c r="B12" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="C12" s="2" t="s">
         <v>84</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>85</v>
       </c>
       <c r="D12" s="3">
         <v>300</v>
@@ -1393,13 +1393,13 @@
       <c r="B13" s="11"/>
       <c r="C13" s="2"/>
       <c r="D13" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="E13" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="E13" s="4" t="s">
-        <v>87</v>
-      </c>
       <c r="F13" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="G13" s="4" t="s">
         <v>10</v>
@@ -1416,7 +1416,7 @@
         <v>6</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C14" s="5"/>
       <c r="D14" s="6"/>
@@ -1441,7 +1441,7 @@
       <c r="D15" s="7"/>
       <c r="E15" s="7"/>
       <c r="F15" s="7" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G15" s="7" t="s">
         <v>10</v>
@@ -1458,7 +1458,7 @@
         <v>7</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" s="3"/>
@@ -1483,7 +1483,7 @@
       <c r="D17" s="4"/>
       <c r="E17" s="4"/>
       <c r="F17" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G17" s="4" t="s">
         <v>10</v>
@@ -1500,10 +1500,10 @@
         <v>8</v>
       </c>
       <c r="B18" s="13" t="s">
+        <v>90</v>
+      </c>
+      <c r="C18" s="5" t="s">
         <v>91</v>
-      </c>
-      <c r="C18" s="5" t="s">
-        <v>92</v>
       </c>
       <c r="D18" s="6">
         <v>300</v>
@@ -1529,13 +1529,13 @@
       <c r="B19" s="13"/>
       <c r="C19" s="5"/>
       <c r="D19" s="7" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E19" s="7" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G19" s="7" t="s">
         <v>10</v>
@@ -2194,17 +2194,17 @@
       </c>
     </row>
     <row r="46" spans="1:9" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="B46" s="9"/>
-      <c r="C46" s="9"/>
-      <c r="D46" s="9"/>
-      <c r="E46" s="9"/>
-      <c r="F46" s="9"/>
-      <c r="G46" s="9"/>
-      <c r="H46" s="9"/>
-      <c r="I46" s="9"/>
+      <c r="A46" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="B46" s="14"/>
+      <c r="C46" s="14"/>
+      <c r="D46" s="14"/>
+      <c r="E46" s="14"/>
+      <c r="F46" s="14"/>
+      <c r="G46" s="14"/>
+      <c r="H46" s="14"/>
+      <c r="I46" s="14"/>
     </row>
     <row r="47" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
@@ -2240,10 +2240,10 @@
         <v>1</v>
       </c>
       <c r="B48" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="C48" s="2" t="s">
         <v>95</v>
-      </c>
-      <c r="C48" s="2" t="s">
-        <v>96</v>
       </c>
       <c r="D48" s="3">
         <v>300</v>
@@ -2267,13 +2267,13 @@
       <c r="B49" s="11"/>
       <c r="C49" s="2"/>
       <c r="D49" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E49" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F49" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G49" s="4"/>
       <c r="H49" s="4" t="s">
@@ -2288,10 +2288,10 @@
         <v>2</v>
       </c>
       <c r="B50" s="13" t="s">
+        <v>97</v>
+      </c>
+      <c r="C50" s="5" t="s">
         <v>98</v>
-      </c>
-      <c r="C50" s="5" t="s">
-        <v>99</v>
       </c>
       <c r="D50" s="6"/>
       <c r="E50" s="6"/>
@@ -2328,10 +2328,10 @@
         <v>3</v>
       </c>
       <c r="B52" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="C52" s="2" t="s">
         <v>100</v>
-      </c>
-      <c r="C52" s="2" t="s">
-        <v>101</v>
       </c>
       <c r="D52" s="3"/>
       <c r="E52" s="3"/>
@@ -2368,10 +2368,10 @@
         <v>4</v>
       </c>
       <c r="B54" s="13" t="s">
+        <v>101</v>
+      </c>
+      <c r="C54" s="5" t="s">
         <v>102</v>
-      </c>
-      <c r="C54" s="5" t="s">
-        <v>103</v>
       </c>
       <c r="D54" s="6">
         <v>300</v>
@@ -2397,13 +2397,13 @@
       <c r="B55" s="13"/>
       <c r="C55" s="5"/>
       <c r="D55" s="7" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E55" s="7" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F55" s="7" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="G55" s="7" t="s">
         <v>10</v>
@@ -2420,10 +2420,10 @@
         <v>5</v>
       </c>
       <c r="B56" s="11" t="s">
+        <v>104</v>
+      </c>
+      <c r="C56" s="2" t="s">
         <v>105</v>
-      </c>
-      <c r="C56" s="2" t="s">
-        <v>106</v>
       </c>
       <c r="D56" s="3"/>
       <c r="E56" s="3"/>
@@ -2460,10 +2460,10 @@
         <v>6</v>
       </c>
       <c r="B58" s="13" t="s">
+        <v>106</v>
+      </c>
+      <c r="C58" s="5" t="s">
         <v>107</v>
-      </c>
-      <c r="C58" s="5" t="s">
-        <v>108</v>
       </c>
       <c r="D58" s="6"/>
       <c r="E58" s="6"/>
@@ -2500,10 +2500,10 @@
         <v>7</v>
       </c>
       <c r="B60" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="C60" s="2" t="s">
         <v>109</v>
-      </c>
-      <c r="C60" s="2" t="s">
-        <v>110</v>
       </c>
       <c r="D60" s="3"/>
       <c r="E60" s="3"/>
@@ -2540,10 +2540,10 @@
         <v>8</v>
       </c>
       <c r="B62" s="13" t="s">
+        <v>110</v>
+      </c>
+      <c r="C62" s="5" t="s">
         <v>111</v>
-      </c>
-      <c r="C62" s="5" t="s">
-        <v>112</v>
       </c>
       <c r="D62" s="6"/>
       <c r="E62" s="6"/>
@@ -2580,10 +2580,10 @@
         <v>9</v>
       </c>
       <c r="B64" s="11" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D64" s="3"/>
       <c r="E64" s="3"/>
@@ -2620,10 +2620,10 @@
         <v>10</v>
       </c>
       <c r="B66" s="13" t="s">
+        <v>113</v>
+      </c>
+      <c r="C66" s="5" t="s">
         <v>114</v>
-      </c>
-      <c r="C66" s="5" t="s">
-        <v>115</v>
       </c>
       <c r="D66" s="6"/>
       <c r="E66" s="6"/>
@@ -3196,17 +3196,17 @@
       </c>
     </row>
     <row r="90" spans="1:9" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A90" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="B90" s="9"/>
-      <c r="C90" s="9"/>
-      <c r="D90" s="9"/>
-      <c r="E90" s="9"/>
-      <c r="F90" s="9"/>
-      <c r="G90" s="9"/>
-      <c r="H90" s="9"/>
-      <c r="I90" s="9"/>
+      <c r="A90" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="B90" s="14"/>
+      <c r="C90" s="14"/>
+      <c r="D90" s="14"/>
+      <c r="E90" s="14"/>
+      <c r="F90" s="14"/>
+      <c r="G90" s="14"/>
+      <c r="H90" s="14"/>
+      <c r="I90" s="14"/>
     </row>
     <row r="91" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
@@ -4318,17 +4318,17 @@
       </c>
     </row>
     <row r="134" spans="1:9" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A134" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="B134" s="9"/>
-      <c r="C134" s="9"/>
-      <c r="D134" s="9"/>
-      <c r="E134" s="9"/>
-      <c r="F134" s="9"/>
-      <c r="G134" s="9"/>
-      <c r="H134" s="9"/>
-      <c r="I134" s="9"/>
+      <c r="A134" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="B134" s="14"/>
+      <c r="C134" s="14"/>
+      <c r="D134" s="14"/>
+      <c r="E134" s="14"/>
+      <c r="F134" s="14"/>
+      <c r="G134" s="14"/>
+      <c r="H134" s="14"/>
+      <c r="I134" s="14"/>
     </row>
     <row r="135" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" s="1" t="s">
@@ -4364,10 +4364,10 @@
         <v>1</v>
       </c>
       <c r="B136" s="11" t="s">
+        <v>115</v>
+      </c>
+      <c r="C136" s="2" t="s">
         <v>116</v>
-      </c>
-      <c r="C136" s="2" t="s">
-        <v>117</v>
       </c>
       <c r="D136" s="3"/>
       <c r="E136" s="3"/>
@@ -4391,7 +4391,7 @@
       <c r="D137" s="4"/>
       <c r="E137" s="4"/>
       <c r="F137" s="4" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="G137" s="4" t="s">
         <v>10</v>
@@ -4408,10 +4408,10 @@
         <v>2</v>
       </c>
       <c r="B138" s="13" t="s">
+        <v>118</v>
+      </c>
+      <c r="C138" s="5" t="s">
         <v>119</v>
-      </c>
-      <c r="C138" s="5" t="s">
-        <v>120</v>
       </c>
       <c r="D138" s="6">
         <v>300</v>
@@ -4437,13 +4437,13 @@
       <c r="B139" s="13"/>
       <c r="C139" s="5"/>
       <c r="D139" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="E139" s="7" t="s">
         <v>121</v>
       </c>
-      <c r="E139" s="7" t="s">
-        <v>122</v>
-      </c>
       <c r="F139" s="7" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="G139" s="7" t="s">
         <v>10</v>
@@ -4460,7 +4460,7 @@
         <v>3</v>
       </c>
       <c r="B140" s="11" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" s="3"/>
@@ -4498,7 +4498,7 @@
         <v>4</v>
       </c>
       <c r="B142" s="13" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C142" s="5"/>
       <c r="D142" s="6">
@@ -4525,13 +4525,13 @@
       <c r="B143" s="13"/>
       <c r="C143" s="5"/>
       <c r="D143" s="7" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E143" s="7" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F143" s="7" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G143" s="7" t="s">
         <v>10</v>
@@ -4548,7 +4548,7 @@
         <v>5</v>
       </c>
       <c r="B144" s="11" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C144" s="2" t="s">
         <v>10</v>
@@ -4582,10 +4582,10 @@
         <v>10</v>
       </c>
       <c r="E145" s="7" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F145" s="7" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G145" s="4" t="s">
         <v>10</v>
@@ -4602,7 +4602,7 @@
         <v>6</v>
       </c>
       <c r="B146" s="13" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C146" s="5" t="s">
         <v>10</v>
@@ -4635,11 +4635,11 @@
       <c r="D147" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="E147" s="14" t="s">
-        <v>128</v>
-      </c>
-      <c r="F147" s="14" t="s">
-        <v>128</v>
+      <c r="E147" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="F147" s="9" t="s">
+        <v>127</v>
       </c>
       <c r="G147" s="7" t="s">
         <v>10</v>
@@ -5408,17 +5408,17 @@
       </c>
     </row>
     <row r="178" spans="1:9" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A178" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="B178" s="9"/>
-      <c r="C178" s="9"/>
-      <c r="D178" s="9"/>
-      <c r="E178" s="9"/>
-      <c r="F178" s="9"/>
-      <c r="G178" s="9"/>
-      <c r="H178" s="9"/>
-      <c r="I178" s="9"/>
+      <c r="A178" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="B178" s="14"/>
+      <c r="C178" s="14"/>
+      <c r="D178" s="14"/>
+      <c r="E178" s="14"/>
+      <c r="F178" s="14"/>
+      <c r="G178" s="14"/>
+      <c r="H178" s="14"/>
+      <c r="I178" s="14"/>
     </row>
     <row r="179" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A179" s="1" t="s">
@@ -6530,17 +6530,17 @@
       </c>
     </row>
     <row r="222" spans="1:9" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A222" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="B222" s="9"/>
-      <c r="C222" s="9"/>
-      <c r="D222" s="9"/>
-      <c r="E222" s="9"/>
-      <c r="F222" s="9"/>
-      <c r="G222" s="9"/>
-      <c r="H222" s="9"/>
-      <c r="I222" s="9"/>
+      <c r="A222" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="B222" s="14"/>
+      <c r="C222" s="14"/>
+      <c r="D222" s="14"/>
+      <c r="E222" s="14"/>
+      <c r="F222" s="14"/>
+      <c r="G222" s="14"/>
+      <c r="H222" s="14"/>
+      <c r="I222" s="14"/>
     </row>
     <row r="223" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A223" s="1" t="s">
@@ -7652,17 +7652,17 @@
       </c>
     </row>
     <row r="266" spans="1:9" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A266" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="B266" s="9"/>
-      <c r="C266" s="9"/>
-      <c r="D266" s="9"/>
-      <c r="E266" s="9"/>
-      <c r="F266" s="9"/>
-      <c r="G266" s="9"/>
-      <c r="H266" s="9"/>
-      <c r="I266" s="9"/>
+      <c r="A266" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="B266" s="14"/>
+      <c r="C266" s="14"/>
+      <c r="D266" s="14"/>
+      <c r="E266" s="14"/>
+      <c r="F266" s="14"/>
+      <c r="G266" s="14"/>
+      <c r="H266" s="14"/>
+      <c r="I266" s="14"/>
     </row>
     <row r="267" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A267" s="1" t="s">
@@ -8774,17 +8774,17 @@
       </c>
     </row>
     <row r="310" spans="1:9" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A310" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="B310" s="9"/>
-      <c r="C310" s="9"/>
-      <c r="D310" s="9"/>
-      <c r="E310" s="9"/>
-      <c r="F310" s="9"/>
-      <c r="G310" s="9"/>
-      <c r="H310" s="9"/>
-      <c r="I310" s="9"/>
+      <c r="A310" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="B310" s="14"/>
+      <c r="C310" s="14"/>
+      <c r="D310" s="14"/>
+      <c r="E310" s="14"/>
+      <c r="F310" s="14"/>
+      <c r="G310" s="14"/>
+      <c r="H310" s="14"/>
+      <c r="I310" s="14"/>
     </row>
     <row r="311" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A311" s="1" t="s">
@@ -9896,17 +9896,17 @@
       </c>
     </row>
     <row r="354" spans="1:9" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A354" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="B354" s="9"/>
-      <c r="C354" s="9"/>
-      <c r="D354" s="9"/>
-      <c r="E354" s="9"/>
-      <c r="F354" s="9"/>
-      <c r="G354" s="9"/>
-      <c r="H354" s="9"/>
-      <c r="I354" s="9"/>
+      <c r="A354" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="B354" s="14"/>
+      <c r="C354" s="14"/>
+      <c r="D354" s="14"/>
+      <c r="E354" s="14"/>
+      <c r="F354" s="14"/>
+      <c r="G354" s="14"/>
+      <c r="H354" s="14"/>
+      <c r="I354" s="14"/>
     </row>
     <row r="355" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A355" s="1" t="s">
@@ -11018,17 +11018,17 @@
       </c>
     </row>
     <row r="398" spans="1:9" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A398" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="B398" s="9"/>
-      <c r="C398" s="9"/>
-      <c r="D398" s="9"/>
-      <c r="E398" s="9"/>
-      <c r="F398" s="9"/>
-      <c r="G398" s="9"/>
-      <c r="H398" s="9"/>
-      <c r="I398" s="9"/>
+      <c r="A398" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="B398" s="14"/>
+      <c r="C398" s="14"/>
+      <c r="D398" s="14"/>
+      <c r="E398" s="14"/>
+      <c r="F398" s="14"/>
+      <c r="G398" s="14"/>
+      <c r="H398" s="14"/>
+      <c r="I398" s="14"/>
     </row>
     <row r="399" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A399" s="1" t="s">
@@ -12140,17 +12140,17 @@
       </c>
     </row>
     <row r="442" spans="1:9" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A442" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="B442" s="9"/>
-      <c r="C442" s="9"/>
-      <c r="D442" s="9"/>
-      <c r="E442" s="9"/>
-      <c r="F442" s="9"/>
-      <c r="G442" s="9"/>
-      <c r="H442" s="9"/>
-      <c r="I442" s="9"/>
+      <c r="A442" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="B442" s="14"/>
+      <c r="C442" s="14"/>
+      <c r="D442" s="14"/>
+      <c r="E442" s="14"/>
+      <c r="F442" s="14"/>
+      <c r="G442" s="14"/>
+      <c r="H442" s="14"/>
+      <c r="I442" s="14"/>
     </row>
     <row r="443" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A443" s="1" t="s">
@@ -13262,17 +13262,17 @@
       </c>
     </row>
     <row r="486" spans="1:9" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A486" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="B486" s="9"/>
-      <c r="C486" s="9"/>
-      <c r="D486" s="9"/>
-      <c r="E486" s="9"/>
-      <c r="F486" s="9"/>
-      <c r="G486" s="9"/>
-      <c r="H486" s="9"/>
-      <c r="I486" s="9"/>
+      <c r="A486" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="B486" s="14"/>
+      <c r="C486" s="14"/>
+      <c r="D486" s="14"/>
+      <c r="E486" s="14"/>
+      <c r="F486" s="14"/>
+      <c r="G486" s="14"/>
+      <c r="H486" s="14"/>
+      <c r="I486" s="14"/>
     </row>
     <row r="487" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A487" s="1" t="s">
@@ -14385,6 +14385,484 @@
     </row>
   </sheetData>
   <mergeCells count="492">
+    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="A18:A19"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="A20:A21"/>
+    <mergeCell ref="B20:B21"/>
+    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="B22:B23"/>
+    <mergeCell ref="A24:A25"/>
+    <mergeCell ref="B24:B25"/>
+    <mergeCell ref="A26:A27"/>
+    <mergeCell ref="B26:B27"/>
+    <mergeCell ref="A28:A29"/>
+    <mergeCell ref="B28:B29"/>
+    <mergeCell ref="A30:A31"/>
+    <mergeCell ref="B30:B31"/>
+    <mergeCell ref="A32:A33"/>
+    <mergeCell ref="B32:B33"/>
+    <mergeCell ref="A34:A35"/>
+    <mergeCell ref="B34:B35"/>
+    <mergeCell ref="A36:A37"/>
+    <mergeCell ref="B36:B37"/>
+    <mergeCell ref="A38:A39"/>
+    <mergeCell ref="B38:B39"/>
+    <mergeCell ref="A40:A41"/>
+    <mergeCell ref="B40:B41"/>
+    <mergeCell ref="A42:A43"/>
+    <mergeCell ref="B42:B43"/>
+    <mergeCell ref="A46:I46"/>
+    <mergeCell ref="A48:A49"/>
+    <mergeCell ref="B48:B49"/>
+    <mergeCell ref="A50:A51"/>
+    <mergeCell ref="B50:B51"/>
+    <mergeCell ref="A52:A53"/>
+    <mergeCell ref="B52:B53"/>
+    <mergeCell ref="A54:A55"/>
+    <mergeCell ref="B54:B55"/>
+    <mergeCell ref="A56:A57"/>
+    <mergeCell ref="B56:B57"/>
+    <mergeCell ref="A58:A59"/>
+    <mergeCell ref="B58:B59"/>
+    <mergeCell ref="A60:A61"/>
+    <mergeCell ref="B60:B61"/>
+    <mergeCell ref="A62:A63"/>
+    <mergeCell ref="B62:B63"/>
+    <mergeCell ref="A64:A65"/>
+    <mergeCell ref="B64:B65"/>
+    <mergeCell ref="A66:A67"/>
+    <mergeCell ref="B66:B67"/>
+    <mergeCell ref="A68:A69"/>
+    <mergeCell ref="B68:B69"/>
+    <mergeCell ref="A70:A71"/>
+    <mergeCell ref="B70:B71"/>
+    <mergeCell ref="A72:A73"/>
+    <mergeCell ref="B72:B73"/>
+    <mergeCell ref="A74:A75"/>
+    <mergeCell ref="B74:B75"/>
+    <mergeCell ref="A76:A77"/>
+    <mergeCell ref="B76:B77"/>
+    <mergeCell ref="A78:A79"/>
+    <mergeCell ref="B78:B79"/>
+    <mergeCell ref="A80:A81"/>
+    <mergeCell ref="B80:B81"/>
+    <mergeCell ref="A82:A83"/>
+    <mergeCell ref="B82:B83"/>
+    <mergeCell ref="A84:A85"/>
+    <mergeCell ref="B84:B85"/>
+    <mergeCell ref="A86:A87"/>
+    <mergeCell ref="B86:B87"/>
+    <mergeCell ref="A90:I90"/>
+    <mergeCell ref="A92:A93"/>
+    <mergeCell ref="B92:B93"/>
+    <mergeCell ref="A94:A95"/>
+    <mergeCell ref="B94:B95"/>
+    <mergeCell ref="A96:A97"/>
+    <mergeCell ref="B96:B97"/>
+    <mergeCell ref="A98:A99"/>
+    <mergeCell ref="B98:B99"/>
+    <mergeCell ref="A100:A101"/>
+    <mergeCell ref="B100:B101"/>
+    <mergeCell ref="A102:A103"/>
+    <mergeCell ref="B102:B103"/>
+    <mergeCell ref="A104:A105"/>
+    <mergeCell ref="B104:B105"/>
+    <mergeCell ref="A106:A107"/>
+    <mergeCell ref="B106:B107"/>
+    <mergeCell ref="A108:A109"/>
+    <mergeCell ref="B108:B109"/>
+    <mergeCell ref="A110:A111"/>
+    <mergeCell ref="B110:B111"/>
+    <mergeCell ref="A112:A113"/>
+    <mergeCell ref="B112:B113"/>
+    <mergeCell ref="A114:A115"/>
+    <mergeCell ref="B114:B115"/>
+    <mergeCell ref="A116:A117"/>
+    <mergeCell ref="B116:B117"/>
+    <mergeCell ref="A118:A119"/>
+    <mergeCell ref="B118:B119"/>
+    <mergeCell ref="A120:A121"/>
+    <mergeCell ref="B120:B121"/>
+    <mergeCell ref="A122:A123"/>
+    <mergeCell ref="B122:B123"/>
+    <mergeCell ref="A124:A125"/>
+    <mergeCell ref="B124:B125"/>
+    <mergeCell ref="A126:A127"/>
+    <mergeCell ref="B126:B127"/>
+    <mergeCell ref="A128:A129"/>
+    <mergeCell ref="B128:B129"/>
+    <mergeCell ref="A130:A131"/>
+    <mergeCell ref="B130:B131"/>
+    <mergeCell ref="A134:I134"/>
+    <mergeCell ref="A136:A137"/>
+    <mergeCell ref="B136:B137"/>
+    <mergeCell ref="A138:A139"/>
+    <mergeCell ref="B138:B139"/>
+    <mergeCell ref="A140:A141"/>
+    <mergeCell ref="B140:B141"/>
+    <mergeCell ref="A142:A143"/>
+    <mergeCell ref="B142:B143"/>
+    <mergeCell ref="A144:A145"/>
+    <mergeCell ref="B144:B145"/>
+    <mergeCell ref="A146:A147"/>
+    <mergeCell ref="B146:B147"/>
+    <mergeCell ref="A148:A149"/>
+    <mergeCell ref="B148:B149"/>
+    <mergeCell ref="A150:A151"/>
+    <mergeCell ref="B150:B151"/>
+    <mergeCell ref="A152:A153"/>
+    <mergeCell ref="B152:B153"/>
+    <mergeCell ref="A154:A155"/>
+    <mergeCell ref="B154:B155"/>
+    <mergeCell ref="A156:A157"/>
+    <mergeCell ref="B156:B157"/>
+    <mergeCell ref="A158:A159"/>
+    <mergeCell ref="B158:B159"/>
+    <mergeCell ref="A160:A161"/>
+    <mergeCell ref="B160:B161"/>
+    <mergeCell ref="A162:A163"/>
+    <mergeCell ref="B162:B163"/>
+    <mergeCell ref="A164:A165"/>
+    <mergeCell ref="B164:B165"/>
+    <mergeCell ref="A166:A167"/>
+    <mergeCell ref="B166:B167"/>
+    <mergeCell ref="A168:A169"/>
+    <mergeCell ref="B168:B169"/>
+    <mergeCell ref="A170:A171"/>
+    <mergeCell ref="B170:B171"/>
+    <mergeCell ref="A172:A173"/>
+    <mergeCell ref="B172:B173"/>
+    <mergeCell ref="A174:A175"/>
+    <mergeCell ref="B174:B175"/>
+    <mergeCell ref="A178:I178"/>
+    <mergeCell ref="A180:A181"/>
+    <mergeCell ref="B180:B181"/>
+    <mergeCell ref="A182:A183"/>
+    <mergeCell ref="B182:B183"/>
+    <mergeCell ref="A184:A185"/>
+    <mergeCell ref="B184:B185"/>
+    <mergeCell ref="A186:A187"/>
+    <mergeCell ref="B186:B187"/>
+    <mergeCell ref="A188:A189"/>
+    <mergeCell ref="B188:B189"/>
+    <mergeCell ref="A190:A191"/>
+    <mergeCell ref="B190:B191"/>
+    <mergeCell ref="A192:A193"/>
+    <mergeCell ref="B192:B193"/>
+    <mergeCell ref="A194:A195"/>
+    <mergeCell ref="B194:B195"/>
+    <mergeCell ref="A196:A197"/>
+    <mergeCell ref="B196:B197"/>
+    <mergeCell ref="A198:A199"/>
+    <mergeCell ref="B198:B199"/>
+    <mergeCell ref="A200:A201"/>
+    <mergeCell ref="B200:B201"/>
+    <mergeCell ref="A202:A203"/>
+    <mergeCell ref="B202:B203"/>
+    <mergeCell ref="A204:A205"/>
+    <mergeCell ref="B204:B205"/>
+    <mergeCell ref="A206:A207"/>
+    <mergeCell ref="B206:B207"/>
+    <mergeCell ref="A208:A209"/>
+    <mergeCell ref="B208:B209"/>
+    <mergeCell ref="A210:A211"/>
+    <mergeCell ref="B210:B211"/>
+    <mergeCell ref="A212:A213"/>
+    <mergeCell ref="B212:B213"/>
+    <mergeCell ref="A214:A215"/>
+    <mergeCell ref="B214:B215"/>
+    <mergeCell ref="A216:A217"/>
+    <mergeCell ref="B216:B217"/>
+    <mergeCell ref="A218:A219"/>
+    <mergeCell ref="B218:B219"/>
+    <mergeCell ref="A222:I222"/>
+    <mergeCell ref="A224:A225"/>
+    <mergeCell ref="B224:B225"/>
+    <mergeCell ref="A226:A227"/>
+    <mergeCell ref="B226:B227"/>
+    <mergeCell ref="A228:A229"/>
+    <mergeCell ref="B228:B229"/>
+    <mergeCell ref="A230:A231"/>
+    <mergeCell ref="B230:B231"/>
+    <mergeCell ref="A232:A233"/>
+    <mergeCell ref="B232:B233"/>
+    <mergeCell ref="A234:A235"/>
+    <mergeCell ref="B234:B235"/>
+    <mergeCell ref="A236:A237"/>
+    <mergeCell ref="B236:B237"/>
+    <mergeCell ref="A238:A239"/>
+    <mergeCell ref="B238:B239"/>
+    <mergeCell ref="A240:A241"/>
+    <mergeCell ref="B240:B241"/>
+    <mergeCell ref="A242:A243"/>
+    <mergeCell ref="B242:B243"/>
+    <mergeCell ref="A244:A245"/>
+    <mergeCell ref="B244:B245"/>
+    <mergeCell ref="A246:A247"/>
+    <mergeCell ref="B246:B247"/>
+    <mergeCell ref="A248:A249"/>
+    <mergeCell ref="B248:B249"/>
+    <mergeCell ref="A250:A251"/>
+    <mergeCell ref="B250:B251"/>
+    <mergeCell ref="A252:A253"/>
+    <mergeCell ref="B252:B253"/>
+    <mergeCell ref="A254:A255"/>
+    <mergeCell ref="B254:B255"/>
+    <mergeCell ref="A256:A257"/>
+    <mergeCell ref="B256:B257"/>
+    <mergeCell ref="A258:A259"/>
+    <mergeCell ref="B258:B259"/>
+    <mergeCell ref="A260:A261"/>
+    <mergeCell ref="B260:B261"/>
+    <mergeCell ref="A262:A263"/>
+    <mergeCell ref="B262:B263"/>
+    <mergeCell ref="A266:I266"/>
+    <mergeCell ref="A268:A269"/>
+    <mergeCell ref="B268:B269"/>
+    <mergeCell ref="A270:A271"/>
+    <mergeCell ref="B270:B271"/>
+    <mergeCell ref="A272:A273"/>
+    <mergeCell ref="B272:B273"/>
+    <mergeCell ref="A274:A275"/>
+    <mergeCell ref="B274:B275"/>
+    <mergeCell ref="A276:A277"/>
+    <mergeCell ref="B276:B277"/>
+    <mergeCell ref="A278:A279"/>
+    <mergeCell ref="B278:B279"/>
+    <mergeCell ref="A280:A281"/>
+    <mergeCell ref="B280:B281"/>
+    <mergeCell ref="A282:A283"/>
+    <mergeCell ref="B282:B283"/>
+    <mergeCell ref="A284:A285"/>
+    <mergeCell ref="B284:B285"/>
+    <mergeCell ref="A286:A287"/>
+    <mergeCell ref="B286:B287"/>
+    <mergeCell ref="A288:A289"/>
+    <mergeCell ref="B288:B289"/>
+    <mergeCell ref="A290:A291"/>
+    <mergeCell ref="B290:B291"/>
+    <mergeCell ref="A292:A293"/>
+    <mergeCell ref="B292:B293"/>
+    <mergeCell ref="A294:A295"/>
+    <mergeCell ref="B294:B295"/>
+    <mergeCell ref="A296:A297"/>
+    <mergeCell ref="B296:B297"/>
+    <mergeCell ref="A298:A299"/>
+    <mergeCell ref="B298:B299"/>
+    <mergeCell ref="A300:A301"/>
+    <mergeCell ref="B300:B301"/>
+    <mergeCell ref="A302:A303"/>
+    <mergeCell ref="B302:B303"/>
+    <mergeCell ref="A304:A305"/>
+    <mergeCell ref="B304:B305"/>
+    <mergeCell ref="A306:A307"/>
+    <mergeCell ref="B306:B307"/>
+    <mergeCell ref="A310:I310"/>
+    <mergeCell ref="A312:A313"/>
+    <mergeCell ref="B312:B313"/>
+    <mergeCell ref="A314:A315"/>
+    <mergeCell ref="B314:B315"/>
+    <mergeCell ref="A316:A317"/>
+    <mergeCell ref="B316:B317"/>
+    <mergeCell ref="A318:A319"/>
+    <mergeCell ref="B318:B319"/>
+    <mergeCell ref="A320:A321"/>
+    <mergeCell ref="B320:B321"/>
+    <mergeCell ref="A322:A323"/>
+    <mergeCell ref="B322:B323"/>
+    <mergeCell ref="A324:A325"/>
+    <mergeCell ref="B324:B325"/>
+    <mergeCell ref="A326:A327"/>
+    <mergeCell ref="B326:B327"/>
+    <mergeCell ref="A328:A329"/>
+    <mergeCell ref="B328:B329"/>
+    <mergeCell ref="A330:A331"/>
+    <mergeCell ref="B330:B331"/>
+    <mergeCell ref="A332:A333"/>
+    <mergeCell ref="B332:B333"/>
+    <mergeCell ref="A334:A335"/>
+    <mergeCell ref="B334:B335"/>
+    <mergeCell ref="A336:A337"/>
+    <mergeCell ref="B336:B337"/>
+    <mergeCell ref="A338:A339"/>
+    <mergeCell ref="B338:B339"/>
+    <mergeCell ref="A340:A341"/>
+    <mergeCell ref="B340:B341"/>
+    <mergeCell ref="A342:A343"/>
+    <mergeCell ref="B342:B343"/>
+    <mergeCell ref="A344:A345"/>
+    <mergeCell ref="B344:B345"/>
+    <mergeCell ref="A346:A347"/>
+    <mergeCell ref="B346:B347"/>
+    <mergeCell ref="A348:A349"/>
+    <mergeCell ref="B348:B349"/>
+    <mergeCell ref="A350:A351"/>
+    <mergeCell ref="B350:B351"/>
+    <mergeCell ref="A354:I354"/>
+    <mergeCell ref="A356:A357"/>
+    <mergeCell ref="B356:B357"/>
+    <mergeCell ref="A358:A359"/>
+    <mergeCell ref="B358:B359"/>
+    <mergeCell ref="A360:A361"/>
+    <mergeCell ref="B360:B361"/>
+    <mergeCell ref="A362:A363"/>
+    <mergeCell ref="B362:B363"/>
+    <mergeCell ref="A364:A365"/>
+    <mergeCell ref="B364:B365"/>
+    <mergeCell ref="A366:A367"/>
+    <mergeCell ref="B366:B367"/>
+    <mergeCell ref="A368:A369"/>
+    <mergeCell ref="B368:B369"/>
+    <mergeCell ref="A370:A371"/>
+    <mergeCell ref="B370:B371"/>
+    <mergeCell ref="A372:A373"/>
+    <mergeCell ref="B372:B373"/>
+    <mergeCell ref="A374:A375"/>
+    <mergeCell ref="B374:B375"/>
+    <mergeCell ref="A376:A377"/>
+    <mergeCell ref="B376:B377"/>
+    <mergeCell ref="A378:A379"/>
+    <mergeCell ref="B378:B379"/>
+    <mergeCell ref="A380:A381"/>
+    <mergeCell ref="B380:B381"/>
+    <mergeCell ref="A382:A383"/>
+    <mergeCell ref="B382:B383"/>
+    <mergeCell ref="A384:A385"/>
+    <mergeCell ref="B384:B385"/>
+    <mergeCell ref="A386:A387"/>
+    <mergeCell ref="B386:B387"/>
+    <mergeCell ref="A388:A389"/>
+    <mergeCell ref="B388:B389"/>
+    <mergeCell ref="A390:A391"/>
+    <mergeCell ref="B390:B391"/>
+    <mergeCell ref="A392:A393"/>
+    <mergeCell ref="B392:B393"/>
+    <mergeCell ref="A394:A395"/>
+    <mergeCell ref="B394:B395"/>
+    <mergeCell ref="A398:I398"/>
+    <mergeCell ref="A400:A401"/>
+    <mergeCell ref="B400:B401"/>
+    <mergeCell ref="A402:A403"/>
+    <mergeCell ref="B402:B403"/>
+    <mergeCell ref="A404:A405"/>
+    <mergeCell ref="B404:B405"/>
+    <mergeCell ref="A406:A407"/>
+    <mergeCell ref="B406:B407"/>
+    <mergeCell ref="A408:A409"/>
+    <mergeCell ref="B408:B409"/>
+    <mergeCell ref="A410:A411"/>
+    <mergeCell ref="B410:B411"/>
+    <mergeCell ref="A412:A413"/>
+    <mergeCell ref="B412:B413"/>
+    <mergeCell ref="A414:A415"/>
+    <mergeCell ref="B414:B415"/>
+    <mergeCell ref="A416:A417"/>
+    <mergeCell ref="B416:B417"/>
+    <mergeCell ref="A418:A419"/>
+    <mergeCell ref="B418:B419"/>
+    <mergeCell ref="A420:A421"/>
+    <mergeCell ref="B420:B421"/>
+    <mergeCell ref="A422:A423"/>
+    <mergeCell ref="B422:B423"/>
+    <mergeCell ref="A424:A425"/>
+    <mergeCell ref="B424:B425"/>
+    <mergeCell ref="A426:A427"/>
+    <mergeCell ref="B426:B427"/>
+    <mergeCell ref="A428:A429"/>
+    <mergeCell ref="B428:B429"/>
+    <mergeCell ref="A430:A431"/>
+    <mergeCell ref="B430:B431"/>
+    <mergeCell ref="A432:A433"/>
+    <mergeCell ref="B432:B433"/>
+    <mergeCell ref="A434:A435"/>
+    <mergeCell ref="B434:B435"/>
+    <mergeCell ref="A436:A437"/>
+    <mergeCell ref="B436:B437"/>
+    <mergeCell ref="A438:A439"/>
+    <mergeCell ref="B438:B439"/>
+    <mergeCell ref="A442:I442"/>
+    <mergeCell ref="A444:A445"/>
+    <mergeCell ref="B444:B445"/>
+    <mergeCell ref="A446:A447"/>
+    <mergeCell ref="B446:B447"/>
+    <mergeCell ref="A448:A449"/>
+    <mergeCell ref="B448:B449"/>
+    <mergeCell ref="A450:A451"/>
+    <mergeCell ref="B450:B451"/>
+    <mergeCell ref="A452:A453"/>
+    <mergeCell ref="B452:B453"/>
+    <mergeCell ref="A454:A455"/>
+    <mergeCell ref="B454:B455"/>
+    <mergeCell ref="A456:A457"/>
+    <mergeCell ref="B456:B457"/>
+    <mergeCell ref="A458:A459"/>
+    <mergeCell ref="B458:B459"/>
+    <mergeCell ref="A460:A461"/>
+    <mergeCell ref="B460:B461"/>
+    <mergeCell ref="A462:A463"/>
+    <mergeCell ref="B462:B463"/>
+    <mergeCell ref="A464:A465"/>
+    <mergeCell ref="B464:B465"/>
+    <mergeCell ref="A466:A467"/>
+    <mergeCell ref="B466:B467"/>
+    <mergeCell ref="A468:A469"/>
+    <mergeCell ref="B468:B469"/>
+    <mergeCell ref="A470:A471"/>
+    <mergeCell ref="B470:B471"/>
+    <mergeCell ref="A472:A473"/>
+    <mergeCell ref="B472:B473"/>
+    <mergeCell ref="A474:A475"/>
+    <mergeCell ref="B474:B475"/>
+    <mergeCell ref="A476:A477"/>
+    <mergeCell ref="B476:B477"/>
+    <mergeCell ref="A478:A479"/>
+    <mergeCell ref="B478:B479"/>
+    <mergeCell ref="A480:A481"/>
+    <mergeCell ref="B480:B481"/>
+    <mergeCell ref="A482:A483"/>
+    <mergeCell ref="B482:B483"/>
+    <mergeCell ref="A486:I486"/>
+    <mergeCell ref="A488:A489"/>
+    <mergeCell ref="B488:B489"/>
+    <mergeCell ref="A490:A491"/>
+    <mergeCell ref="B490:B491"/>
+    <mergeCell ref="A492:A493"/>
+    <mergeCell ref="B492:B493"/>
+    <mergeCell ref="A494:A495"/>
+    <mergeCell ref="B494:B495"/>
+    <mergeCell ref="A496:A497"/>
+    <mergeCell ref="B496:B497"/>
+    <mergeCell ref="A498:A499"/>
+    <mergeCell ref="B498:B499"/>
+    <mergeCell ref="A500:A501"/>
+    <mergeCell ref="B500:B501"/>
+    <mergeCell ref="A502:A503"/>
+    <mergeCell ref="B502:B503"/>
+    <mergeCell ref="A504:A505"/>
+    <mergeCell ref="B504:B505"/>
+    <mergeCell ref="A506:A507"/>
+    <mergeCell ref="B506:B507"/>
+    <mergeCell ref="A508:A509"/>
+    <mergeCell ref="B508:B509"/>
+    <mergeCell ref="A510:A511"/>
+    <mergeCell ref="B510:B511"/>
+    <mergeCell ref="A512:A513"/>
+    <mergeCell ref="B512:B513"/>
     <mergeCell ref="A524:A525"/>
     <mergeCell ref="B524:B525"/>
     <mergeCell ref="A526:A527"/>
@@ -14399,484 +14877,6 @@
     <mergeCell ref="B520:B521"/>
     <mergeCell ref="A522:A523"/>
     <mergeCell ref="B522:B523"/>
-    <mergeCell ref="A504:A505"/>
-    <mergeCell ref="B504:B505"/>
-    <mergeCell ref="A506:A507"/>
-    <mergeCell ref="B506:B507"/>
-    <mergeCell ref="A508:A509"/>
-    <mergeCell ref="B508:B509"/>
-    <mergeCell ref="A510:A511"/>
-    <mergeCell ref="B510:B511"/>
-    <mergeCell ref="A512:A513"/>
-    <mergeCell ref="B512:B513"/>
-    <mergeCell ref="A494:A495"/>
-    <mergeCell ref="B494:B495"/>
-    <mergeCell ref="A496:A497"/>
-    <mergeCell ref="B496:B497"/>
-    <mergeCell ref="A498:A499"/>
-    <mergeCell ref="B498:B499"/>
-    <mergeCell ref="A500:A501"/>
-    <mergeCell ref="B500:B501"/>
-    <mergeCell ref="A502:A503"/>
-    <mergeCell ref="B502:B503"/>
-    <mergeCell ref="A482:A483"/>
-    <mergeCell ref="B482:B483"/>
-    <mergeCell ref="A486:I486"/>
-    <mergeCell ref="A488:A489"/>
-    <mergeCell ref="B488:B489"/>
-    <mergeCell ref="A490:A491"/>
-    <mergeCell ref="B490:B491"/>
-    <mergeCell ref="A492:A493"/>
-    <mergeCell ref="B492:B493"/>
-    <mergeCell ref="A472:A473"/>
-    <mergeCell ref="B472:B473"/>
-    <mergeCell ref="A474:A475"/>
-    <mergeCell ref="B474:B475"/>
-    <mergeCell ref="A476:A477"/>
-    <mergeCell ref="B476:B477"/>
-    <mergeCell ref="A478:A479"/>
-    <mergeCell ref="B478:B479"/>
-    <mergeCell ref="A480:A481"/>
-    <mergeCell ref="B480:B481"/>
-    <mergeCell ref="A462:A463"/>
-    <mergeCell ref="B462:B463"/>
-    <mergeCell ref="A464:A465"/>
-    <mergeCell ref="B464:B465"/>
-    <mergeCell ref="A466:A467"/>
-    <mergeCell ref="B466:B467"/>
-    <mergeCell ref="A468:A469"/>
-    <mergeCell ref="B468:B469"/>
-    <mergeCell ref="A470:A471"/>
-    <mergeCell ref="B470:B471"/>
-    <mergeCell ref="A452:A453"/>
-    <mergeCell ref="B452:B453"/>
-    <mergeCell ref="A454:A455"/>
-    <mergeCell ref="B454:B455"/>
-    <mergeCell ref="A456:A457"/>
-    <mergeCell ref="B456:B457"/>
-    <mergeCell ref="A458:A459"/>
-    <mergeCell ref="B458:B459"/>
-    <mergeCell ref="A460:A461"/>
-    <mergeCell ref="B460:B461"/>
-    <mergeCell ref="A442:I442"/>
-    <mergeCell ref="A444:A445"/>
-    <mergeCell ref="B444:B445"/>
-    <mergeCell ref="A446:A447"/>
-    <mergeCell ref="B446:B447"/>
-    <mergeCell ref="A448:A449"/>
-    <mergeCell ref="B448:B449"/>
-    <mergeCell ref="A450:A451"/>
-    <mergeCell ref="B450:B451"/>
-    <mergeCell ref="A430:A431"/>
-    <mergeCell ref="B430:B431"/>
-    <mergeCell ref="A432:A433"/>
-    <mergeCell ref="B432:B433"/>
-    <mergeCell ref="A434:A435"/>
-    <mergeCell ref="B434:B435"/>
-    <mergeCell ref="A436:A437"/>
-    <mergeCell ref="B436:B437"/>
-    <mergeCell ref="A438:A439"/>
-    <mergeCell ref="B438:B439"/>
-    <mergeCell ref="A420:A421"/>
-    <mergeCell ref="B420:B421"/>
-    <mergeCell ref="A422:A423"/>
-    <mergeCell ref="B422:B423"/>
-    <mergeCell ref="A424:A425"/>
-    <mergeCell ref="B424:B425"/>
-    <mergeCell ref="A426:A427"/>
-    <mergeCell ref="B426:B427"/>
-    <mergeCell ref="A428:A429"/>
-    <mergeCell ref="B428:B429"/>
-    <mergeCell ref="A410:A411"/>
-    <mergeCell ref="B410:B411"/>
-    <mergeCell ref="A412:A413"/>
-    <mergeCell ref="B412:B413"/>
-    <mergeCell ref="A414:A415"/>
-    <mergeCell ref="B414:B415"/>
-    <mergeCell ref="A416:A417"/>
-    <mergeCell ref="B416:B417"/>
-    <mergeCell ref="A418:A419"/>
-    <mergeCell ref="B418:B419"/>
-    <mergeCell ref="A400:A401"/>
-    <mergeCell ref="B400:B401"/>
-    <mergeCell ref="A402:A403"/>
-    <mergeCell ref="B402:B403"/>
-    <mergeCell ref="A404:A405"/>
-    <mergeCell ref="B404:B405"/>
-    <mergeCell ref="A406:A407"/>
-    <mergeCell ref="B406:B407"/>
-    <mergeCell ref="A408:A409"/>
-    <mergeCell ref="B408:B409"/>
-    <mergeCell ref="A388:A389"/>
-    <mergeCell ref="B388:B389"/>
-    <mergeCell ref="A390:A391"/>
-    <mergeCell ref="B390:B391"/>
-    <mergeCell ref="A392:A393"/>
-    <mergeCell ref="B392:B393"/>
-    <mergeCell ref="A394:A395"/>
-    <mergeCell ref="B394:B395"/>
-    <mergeCell ref="A398:I398"/>
-    <mergeCell ref="A378:A379"/>
-    <mergeCell ref="B378:B379"/>
-    <mergeCell ref="A380:A381"/>
-    <mergeCell ref="B380:B381"/>
-    <mergeCell ref="A382:A383"/>
-    <mergeCell ref="B382:B383"/>
-    <mergeCell ref="A384:A385"/>
-    <mergeCell ref="B384:B385"/>
-    <mergeCell ref="A386:A387"/>
-    <mergeCell ref="B386:B387"/>
-    <mergeCell ref="A368:A369"/>
-    <mergeCell ref="B368:B369"/>
-    <mergeCell ref="A370:A371"/>
-    <mergeCell ref="B370:B371"/>
-    <mergeCell ref="A372:A373"/>
-    <mergeCell ref="B372:B373"/>
-    <mergeCell ref="A374:A375"/>
-    <mergeCell ref="B374:B375"/>
-    <mergeCell ref="A376:A377"/>
-    <mergeCell ref="B376:B377"/>
-    <mergeCell ref="A358:A359"/>
-    <mergeCell ref="B358:B359"/>
-    <mergeCell ref="A360:A361"/>
-    <mergeCell ref="B360:B361"/>
-    <mergeCell ref="A362:A363"/>
-    <mergeCell ref="B362:B363"/>
-    <mergeCell ref="A364:A365"/>
-    <mergeCell ref="B364:B365"/>
-    <mergeCell ref="A366:A367"/>
-    <mergeCell ref="B366:B367"/>
-    <mergeCell ref="A346:A347"/>
-    <mergeCell ref="B346:B347"/>
-    <mergeCell ref="A348:A349"/>
-    <mergeCell ref="B348:B349"/>
-    <mergeCell ref="A350:A351"/>
-    <mergeCell ref="B350:B351"/>
-    <mergeCell ref="A354:I354"/>
-    <mergeCell ref="A356:A357"/>
-    <mergeCell ref="B356:B357"/>
-    <mergeCell ref="A336:A337"/>
-    <mergeCell ref="B336:B337"/>
-    <mergeCell ref="A338:A339"/>
-    <mergeCell ref="B338:B339"/>
-    <mergeCell ref="A340:A341"/>
-    <mergeCell ref="B340:B341"/>
-    <mergeCell ref="A342:A343"/>
-    <mergeCell ref="B342:B343"/>
-    <mergeCell ref="A344:A345"/>
-    <mergeCell ref="B344:B345"/>
-    <mergeCell ref="A326:A327"/>
-    <mergeCell ref="B326:B327"/>
-    <mergeCell ref="A328:A329"/>
-    <mergeCell ref="B328:B329"/>
-    <mergeCell ref="A330:A331"/>
-    <mergeCell ref="B330:B331"/>
-    <mergeCell ref="A332:A333"/>
-    <mergeCell ref="B332:B333"/>
-    <mergeCell ref="A334:A335"/>
-    <mergeCell ref="B334:B335"/>
-    <mergeCell ref="A316:A317"/>
-    <mergeCell ref="B316:B317"/>
-    <mergeCell ref="A318:A319"/>
-    <mergeCell ref="B318:B319"/>
-    <mergeCell ref="A320:A321"/>
-    <mergeCell ref="B320:B321"/>
-    <mergeCell ref="A322:A323"/>
-    <mergeCell ref="B322:B323"/>
-    <mergeCell ref="A324:A325"/>
-    <mergeCell ref="B324:B325"/>
-    <mergeCell ref="A304:A305"/>
-    <mergeCell ref="B304:B305"/>
-    <mergeCell ref="A306:A307"/>
-    <mergeCell ref="B306:B307"/>
-    <mergeCell ref="A310:I310"/>
-    <mergeCell ref="A312:A313"/>
-    <mergeCell ref="B312:B313"/>
-    <mergeCell ref="A314:A315"/>
-    <mergeCell ref="B314:B315"/>
-    <mergeCell ref="A294:A295"/>
-    <mergeCell ref="B294:B295"/>
-    <mergeCell ref="A296:A297"/>
-    <mergeCell ref="B296:B297"/>
-    <mergeCell ref="A298:A299"/>
-    <mergeCell ref="B298:B299"/>
-    <mergeCell ref="A300:A301"/>
-    <mergeCell ref="B300:B301"/>
-    <mergeCell ref="A302:A303"/>
-    <mergeCell ref="B302:B303"/>
-    <mergeCell ref="A284:A285"/>
-    <mergeCell ref="B284:B285"/>
-    <mergeCell ref="A286:A287"/>
-    <mergeCell ref="B286:B287"/>
-    <mergeCell ref="A288:A289"/>
-    <mergeCell ref="B288:B289"/>
-    <mergeCell ref="A290:A291"/>
-    <mergeCell ref="B290:B291"/>
-    <mergeCell ref="A292:A293"/>
-    <mergeCell ref="B292:B293"/>
-    <mergeCell ref="A274:A275"/>
-    <mergeCell ref="B274:B275"/>
-    <mergeCell ref="A276:A277"/>
-    <mergeCell ref="B276:B277"/>
-    <mergeCell ref="A278:A279"/>
-    <mergeCell ref="B278:B279"/>
-    <mergeCell ref="A280:A281"/>
-    <mergeCell ref="B280:B281"/>
-    <mergeCell ref="A282:A283"/>
-    <mergeCell ref="B282:B283"/>
-    <mergeCell ref="A262:A263"/>
-    <mergeCell ref="B262:B263"/>
-    <mergeCell ref="A266:I266"/>
-    <mergeCell ref="A268:A269"/>
-    <mergeCell ref="B268:B269"/>
-    <mergeCell ref="A270:A271"/>
-    <mergeCell ref="B270:B271"/>
-    <mergeCell ref="A272:A273"/>
-    <mergeCell ref="B272:B273"/>
-    <mergeCell ref="A252:A253"/>
-    <mergeCell ref="B252:B253"/>
-    <mergeCell ref="A254:A255"/>
-    <mergeCell ref="B254:B255"/>
-    <mergeCell ref="A256:A257"/>
-    <mergeCell ref="B256:B257"/>
-    <mergeCell ref="A258:A259"/>
-    <mergeCell ref="B258:B259"/>
-    <mergeCell ref="A260:A261"/>
-    <mergeCell ref="B260:B261"/>
-    <mergeCell ref="A242:A243"/>
-    <mergeCell ref="B242:B243"/>
-    <mergeCell ref="A244:A245"/>
-    <mergeCell ref="B244:B245"/>
-    <mergeCell ref="A246:A247"/>
-    <mergeCell ref="B246:B247"/>
-    <mergeCell ref="A248:A249"/>
-    <mergeCell ref="B248:B249"/>
-    <mergeCell ref="A250:A251"/>
-    <mergeCell ref="B250:B251"/>
-    <mergeCell ref="A232:A233"/>
-    <mergeCell ref="B232:B233"/>
-    <mergeCell ref="A234:A235"/>
-    <mergeCell ref="B234:B235"/>
-    <mergeCell ref="A236:A237"/>
-    <mergeCell ref="B236:B237"/>
-    <mergeCell ref="A238:A239"/>
-    <mergeCell ref="B238:B239"/>
-    <mergeCell ref="A240:A241"/>
-    <mergeCell ref="B240:B241"/>
-    <mergeCell ref="A222:I222"/>
-    <mergeCell ref="A224:A225"/>
-    <mergeCell ref="B224:B225"/>
-    <mergeCell ref="A226:A227"/>
-    <mergeCell ref="B226:B227"/>
-    <mergeCell ref="A228:A229"/>
-    <mergeCell ref="B228:B229"/>
-    <mergeCell ref="A230:A231"/>
-    <mergeCell ref="B230:B231"/>
-    <mergeCell ref="A210:A211"/>
-    <mergeCell ref="B210:B211"/>
-    <mergeCell ref="A212:A213"/>
-    <mergeCell ref="B212:B213"/>
-    <mergeCell ref="A214:A215"/>
-    <mergeCell ref="B214:B215"/>
-    <mergeCell ref="A216:A217"/>
-    <mergeCell ref="B216:B217"/>
-    <mergeCell ref="A218:A219"/>
-    <mergeCell ref="B218:B219"/>
-    <mergeCell ref="A200:A201"/>
-    <mergeCell ref="B200:B201"/>
-    <mergeCell ref="A202:A203"/>
-    <mergeCell ref="B202:B203"/>
-    <mergeCell ref="A204:A205"/>
-    <mergeCell ref="B204:B205"/>
-    <mergeCell ref="A206:A207"/>
-    <mergeCell ref="B206:B207"/>
-    <mergeCell ref="A208:A209"/>
-    <mergeCell ref="B208:B209"/>
-    <mergeCell ref="A190:A191"/>
-    <mergeCell ref="B190:B191"/>
-    <mergeCell ref="A192:A193"/>
-    <mergeCell ref="B192:B193"/>
-    <mergeCell ref="A194:A195"/>
-    <mergeCell ref="B194:B195"/>
-    <mergeCell ref="A196:A197"/>
-    <mergeCell ref="B196:B197"/>
-    <mergeCell ref="A198:A199"/>
-    <mergeCell ref="B198:B199"/>
-    <mergeCell ref="A180:A181"/>
-    <mergeCell ref="B180:B181"/>
-    <mergeCell ref="A182:A183"/>
-    <mergeCell ref="B182:B183"/>
-    <mergeCell ref="A184:A185"/>
-    <mergeCell ref="B184:B185"/>
-    <mergeCell ref="A186:A187"/>
-    <mergeCell ref="B186:B187"/>
-    <mergeCell ref="A188:A189"/>
-    <mergeCell ref="B188:B189"/>
-    <mergeCell ref="A168:A169"/>
-    <mergeCell ref="B168:B169"/>
-    <mergeCell ref="A170:A171"/>
-    <mergeCell ref="B170:B171"/>
-    <mergeCell ref="A172:A173"/>
-    <mergeCell ref="B172:B173"/>
-    <mergeCell ref="A174:A175"/>
-    <mergeCell ref="B174:B175"/>
-    <mergeCell ref="A178:I178"/>
-    <mergeCell ref="A158:A159"/>
-    <mergeCell ref="B158:B159"/>
-    <mergeCell ref="A160:A161"/>
-    <mergeCell ref="B160:B161"/>
-    <mergeCell ref="A162:A163"/>
-    <mergeCell ref="B162:B163"/>
-    <mergeCell ref="A164:A165"/>
-    <mergeCell ref="B164:B165"/>
-    <mergeCell ref="A166:A167"/>
-    <mergeCell ref="B166:B167"/>
-    <mergeCell ref="A148:A149"/>
-    <mergeCell ref="B148:B149"/>
-    <mergeCell ref="A150:A151"/>
-    <mergeCell ref="B150:B151"/>
-    <mergeCell ref="A152:A153"/>
-    <mergeCell ref="B152:B153"/>
-    <mergeCell ref="A154:A155"/>
-    <mergeCell ref="B154:B155"/>
-    <mergeCell ref="A156:A157"/>
-    <mergeCell ref="B156:B157"/>
-    <mergeCell ref="A138:A139"/>
-    <mergeCell ref="B138:B139"/>
-    <mergeCell ref="A140:A141"/>
-    <mergeCell ref="B140:B141"/>
-    <mergeCell ref="A142:A143"/>
-    <mergeCell ref="B142:B143"/>
-    <mergeCell ref="A144:A145"/>
-    <mergeCell ref="B144:B145"/>
-    <mergeCell ref="A146:A147"/>
-    <mergeCell ref="B146:B147"/>
-    <mergeCell ref="A126:A127"/>
-    <mergeCell ref="B126:B127"/>
-    <mergeCell ref="A128:A129"/>
-    <mergeCell ref="B128:B129"/>
-    <mergeCell ref="A130:A131"/>
-    <mergeCell ref="B130:B131"/>
-    <mergeCell ref="A134:I134"/>
-    <mergeCell ref="A136:A137"/>
-    <mergeCell ref="B136:B137"/>
-    <mergeCell ref="A116:A117"/>
-    <mergeCell ref="B116:B117"/>
-    <mergeCell ref="A118:A119"/>
-    <mergeCell ref="B118:B119"/>
-    <mergeCell ref="A120:A121"/>
-    <mergeCell ref="B120:B121"/>
-    <mergeCell ref="A122:A123"/>
-    <mergeCell ref="B122:B123"/>
-    <mergeCell ref="A124:A125"/>
-    <mergeCell ref="B124:B125"/>
-    <mergeCell ref="A106:A107"/>
-    <mergeCell ref="B106:B107"/>
-    <mergeCell ref="A108:A109"/>
-    <mergeCell ref="B108:B109"/>
-    <mergeCell ref="A110:A111"/>
-    <mergeCell ref="B110:B111"/>
-    <mergeCell ref="A112:A113"/>
-    <mergeCell ref="B112:B113"/>
-    <mergeCell ref="A114:A115"/>
-    <mergeCell ref="B114:B115"/>
-    <mergeCell ref="A96:A97"/>
-    <mergeCell ref="B96:B97"/>
-    <mergeCell ref="A98:A99"/>
-    <mergeCell ref="B98:B99"/>
-    <mergeCell ref="A100:A101"/>
-    <mergeCell ref="B100:B101"/>
-    <mergeCell ref="A102:A103"/>
-    <mergeCell ref="B102:B103"/>
-    <mergeCell ref="A104:A105"/>
-    <mergeCell ref="B104:B105"/>
-    <mergeCell ref="A84:A85"/>
-    <mergeCell ref="B84:B85"/>
-    <mergeCell ref="A86:A87"/>
-    <mergeCell ref="B86:B87"/>
-    <mergeCell ref="A90:I90"/>
-    <mergeCell ref="A92:A93"/>
-    <mergeCell ref="B92:B93"/>
-    <mergeCell ref="A94:A95"/>
-    <mergeCell ref="B94:B95"/>
-    <mergeCell ref="A74:A75"/>
-    <mergeCell ref="B74:B75"/>
-    <mergeCell ref="A76:A77"/>
-    <mergeCell ref="B76:B77"/>
-    <mergeCell ref="A78:A79"/>
-    <mergeCell ref="B78:B79"/>
-    <mergeCell ref="A80:A81"/>
-    <mergeCell ref="B80:B81"/>
-    <mergeCell ref="A82:A83"/>
-    <mergeCell ref="B82:B83"/>
-    <mergeCell ref="A64:A65"/>
-    <mergeCell ref="B64:B65"/>
-    <mergeCell ref="A66:A67"/>
-    <mergeCell ref="B66:B67"/>
-    <mergeCell ref="A68:A69"/>
-    <mergeCell ref="B68:B69"/>
-    <mergeCell ref="A70:A71"/>
-    <mergeCell ref="B70:B71"/>
-    <mergeCell ref="A72:A73"/>
-    <mergeCell ref="B72:B73"/>
-    <mergeCell ref="A54:A55"/>
-    <mergeCell ref="B54:B55"/>
-    <mergeCell ref="A56:A57"/>
-    <mergeCell ref="B56:B57"/>
-    <mergeCell ref="A58:A59"/>
-    <mergeCell ref="B58:B59"/>
-    <mergeCell ref="A60:A61"/>
-    <mergeCell ref="B60:B61"/>
-    <mergeCell ref="A62:A63"/>
-    <mergeCell ref="B62:B63"/>
-    <mergeCell ref="A42:A43"/>
-    <mergeCell ref="B42:B43"/>
-    <mergeCell ref="A46:I46"/>
-    <mergeCell ref="A48:A49"/>
-    <mergeCell ref="B48:B49"/>
-    <mergeCell ref="A50:A51"/>
-    <mergeCell ref="B50:B51"/>
-    <mergeCell ref="A52:A53"/>
-    <mergeCell ref="B52:B53"/>
-    <mergeCell ref="A32:A33"/>
-    <mergeCell ref="B32:B33"/>
-    <mergeCell ref="A34:A35"/>
-    <mergeCell ref="B34:B35"/>
-    <mergeCell ref="A36:A37"/>
-    <mergeCell ref="B36:B37"/>
-    <mergeCell ref="A38:A39"/>
-    <mergeCell ref="B38:B39"/>
-    <mergeCell ref="A40:A41"/>
-    <mergeCell ref="B40:B41"/>
-    <mergeCell ref="A22:A23"/>
-    <mergeCell ref="B22:B23"/>
-    <mergeCell ref="A24:A25"/>
-    <mergeCell ref="B24:B25"/>
-    <mergeCell ref="A26:A27"/>
-    <mergeCell ref="B26:B27"/>
-    <mergeCell ref="A28:A29"/>
-    <mergeCell ref="B28:B29"/>
-    <mergeCell ref="A30:A31"/>
-    <mergeCell ref="B30:B31"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="B14:B15"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="A18:A19"/>
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="A20:A21"/>
-    <mergeCell ref="B20:B21"/>
-    <mergeCell ref="A2:I2"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="B10:B11"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
@@ -14896,17 +14896,17 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:9" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="9"/>
-      <c r="C2" s="9"/>
-      <c r="D2" s="9"/>
-      <c r="E2" s="9"/>
-      <c r="F2" s="9"/>
-      <c r="G2" s="9"/>
-      <c r="H2" s="9"/>
-      <c r="I2" s="9"/>
+      <c r="B2" s="14"/>
+      <c r="C2" s="14"/>
+      <c r="D2" s="14"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="14"/>
+      <c r="G2" s="14"/>
+      <c r="H2" s="14"/>
+      <c r="I2" s="14"/>
     </row>
     <row r="3" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
@@ -14942,10 +14942,10 @@
         <v>1</v>
       </c>
       <c r="B4" s="17" t="s">
+        <v>128</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>129</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>130</v>
       </c>
       <c r="D4" s="3">
         <v>300</v>
@@ -14971,13 +14971,13 @@
       <c r="B5" s="18"/>
       <c r="C5" s="2"/>
       <c r="D5" s="4" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="G5" s="4" t="s">
         <v>10</v>
@@ -14994,10 +14994,10 @@
         <v>2</v>
       </c>
       <c r="B6" s="15" t="s">
+        <v>131</v>
+      </c>
+      <c r="C6" s="5" t="s">
         <v>132</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>133</v>
       </c>
       <c r="D6" s="6">
         <v>300</v>
@@ -15023,13 +15023,13 @@
       <c r="B7" s="16"/>
       <c r="C7" s="5"/>
       <c r="D7" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="E7" s="7" t="s">
         <v>134</v>
       </c>
-      <c r="E7" s="7" t="s">
-        <v>135</v>
-      </c>
       <c r="F7" s="7" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="G7" s="7" t="s">
         <v>10</v>
@@ -15046,10 +15046,10 @@
         <v>3</v>
       </c>
       <c r="B8" s="17" t="s">
+        <v>135</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>136</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>137</v>
       </c>
       <c r="D8" s="3"/>
       <c r="E8" s="3">
@@ -15074,10 +15074,10 @@
       <c r="C9" s="2"/>
       <c r="D9" s="4"/>
       <c r="E9" s="4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="G9" s="4" t="s">
         <v>10</v>
@@ -15094,10 +15094,10 @@
         <v>4</v>
       </c>
       <c r="B10" s="15" t="s">
+        <v>138</v>
+      </c>
+      <c r="C10" s="5" t="s">
         <v>139</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>140</v>
       </c>
       <c r="D10" s="6">
         <v>300</v>
@@ -15123,13 +15123,13 @@
       <c r="B11" s="16"/>
       <c r="C11" s="5"/>
       <c r="D11" s="7" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="G11" s="7" t="s">
         <v>10</v>
@@ -15146,10 +15146,10 @@
         <v>5</v>
       </c>
       <c r="B12" s="17" t="s">
+        <v>141</v>
+      </c>
+      <c r="C12" s="2" t="s">
         <v>142</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>143</v>
       </c>
       <c r="D12" s="3">
         <v>300</v>
@@ -15175,13 +15175,13 @@
       <c r="B13" s="18"/>
       <c r="C13" s="2"/>
       <c r="D13" s="4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G13" s="4" t="s">
         <v>10</v>
@@ -16004,17 +16004,17 @@
       </c>
     </row>
     <row r="46" spans="1:9" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="9" t="s">
+      <c r="A46" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="B46" s="9"/>
-      <c r="C46" s="9"/>
-      <c r="D46" s="9"/>
-      <c r="E46" s="9"/>
-      <c r="F46" s="9"/>
-      <c r="G46" s="9"/>
-      <c r="H46" s="9"/>
-      <c r="I46" s="9"/>
+      <c r="B46" s="14"/>
+      <c r="C46" s="14"/>
+      <c r="D46" s="14"/>
+      <c r="E46" s="14"/>
+      <c r="F46" s="14"/>
+      <c r="G46" s="14"/>
+      <c r="H46" s="14"/>
+      <c r="I46" s="14"/>
     </row>
     <row r="47" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
@@ -17126,17 +17126,17 @@
       </c>
     </row>
     <row r="90" spans="1:9" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A90" s="9" t="s">
+      <c r="A90" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="B90" s="9"/>
-      <c r="C90" s="9"/>
-      <c r="D90" s="9"/>
-      <c r="E90" s="9"/>
-      <c r="F90" s="9"/>
-      <c r="G90" s="9"/>
-      <c r="H90" s="9"/>
-      <c r="I90" s="9"/>
+      <c r="B90" s="14"/>
+      <c r="C90" s="14"/>
+      <c r="D90" s="14"/>
+      <c r="E90" s="14"/>
+      <c r="F90" s="14"/>
+      <c r="G90" s="14"/>
+      <c r="H90" s="14"/>
+      <c r="I90" s="14"/>
     </row>
     <row r="91" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
@@ -18248,17 +18248,17 @@
       </c>
     </row>
     <row r="134" spans="1:9" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A134" s="9" t="s">
+      <c r="A134" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="B134" s="9"/>
-      <c r="C134" s="9"/>
-      <c r="D134" s="9"/>
-      <c r="E134" s="9"/>
-      <c r="F134" s="9"/>
-      <c r="G134" s="9"/>
-      <c r="H134" s="9"/>
-      <c r="I134" s="9"/>
+      <c r="B134" s="14"/>
+      <c r="C134" s="14"/>
+      <c r="D134" s="14"/>
+      <c r="E134" s="14"/>
+      <c r="F134" s="14"/>
+      <c r="G134" s="14"/>
+      <c r="H134" s="14"/>
+      <c r="I134" s="14"/>
     </row>
     <row r="135" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" s="1" t="s">
@@ -18294,7 +18294,7 @@
         <v>1</v>
       </c>
       <c r="B136" s="17" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" s="3">
@@ -18321,13 +18321,13 @@
       <c r="B137" s="18"/>
       <c r="C137" s="2"/>
       <c r="D137" s="4" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E137" s="4" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F137" s="4" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G137" s="4" t="s">
         <v>10</v>
@@ -18344,7 +18344,7 @@
         <v>2</v>
       </c>
       <c r="B138" s="15" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C138" s="5"/>
       <c r="D138" s="6">
@@ -18371,13 +18371,13 @@
       <c r="B139" s="16"/>
       <c r="C139" s="5"/>
       <c r="D139" s="7" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E139" s="7" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F139" s="7" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G139" s="7" t="s">
         <v>10</v>
@@ -18394,7 +18394,7 @@
         <v>3</v>
       </c>
       <c r="B140" s="17" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" s="3">
@@ -18421,13 +18421,13 @@
       <c r="B141" s="18"/>
       <c r="C141" s="2"/>
       <c r="D141" s="4" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E141" s="4" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F141" s="4" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="G141" s="4" t="s">
         <v>10</v>
@@ -18444,10 +18444,10 @@
         <v>4</v>
       </c>
       <c r="B142" s="13" t="s">
+        <v>150</v>
+      </c>
+      <c r="C142" s="5" t="s">
         <v>151</v>
-      </c>
-      <c r="C142" s="5" t="s">
-        <v>152</v>
       </c>
       <c r="D142" s="6">
         <v>300</v>
@@ -18473,7 +18473,7 @@
       <c r="B143" s="13"/>
       <c r="C143" s="5"/>
       <c r="D143" s="7" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E143" s="7" t="s">
         <v>10</v>
@@ -18496,10 +18496,10 @@
         <v>5</v>
       </c>
       <c r="B144" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="C144" s="2" t="s">
         <v>154</v>
-      </c>
-      <c r="C144" s="2" t="s">
-        <v>155</v>
       </c>
       <c r="D144" s="3">
         <v>300</v>
@@ -18525,7 +18525,7 @@
       <c r="B145" s="11"/>
       <c r="C145" s="2"/>
       <c r="D145" s="4" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E145" s="4" t="s">
         <v>10</v>
@@ -18548,10 +18548,10 @@
         <v>6</v>
       </c>
       <c r="B146" s="13" t="s">
+        <v>156</v>
+      </c>
+      <c r="C146" s="5" t="s">
         <v>157</v>
-      </c>
-      <c r="C146" s="5" t="s">
-        <v>158</v>
       </c>
       <c r="D146" s="6">
         <v>300</v>
@@ -18577,7 +18577,7 @@
       <c r="B147" s="13"/>
       <c r="C147" s="5"/>
       <c r="D147" s="7" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E147" s="7" t="s">
         <v>10</v>
@@ -19352,17 +19352,17 @@
       </c>
     </row>
     <row r="178" spans="1:9" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A178" s="9" t="s">
+      <c r="A178" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="B178" s="9"/>
-      <c r="C178" s="9"/>
-      <c r="D178" s="9"/>
-      <c r="E178" s="9"/>
-      <c r="F178" s="9"/>
-      <c r="G178" s="9"/>
-      <c r="H178" s="9"/>
-      <c r="I178" s="9"/>
+      <c r="B178" s="14"/>
+      <c r="C178" s="14"/>
+      <c r="D178" s="14"/>
+      <c r="E178" s="14"/>
+      <c r="F178" s="14"/>
+      <c r="G178" s="14"/>
+      <c r="H178" s="14"/>
+      <c r="I178" s="14"/>
     </row>
     <row r="179" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A179" s="1" t="s">
@@ -20474,17 +20474,17 @@
       </c>
     </row>
     <row r="222" spans="1:9" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A222" s="9" t="s">
+      <c r="A222" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="B222" s="9"/>
-      <c r="C222" s="9"/>
-      <c r="D222" s="9"/>
-      <c r="E222" s="9"/>
-      <c r="F222" s="9"/>
-      <c r="G222" s="9"/>
-      <c r="H222" s="9"/>
-      <c r="I222" s="9"/>
+      <c r="B222" s="14"/>
+      <c r="C222" s="14"/>
+      <c r="D222" s="14"/>
+      <c r="E222" s="14"/>
+      <c r="F222" s="14"/>
+      <c r="G222" s="14"/>
+      <c r="H222" s="14"/>
+      <c r="I222" s="14"/>
     </row>
     <row r="223" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A223" s="1" t="s">
@@ -21596,17 +21596,17 @@
       </c>
     </row>
     <row r="266" spans="1:9" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A266" s="9" t="s">
+      <c r="A266" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="B266" s="9"/>
-      <c r="C266" s="9"/>
-      <c r="D266" s="9"/>
-      <c r="E266" s="9"/>
-      <c r="F266" s="9"/>
-      <c r="G266" s="9"/>
-      <c r="H266" s="9"/>
-      <c r="I266" s="9"/>
+      <c r="B266" s="14"/>
+      <c r="C266" s="14"/>
+      <c r="D266" s="14"/>
+      <c r="E266" s="14"/>
+      <c r="F266" s="14"/>
+      <c r="G266" s="14"/>
+      <c r="H266" s="14"/>
+      <c r="I266" s="14"/>
     </row>
     <row r="267" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A267" s="1" t="s">
@@ -22718,17 +22718,17 @@
       </c>
     </row>
     <row r="310" spans="1:9" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A310" s="9" t="s">
+      <c r="A310" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="B310" s="9"/>
-      <c r="C310" s="9"/>
-      <c r="D310" s="9"/>
-      <c r="E310" s="9"/>
-      <c r="F310" s="9"/>
-      <c r="G310" s="9"/>
-      <c r="H310" s="9"/>
-      <c r="I310" s="9"/>
+      <c r="B310" s="14"/>
+      <c r="C310" s="14"/>
+      <c r="D310" s="14"/>
+      <c r="E310" s="14"/>
+      <c r="F310" s="14"/>
+      <c r="G310" s="14"/>
+      <c r="H310" s="14"/>
+      <c r="I310" s="14"/>
     </row>
     <row r="311" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A311" s="1" t="s">
@@ -23840,17 +23840,17 @@
       </c>
     </row>
     <row r="354" spans="1:9" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A354" s="9" t="s">
+      <c r="A354" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="B354" s="9"/>
-      <c r="C354" s="9"/>
-      <c r="D354" s="9"/>
-      <c r="E354" s="9"/>
-      <c r="F354" s="9"/>
-      <c r="G354" s="9"/>
-      <c r="H354" s="9"/>
-      <c r="I354" s="9"/>
+      <c r="B354" s="14"/>
+      <c r="C354" s="14"/>
+      <c r="D354" s="14"/>
+      <c r="E354" s="14"/>
+      <c r="F354" s="14"/>
+      <c r="G354" s="14"/>
+      <c r="H354" s="14"/>
+      <c r="I354" s="14"/>
     </row>
     <row r="355" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A355" s="1" t="s">
@@ -24962,17 +24962,17 @@
       </c>
     </row>
     <row r="398" spans="1:9" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A398" s="9" t="s">
+      <c r="A398" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="B398" s="9"/>
-      <c r="C398" s="9"/>
-      <c r="D398" s="9"/>
-      <c r="E398" s="9"/>
-      <c r="F398" s="9"/>
-      <c r="G398" s="9"/>
-      <c r="H398" s="9"/>
-      <c r="I398" s="9"/>
+      <c r="B398" s="14"/>
+      <c r="C398" s="14"/>
+      <c r="D398" s="14"/>
+      <c r="E398" s="14"/>
+      <c r="F398" s="14"/>
+      <c r="G398" s="14"/>
+      <c r="H398" s="14"/>
+      <c r="I398" s="14"/>
     </row>
     <row r="399" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A399" s="1" t="s">
@@ -26084,17 +26084,17 @@
       </c>
     </row>
     <row r="442" spans="1:9" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A442" s="9" t="s">
+      <c r="A442" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="B442" s="9"/>
-      <c r="C442" s="9"/>
-      <c r="D442" s="9"/>
-      <c r="E442" s="9"/>
-      <c r="F442" s="9"/>
-      <c r="G442" s="9"/>
-      <c r="H442" s="9"/>
-      <c r="I442" s="9"/>
+      <c r="B442" s="14"/>
+      <c r="C442" s="14"/>
+      <c r="D442" s="14"/>
+      <c r="E442" s="14"/>
+      <c r="F442" s="14"/>
+      <c r="G442" s="14"/>
+      <c r="H442" s="14"/>
+      <c r="I442" s="14"/>
     </row>
     <row r="443" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A443" s="1" t="s">
@@ -27206,17 +27206,17 @@
       </c>
     </row>
     <row r="486" spans="1:9" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A486" s="9" t="s">
+      <c r="A486" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="B486" s="9"/>
-      <c r="C486" s="9"/>
-      <c r="D486" s="9"/>
-      <c r="E486" s="9"/>
-      <c r="F486" s="9"/>
-      <c r="G486" s="9"/>
-      <c r="H486" s="9"/>
-      <c r="I486" s="9"/>
+      <c r="B486" s="14"/>
+      <c r="C486" s="14"/>
+      <c r="D486" s="14"/>
+      <c r="E486" s="14"/>
+      <c r="F486" s="14"/>
+      <c r="G486" s="14"/>
+      <c r="H486" s="14"/>
+      <c r="I486" s="14"/>
     </row>
     <row r="487" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A487" s="1" t="s">
@@ -28329,6 +28329,484 @@
     </row>
   </sheetData>
   <mergeCells count="492">
+    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="A18:A19"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="A20:A21"/>
+    <mergeCell ref="B20:B21"/>
+    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="B22:B23"/>
+    <mergeCell ref="A24:A25"/>
+    <mergeCell ref="B24:B25"/>
+    <mergeCell ref="A26:A27"/>
+    <mergeCell ref="B26:B27"/>
+    <mergeCell ref="A28:A29"/>
+    <mergeCell ref="B28:B29"/>
+    <mergeCell ref="A30:A31"/>
+    <mergeCell ref="B30:B31"/>
+    <mergeCell ref="A32:A33"/>
+    <mergeCell ref="B32:B33"/>
+    <mergeCell ref="A34:A35"/>
+    <mergeCell ref="B34:B35"/>
+    <mergeCell ref="A36:A37"/>
+    <mergeCell ref="B36:B37"/>
+    <mergeCell ref="A38:A39"/>
+    <mergeCell ref="B38:B39"/>
+    <mergeCell ref="A40:A41"/>
+    <mergeCell ref="B40:B41"/>
+    <mergeCell ref="A42:A43"/>
+    <mergeCell ref="B42:B43"/>
+    <mergeCell ref="A46:I46"/>
+    <mergeCell ref="A48:A49"/>
+    <mergeCell ref="B48:B49"/>
+    <mergeCell ref="A50:A51"/>
+    <mergeCell ref="B50:B51"/>
+    <mergeCell ref="A52:A53"/>
+    <mergeCell ref="B52:B53"/>
+    <mergeCell ref="A54:A55"/>
+    <mergeCell ref="B54:B55"/>
+    <mergeCell ref="A56:A57"/>
+    <mergeCell ref="B56:B57"/>
+    <mergeCell ref="A58:A59"/>
+    <mergeCell ref="B58:B59"/>
+    <mergeCell ref="A60:A61"/>
+    <mergeCell ref="B60:B61"/>
+    <mergeCell ref="A62:A63"/>
+    <mergeCell ref="B62:B63"/>
+    <mergeCell ref="A64:A65"/>
+    <mergeCell ref="B64:B65"/>
+    <mergeCell ref="A66:A67"/>
+    <mergeCell ref="B66:B67"/>
+    <mergeCell ref="A68:A69"/>
+    <mergeCell ref="B68:B69"/>
+    <mergeCell ref="A70:A71"/>
+    <mergeCell ref="B70:B71"/>
+    <mergeCell ref="A72:A73"/>
+    <mergeCell ref="B72:B73"/>
+    <mergeCell ref="A74:A75"/>
+    <mergeCell ref="B74:B75"/>
+    <mergeCell ref="A76:A77"/>
+    <mergeCell ref="B76:B77"/>
+    <mergeCell ref="A78:A79"/>
+    <mergeCell ref="B78:B79"/>
+    <mergeCell ref="A80:A81"/>
+    <mergeCell ref="B80:B81"/>
+    <mergeCell ref="A82:A83"/>
+    <mergeCell ref="B82:B83"/>
+    <mergeCell ref="A84:A85"/>
+    <mergeCell ref="B84:B85"/>
+    <mergeCell ref="A86:A87"/>
+    <mergeCell ref="B86:B87"/>
+    <mergeCell ref="A90:I90"/>
+    <mergeCell ref="A92:A93"/>
+    <mergeCell ref="B92:B93"/>
+    <mergeCell ref="A94:A95"/>
+    <mergeCell ref="B94:B95"/>
+    <mergeCell ref="A96:A97"/>
+    <mergeCell ref="B96:B97"/>
+    <mergeCell ref="A98:A99"/>
+    <mergeCell ref="B98:B99"/>
+    <mergeCell ref="A100:A101"/>
+    <mergeCell ref="B100:B101"/>
+    <mergeCell ref="A102:A103"/>
+    <mergeCell ref="B102:B103"/>
+    <mergeCell ref="A104:A105"/>
+    <mergeCell ref="B104:B105"/>
+    <mergeCell ref="A106:A107"/>
+    <mergeCell ref="B106:B107"/>
+    <mergeCell ref="A108:A109"/>
+    <mergeCell ref="B108:B109"/>
+    <mergeCell ref="A110:A111"/>
+    <mergeCell ref="B110:B111"/>
+    <mergeCell ref="A112:A113"/>
+    <mergeCell ref="B112:B113"/>
+    <mergeCell ref="A114:A115"/>
+    <mergeCell ref="B114:B115"/>
+    <mergeCell ref="A116:A117"/>
+    <mergeCell ref="B116:B117"/>
+    <mergeCell ref="A118:A119"/>
+    <mergeCell ref="B118:B119"/>
+    <mergeCell ref="A120:A121"/>
+    <mergeCell ref="B120:B121"/>
+    <mergeCell ref="A122:A123"/>
+    <mergeCell ref="B122:B123"/>
+    <mergeCell ref="A124:A125"/>
+    <mergeCell ref="B124:B125"/>
+    <mergeCell ref="A126:A127"/>
+    <mergeCell ref="B126:B127"/>
+    <mergeCell ref="A128:A129"/>
+    <mergeCell ref="B128:B129"/>
+    <mergeCell ref="A130:A131"/>
+    <mergeCell ref="B130:B131"/>
+    <mergeCell ref="A134:I134"/>
+    <mergeCell ref="A136:A137"/>
+    <mergeCell ref="B136:B137"/>
+    <mergeCell ref="A138:A139"/>
+    <mergeCell ref="B138:B139"/>
+    <mergeCell ref="A140:A141"/>
+    <mergeCell ref="B140:B141"/>
+    <mergeCell ref="A142:A143"/>
+    <mergeCell ref="B142:B143"/>
+    <mergeCell ref="A144:A145"/>
+    <mergeCell ref="B144:B145"/>
+    <mergeCell ref="A146:A147"/>
+    <mergeCell ref="B146:B147"/>
+    <mergeCell ref="A148:A149"/>
+    <mergeCell ref="B148:B149"/>
+    <mergeCell ref="A150:A151"/>
+    <mergeCell ref="B150:B151"/>
+    <mergeCell ref="A152:A153"/>
+    <mergeCell ref="B152:B153"/>
+    <mergeCell ref="A154:A155"/>
+    <mergeCell ref="B154:B155"/>
+    <mergeCell ref="A156:A157"/>
+    <mergeCell ref="B156:B157"/>
+    <mergeCell ref="A158:A159"/>
+    <mergeCell ref="B158:B159"/>
+    <mergeCell ref="A160:A161"/>
+    <mergeCell ref="B160:B161"/>
+    <mergeCell ref="A162:A163"/>
+    <mergeCell ref="B162:B163"/>
+    <mergeCell ref="A164:A165"/>
+    <mergeCell ref="B164:B165"/>
+    <mergeCell ref="A166:A167"/>
+    <mergeCell ref="B166:B167"/>
+    <mergeCell ref="A168:A169"/>
+    <mergeCell ref="B168:B169"/>
+    <mergeCell ref="A170:A171"/>
+    <mergeCell ref="B170:B171"/>
+    <mergeCell ref="A172:A173"/>
+    <mergeCell ref="B172:B173"/>
+    <mergeCell ref="A174:A175"/>
+    <mergeCell ref="B174:B175"/>
+    <mergeCell ref="A178:I178"/>
+    <mergeCell ref="A180:A181"/>
+    <mergeCell ref="B180:B181"/>
+    <mergeCell ref="A182:A183"/>
+    <mergeCell ref="B182:B183"/>
+    <mergeCell ref="A184:A185"/>
+    <mergeCell ref="B184:B185"/>
+    <mergeCell ref="A186:A187"/>
+    <mergeCell ref="B186:B187"/>
+    <mergeCell ref="A188:A189"/>
+    <mergeCell ref="B188:B189"/>
+    <mergeCell ref="A190:A191"/>
+    <mergeCell ref="B190:B191"/>
+    <mergeCell ref="A192:A193"/>
+    <mergeCell ref="B192:B193"/>
+    <mergeCell ref="A194:A195"/>
+    <mergeCell ref="B194:B195"/>
+    <mergeCell ref="A196:A197"/>
+    <mergeCell ref="B196:B197"/>
+    <mergeCell ref="A198:A199"/>
+    <mergeCell ref="B198:B199"/>
+    <mergeCell ref="A200:A201"/>
+    <mergeCell ref="B200:B201"/>
+    <mergeCell ref="A202:A203"/>
+    <mergeCell ref="B202:B203"/>
+    <mergeCell ref="A204:A205"/>
+    <mergeCell ref="B204:B205"/>
+    <mergeCell ref="A206:A207"/>
+    <mergeCell ref="B206:B207"/>
+    <mergeCell ref="A208:A209"/>
+    <mergeCell ref="B208:B209"/>
+    <mergeCell ref="A210:A211"/>
+    <mergeCell ref="B210:B211"/>
+    <mergeCell ref="A212:A213"/>
+    <mergeCell ref="B212:B213"/>
+    <mergeCell ref="A214:A215"/>
+    <mergeCell ref="B214:B215"/>
+    <mergeCell ref="A216:A217"/>
+    <mergeCell ref="B216:B217"/>
+    <mergeCell ref="A218:A219"/>
+    <mergeCell ref="B218:B219"/>
+    <mergeCell ref="A222:I222"/>
+    <mergeCell ref="A224:A225"/>
+    <mergeCell ref="B224:B225"/>
+    <mergeCell ref="A226:A227"/>
+    <mergeCell ref="B226:B227"/>
+    <mergeCell ref="A228:A229"/>
+    <mergeCell ref="B228:B229"/>
+    <mergeCell ref="A230:A231"/>
+    <mergeCell ref="B230:B231"/>
+    <mergeCell ref="A232:A233"/>
+    <mergeCell ref="B232:B233"/>
+    <mergeCell ref="A234:A235"/>
+    <mergeCell ref="B234:B235"/>
+    <mergeCell ref="A236:A237"/>
+    <mergeCell ref="B236:B237"/>
+    <mergeCell ref="A238:A239"/>
+    <mergeCell ref="B238:B239"/>
+    <mergeCell ref="A240:A241"/>
+    <mergeCell ref="B240:B241"/>
+    <mergeCell ref="A242:A243"/>
+    <mergeCell ref="B242:B243"/>
+    <mergeCell ref="A244:A245"/>
+    <mergeCell ref="B244:B245"/>
+    <mergeCell ref="A246:A247"/>
+    <mergeCell ref="B246:B247"/>
+    <mergeCell ref="A248:A249"/>
+    <mergeCell ref="B248:B249"/>
+    <mergeCell ref="A250:A251"/>
+    <mergeCell ref="B250:B251"/>
+    <mergeCell ref="A252:A253"/>
+    <mergeCell ref="B252:B253"/>
+    <mergeCell ref="A254:A255"/>
+    <mergeCell ref="B254:B255"/>
+    <mergeCell ref="A256:A257"/>
+    <mergeCell ref="B256:B257"/>
+    <mergeCell ref="A258:A259"/>
+    <mergeCell ref="B258:B259"/>
+    <mergeCell ref="A260:A261"/>
+    <mergeCell ref="B260:B261"/>
+    <mergeCell ref="A262:A263"/>
+    <mergeCell ref="B262:B263"/>
+    <mergeCell ref="A266:I266"/>
+    <mergeCell ref="A268:A269"/>
+    <mergeCell ref="B268:B269"/>
+    <mergeCell ref="A270:A271"/>
+    <mergeCell ref="B270:B271"/>
+    <mergeCell ref="A272:A273"/>
+    <mergeCell ref="B272:B273"/>
+    <mergeCell ref="A274:A275"/>
+    <mergeCell ref="B274:B275"/>
+    <mergeCell ref="A276:A277"/>
+    <mergeCell ref="B276:B277"/>
+    <mergeCell ref="A278:A279"/>
+    <mergeCell ref="B278:B279"/>
+    <mergeCell ref="A280:A281"/>
+    <mergeCell ref="B280:B281"/>
+    <mergeCell ref="A282:A283"/>
+    <mergeCell ref="B282:B283"/>
+    <mergeCell ref="A284:A285"/>
+    <mergeCell ref="B284:B285"/>
+    <mergeCell ref="A286:A287"/>
+    <mergeCell ref="B286:B287"/>
+    <mergeCell ref="A288:A289"/>
+    <mergeCell ref="B288:B289"/>
+    <mergeCell ref="A290:A291"/>
+    <mergeCell ref="B290:B291"/>
+    <mergeCell ref="A292:A293"/>
+    <mergeCell ref="B292:B293"/>
+    <mergeCell ref="A294:A295"/>
+    <mergeCell ref="B294:B295"/>
+    <mergeCell ref="A296:A297"/>
+    <mergeCell ref="B296:B297"/>
+    <mergeCell ref="A298:A299"/>
+    <mergeCell ref="B298:B299"/>
+    <mergeCell ref="A300:A301"/>
+    <mergeCell ref="B300:B301"/>
+    <mergeCell ref="A302:A303"/>
+    <mergeCell ref="B302:B303"/>
+    <mergeCell ref="A304:A305"/>
+    <mergeCell ref="B304:B305"/>
+    <mergeCell ref="A306:A307"/>
+    <mergeCell ref="B306:B307"/>
+    <mergeCell ref="A310:I310"/>
+    <mergeCell ref="A312:A313"/>
+    <mergeCell ref="B312:B313"/>
+    <mergeCell ref="A314:A315"/>
+    <mergeCell ref="B314:B315"/>
+    <mergeCell ref="A316:A317"/>
+    <mergeCell ref="B316:B317"/>
+    <mergeCell ref="A318:A319"/>
+    <mergeCell ref="B318:B319"/>
+    <mergeCell ref="A320:A321"/>
+    <mergeCell ref="B320:B321"/>
+    <mergeCell ref="A322:A323"/>
+    <mergeCell ref="B322:B323"/>
+    <mergeCell ref="A324:A325"/>
+    <mergeCell ref="B324:B325"/>
+    <mergeCell ref="A326:A327"/>
+    <mergeCell ref="B326:B327"/>
+    <mergeCell ref="A328:A329"/>
+    <mergeCell ref="B328:B329"/>
+    <mergeCell ref="A330:A331"/>
+    <mergeCell ref="B330:B331"/>
+    <mergeCell ref="A332:A333"/>
+    <mergeCell ref="B332:B333"/>
+    <mergeCell ref="A334:A335"/>
+    <mergeCell ref="B334:B335"/>
+    <mergeCell ref="A336:A337"/>
+    <mergeCell ref="B336:B337"/>
+    <mergeCell ref="A338:A339"/>
+    <mergeCell ref="B338:B339"/>
+    <mergeCell ref="A340:A341"/>
+    <mergeCell ref="B340:B341"/>
+    <mergeCell ref="A342:A343"/>
+    <mergeCell ref="B342:B343"/>
+    <mergeCell ref="A344:A345"/>
+    <mergeCell ref="B344:B345"/>
+    <mergeCell ref="A346:A347"/>
+    <mergeCell ref="B346:B347"/>
+    <mergeCell ref="A348:A349"/>
+    <mergeCell ref="B348:B349"/>
+    <mergeCell ref="A350:A351"/>
+    <mergeCell ref="B350:B351"/>
+    <mergeCell ref="A354:I354"/>
+    <mergeCell ref="A356:A357"/>
+    <mergeCell ref="B356:B357"/>
+    <mergeCell ref="A358:A359"/>
+    <mergeCell ref="B358:B359"/>
+    <mergeCell ref="A360:A361"/>
+    <mergeCell ref="B360:B361"/>
+    <mergeCell ref="A362:A363"/>
+    <mergeCell ref="B362:B363"/>
+    <mergeCell ref="A364:A365"/>
+    <mergeCell ref="B364:B365"/>
+    <mergeCell ref="A366:A367"/>
+    <mergeCell ref="B366:B367"/>
+    <mergeCell ref="A368:A369"/>
+    <mergeCell ref="B368:B369"/>
+    <mergeCell ref="A370:A371"/>
+    <mergeCell ref="B370:B371"/>
+    <mergeCell ref="A372:A373"/>
+    <mergeCell ref="B372:B373"/>
+    <mergeCell ref="A374:A375"/>
+    <mergeCell ref="B374:B375"/>
+    <mergeCell ref="A376:A377"/>
+    <mergeCell ref="B376:B377"/>
+    <mergeCell ref="A378:A379"/>
+    <mergeCell ref="B378:B379"/>
+    <mergeCell ref="A380:A381"/>
+    <mergeCell ref="B380:B381"/>
+    <mergeCell ref="A382:A383"/>
+    <mergeCell ref="B382:B383"/>
+    <mergeCell ref="A384:A385"/>
+    <mergeCell ref="B384:B385"/>
+    <mergeCell ref="A386:A387"/>
+    <mergeCell ref="B386:B387"/>
+    <mergeCell ref="A388:A389"/>
+    <mergeCell ref="B388:B389"/>
+    <mergeCell ref="A390:A391"/>
+    <mergeCell ref="B390:B391"/>
+    <mergeCell ref="A392:A393"/>
+    <mergeCell ref="B392:B393"/>
+    <mergeCell ref="A394:A395"/>
+    <mergeCell ref="B394:B395"/>
+    <mergeCell ref="A398:I398"/>
+    <mergeCell ref="A400:A401"/>
+    <mergeCell ref="B400:B401"/>
+    <mergeCell ref="A402:A403"/>
+    <mergeCell ref="B402:B403"/>
+    <mergeCell ref="A404:A405"/>
+    <mergeCell ref="B404:B405"/>
+    <mergeCell ref="A406:A407"/>
+    <mergeCell ref="B406:B407"/>
+    <mergeCell ref="A408:A409"/>
+    <mergeCell ref="B408:B409"/>
+    <mergeCell ref="A410:A411"/>
+    <mergeCell ref="B410:B411"/>
+    <mergeCell ref="A412:A413"/>
+    <mergeCell ref="B412:B413"/>
+    <mergeCell ref="A414:A415"/>
+    <mergeCell ref="B414:B415"/>
+    <mergeCell ref="A416:A417"/>
+    <mergeCell ref="B416:B417"/>
+    <mergeCell ref="A418:A419"/>
+    <mergeCell ref="B418:B419"/>
+    <mergeCell ref="A420:A421"/>
+    <mergeCell ref="B420:B421"/>
+    <mergeCell ref="A422:A423"/>
+    <mergeCell ref="B422:B423"/>
+    <mergeCell ref="A424:A425"/>
+    <mergeCell ref="B424:B425"/>
+    <mergeCell ref="A426:A427"/>
+    <mergeCell ref="B426:B427"/>
+    <mergeCell ref="A428:A429"/>
+    <mergeCell ref="B428:B429"/>
+    <mergeCell ref="A430:A431"/>
+    <mergeCell ref="B430:B431"/>
+    <mergeCell ref="A432:A433"/>
+    <mergeCell ref="B432:B433"/>
+    <mergeCell ref="A434:A435"/>
+    <mergeCell ref="B434:B435"/>
+    <mergeCell ref="A436:A437"/>
+    <mergeCell ref="B436:B437"/>
+    <mergeCell ref="A438:A439"/>
+    <mergeCell ref="B438:B439"/>
+    <mergeCell ref="A442:I442"/>
+    <mergeCell ref="A444:A445"/>
+    <mergeCell ref="B444:B445"/>
+    <mergeCell ref="A446:A447"/>
+    <mergeCell ref="B446:B447"/>
+    <mergeCell ref="A448:A449"/>
+    <mergeCell ref="B448:B449"/>
+    <mergeCell ref="A450:A451"/>
+    <mergeCell ref="B450:B451"/>
+    <mergeCell ref="A452:A453"/>
+    <mergeCell ref="B452:B453"/>
+    <mergeCell ref="A454:A455"/>
+    <mergeCell ref="B454:B455"/>
+    <mergeCell ref="A456:A457"/>
+    <mergeCell ref="B456:B457"/>
+    <mergeCell ref="A458:A459"/>
+    <mergeCell ref="B458:B459"/>
+    <mergeCell ref="A460:A461"/>
+    <mergeCell ref="B460:B461"/>
+    <mergeCell ref="A462:A463"/>
+    <mergeCell ref="B462:B463"/>
+    <mergeCell ref="A464:A465"/>
+    <mergeCell ref="B464:B465"/>
+    <mergeCell ref="A466:A467"/>
+    <mergeCell ref="B466:B467"/>
+    <mergeCell ref="A468:A469"/>
+    <mergeCell ref="B468:B469"/>
+    <mergeCell ref="A470:A471"/>
+    <mergeCell ref="B470:B471"/>
+    <mergeCell ref="A472:A473"/>
+    <mergeCell ref="B472:B473"/>
+    <mergeCell ref="A474:A475"/>
+    <mergeCell ref="B474:B475"/>
+    <mergeCell ref="A476:A477"/>
+    <mergeCell ref="B476:B477"/>
+    <mergeCell ref="A478:A479"/>
+    <mergeCell ref="B478:B479"/>
+    <mergeCell ref="A480:A481"/>
+    <mergeCell ref="B480:B481"/>
+    <mergeCell ref="A482:A483"/>
+    <mergeCell ref="B482:B483"/>
+    <mergeCell ref="A486:I486"/>
+    <mergeCell ref="A488:A489"/>
+    <mergeCell ref="B488:B489"/>
+    <mergeCell ref="A490:A491"/>
+    <mergeCell ref="B490:B491"/>
+    <mergeCell ref="A492:A493"/>
+    <mergeCell ref="B492:B493"/>
+    <mergeCell ref="A494:A495"/>
+    <mergeCell ref="B494:B495"/>
+    <mergeCell ref="A496:A497"/>
+    <mergeCell ref="B496:B497"/>
+    <mergeCell ref="A498:A499"/>
+    <mergeCell ref="B498:B499"/>
+    <mergeCell ref="A500:A501"/>
+    <mergeCell ref="B500:B501"/>
+    <mergeCell ref="A502:A503"/>
+    <mergeCell ref="B502:B503"/>
+    <mergeCell ref="A504:A505"/>
+    <mergeCell ref="B504:B505"/>
+    <mergeCell ref="A506:A507"/>
+    <mergeCell ref="B506:B507"/>
+    <mergeCell ref="A508:A509"/>
+    <mergeCell ref="B508:B509"/>
+    <mergeCell ref="A510:A511"/>
+    <mergeCell ref="B510:B511"/>
+    <mergeCell ref="A512:A513"/>
+    <mergeCell ref="B512:B513"/>
     <mergeCell ref="A524:A525"/>
     <mergeCell ref="B524:B525"/>
     <mergeCell ref="A526:A527"/>
@@ -28343,484 +28821,6 @@
     <mergeCell ref="B520:B521"/>
     <mergeCell ref="A522:A523"/>
     <mergeCell ref="B522:B523"/>
-    <mergeCell ref="A504:A505"/>
-    <mergeCell ref="B504:B505"/>
-    <mergeCell ref="A506:A507"/>
-    <mergeCell ref="B506:B507"/>
-    <mergeCell ref="A508:A509"/>
-    <mergeCell ref="B508:B509"/>
-    <mergeCell ref="A510:A511"/>
-    <mergeCell ref="B510:B511"/>
-    <mergeCell ref="A512:A513"/>
-    <mergeCell ref="B512:B513"/>
-    <mergeCell ref="A494:A495"/>
-    <mergeCell ref="B494:B495"/>
-    <mergeCell ref="A496:A497"/>
-    <mergeCell ref="B496:B497"/>
-    <mergeCell ref="A498:A499"/>
-    <mergeCell ref="B498:B499"/>
-    <mergeCell ref="A500:A501"/>
-    <mergeCell ref="B500:B501"/>
-    <mergeCell ref="A502:A503"/>
-    <mergeCell ref="B502:B503"/>
-    <mergeCell ref="A482:A483"/>
-    <mergeCell ref="B482:B483"/>
-    <mergeCell ref="A486:I486"/>
-    <mergeCell ref="A488:A489"/>
-    <mergeCell ref="B488:B489"/>
-    <mergeCell ref="A490:A491"/>
-    <mergeCell ref="B490:B491"/>
-    <mergeCell ref="A492:A493"/>
-    <mergeCell ref="B492:B493"/>
-    <mergeCell ref="A472:A473"/>
-    <mergeCell ref="B472:B473"/>
-    <mergeCell ref="A474:A475"/>
-    <mergeCell ref="B474:B475"/>
-    <mergeCell ref="A476:A477"/>
-    <mergeCell ref="B476:B477"/>
-    <mergeCell ref="A478:A479"/>
-    <mergeCell ref="B478:B479"/>
-    <mergeCell ref="A480:A481"/>
-    <mergeCell ref="B480:B481"/>
-    <mergeCell ref="A462:A463"/>
-    <mergeCell ref="B462:B463"/>
-    <mergeCell ref="A464:A465"/>
-    <mergeCell ref="B464:B465"/>
-    <mergeCell ref="A466:A467"/>
-    <mergeCell ref="B466:B467"/>
-    <mergeCell ref="A468:A469"/>
-    <mergeCell ref="B468:B469"/>
-    <mergeCell ref="A470:A471"/>
-    <mergeCell ref="B470:B471"/>
-    <mergeCell ref="A452:A453"/>
-    <mergeCell ref="B452:B453"/>
-    <mergeCell ref="A454:A455"/>
-    <mergeCell ref="B454:B455"/>
-    <mergeCell ref="A456:A457"/>
-    <mergeCell ref="B456:B457"/>
-    <mergeCell ref="A458:A459"/>
-    <mergeCell ref="B458:B459"/>
-    <mergeCell ref="A460:A461"/>
-    <mergeCell ref="B460:B461"/>
-    <mergeCell ref="A442:I442"/>
-    <mergeCell ref="A444:A445"/>
-    <mergeCell ref="B444:B445"/>
-    <mergeCell ref="A446:A447"/>
-    <mergeCell ref="B446:B447"/>
-    <mergeCell ref="A448:A449"/>
-    <mergeCell ref="B448:B449"/>
-    <mergeCell ref="A450:A451"/>
-    <mergeCell ref="B450:B451"/>
-    <mergeCell ref="A430:A431"/>
-    <mergeCell ref="B430:B431"/>
-    <mergeCell ref="A432:A433"/>
-    <mergeCell ref="B432:B433"/>
-    <mergeCell ref="A434:A435"/>
-    <mergeCell ref="B434:B435"/>
-    <mergeCell ref="A436:A437"/>
-    <mergeCell ref="B436:B437"/>
-    <mergeCell ref="A438:A439"/>
-    <mergeCell ref="B438:B439"/>
-    <mergeCell ref="A420:A421"/>
-    <mergeCell ref="B420:B421"/>
-    <mergeCell ref="A422:A423"/>
-    <mergeCell ref="B422:B423"/>
-    <mergeCell ref="A424:A425"/>
-    <mergeCell ref="B424:B425"/>
-    <mergeCell ref="A426:A427"/>
-    <mergeCell ref="B426:B427"/>
-    <mergeCell ref="A428:A429"/>
-    <mergeCell ref="B428:B429"/>
-    <mergeCell ref="A410:A411"/>
-    <mergeCell ref="B410:B411"/>
-    <mergeCell ref="A412:A413"/>
-    <mergeCell ref="B412:B413"/>
-    <mergeCell ref="A414:A415"/>
-    <mergeCell ref="B414:B415"/>
-    <mergeCell ref="A416:A417"/>
-    <mergeCell ref="B416:B417"/>
-    <mergeCell ref="A418:A419"/>
-    <mergeCell ref="B418:B419"/>
-    <mergeCell ref="A400:A401"/>
-    <mergeCell ref="B400:B401"/>
-    <mergeCell ref="A402:A403"/>
-    <mergeCell ref="B402:B403"/>
-    <mergeCell ref="A404:A405"/>
-    <mergeCell ref="B404:B405"/>
-    <mergeCell ref="A406:A407"/>
-    <mergeCell ref="B406:B407"/>
-    <mergeCell ref="A408:A409"/>
-    <mergeCell ref="B408:B409"/>
-    <mergeCell ref="A388:A389"/>
-    <mergeCell ref="B388:B389"/>
-    <mergeCell ref="A390:A391"/>
-    <mergeCell ref="B390:B391"/>
-    <mergeCell ref="A392:A393"/>
-    <mergeCell ref="B392:B393"/>
-    <mergeCell ref="A394:A395"/>
-    <mergeCell ref="B394:B395"/>
-    <mergeCell ref="A398:I398"/>
-    <mergeCell ref="A378:A379"/>
-    <mergeCell ref="B378:B379"/>
-    <mergeCell ref="A380:A381"/>
-    <mergeCell ref="B380:B381"/>
-    <mergeCell ref="A382:A383"/>
-    <mergeCell ref="B382:B383"/>
-    <mergeCell ref="A384:A385"/>
-    <mergeCell ref="B384:B385"/>
-    <mergeCell ref="A386:A387"/>
-    <mergeCell ref="B386:B387"/>
-    <mergeCell ref="A368:A369"/>
-    <mergeCell ref="B368:B369"/>
-    <mergeCell ref="A370:A371"/>
-    <mergeCell ref="B370:B371"/>
-    <mergeCell ref="A372:A373"/>
-    <mergeCell ref="B372:B373"/>
-    <mergeCell ref="A374:A375"/>
-    <mergeCell ref="B374:B375"/>
-    <mergeCell ref="A376:A377"/>
-    <mergeCell ref="B376:B377"/>
-    <mergeCell ref="A358:A359"/>
-    <mergeCell ref="B358:B359"/>
-    <mergeCell ref="A360:A361"/>
-    <mergeCell ref="B360:B361"/>
-    <mergeCell ref="A362:A363"/>
-    <mergeCell ref="B362:B363"/>
-    <mergeCell ref="A364:A365"/>
-    <mergeCell ref="B364:B365"/>
-    <mergeCell ref="A366:A367"/>
-    <mergeCell ref="B366:B367"/>
-    <mergeCell ref="A346:A347"/>
-    <mergeCell ref="B346:B347"/>
-    <mergeCell ref="A348:A349"/>
-    <mergeCell ref="B348:B349"/>
-    <mergeCell ref="A350:A351"/>
-    <mergeCell ref="B350:B351"/>
-    <mergeCell ref="A354:I354"/>
-    <mergeCell ref="A356:A357"/>
-    <mergeCell ref="B356:B357"/>
-    <mergeCell ref="A336:A337"/>
-    <mergeCell ref="B336:B337"/>
-    <mergeCell ref="A338:A339"/>
-    <mergeCell ref="B338:B339"/>
-    <mergeCell ref="A340:A341"/>
-    <mergeCell ref="B340:B341"/>
-    <mergeCell ref="A342:A343"/>
-    <mergeCell ref="B342:B343"/>
-    <mergeCell ref="A344:A345"/>
-    <mergeCell ref="B344:B345"/>
-    <mergeCell ref="A326:A327"/>
-    <mergeCell ref="B326:B327"/>
-    <mergeCell ref="A328:A329"/>
-    <mergeCell ref="B328:B329"/>
-    <mergeCell ref="A330:A331"/>
-    <mergeCell ref="B330:B331"/>
-    <mergeCell ref="A332:A333"/>
-    <mergeCell ref="B332:B333"/>
-    <mergeCell ref="A334:A335"/>
-    <mergeCell ref="B334:B335"/>
-    <mergeCell ref="A316:A317"/>
-    <mergeCell ref="B316:B317"/>
-    <mergeCell ref="A318:A319"/>
-    <mergeCell ref="B318:B319"/>
-    <mergeCell ref="A320:A321"/>
-    <mergeCell ref="B320:B321"/>
-    <mergeCell ref="A322:A323"/>
-    <mergeCell ref="B322:B323"/>
-    <mergeCell ref="A324:A325"/>
-    <mergeCell ref="B324:B325"/>
-    <mergeCell ref="A304:A305"/>
-    <mergeCell ref="B304:B305"/>
-    <mergeCell ref="A306:A307"/>
-    <mergeCell ref="B306:B307"/>
-    <mergeCell ref="A310:I310"/>
-    <mergeCell ref="A312:A313"/>
-    <mergeCell ref="B312:B313"/>
-    <mergeCell ref="A314:A315"/>
-    <mergeCell ref="B314:B315"/>
-    <mergeCell ref="A294:A295"/>
-    <mergeCell ref="B294:B295"/>
-    <mergeCell ref="A296:A297"/>
-    <mergeCell ref="B296:B297"/>
-    <mergeCell ref="A298:A299"/>
-    <mergeCell ref="B298:B299"/>
-    <mergeCell ref="A300:A301"/>
-    <mergeCell ref="B300:B301"/>
-    <mergeCell ref="A302:A303"/>
-    <mergeCell ref="B302:B303"/>
-    <mergeCell ref="A284:A285"/>
-    <mergeCell ref="B284:B285"/>
-    <mergeCell ref="A286:A287"/>
-    <mergeCell ref="B286:B287"/>
-    <mergeCell ref="A288:A289"/>
-    <mergeCell ref="B288:B289"/>
-    <mergeCell ref="A290:A291"/>
-    <mergeCell ref="B290:B291"/>
-    <mergeCell ref="A292:A293"/>
-    <mergeCell ref="B292:B293"/>
-    <mergeCell ref="A274:A275"/>
-    <mergeCell ref="B274:B275"/>
-    <mergeCell ref="A276:A277"/>
-    <mergeCell ref="B276:B277"/>
-    <mergeCell ref="A278:A279"/>
-    <mergeCell ref="B278:B279"/>
-    <mergeCell ref="A280:A281"/>
-    <mergeCell ref="B280:B281"/>
-    <mergeCell ref="A282:A283"/>
-    <mergeCell ref="B282:B283"/>
-    <mergeCell ref="A262:A263"/>
-    <mergeCell ref="B262:B263"/>
-    <mergeCell ref="A266:I266"/>
-    <mergeCell ref="A268:A269"/>
-    <mergeCell ref="B268:B269"/>
-    <mergeCell ref="A270:A271"/>
-    <mergeCell ref="B270:B271"/>
-    <mergeCell ref="A272:A273"/>
-    <mergeCell ref="B272:B273"/>
-    <mergeCell ref="A252:A253"/>
-    <mergeCell ref="B252:B253"/>
-    <mergeCell ref="A254:A255"/>
-    <mergeCell ref="B254:B255"/>
-    <mergeCell ref="A256:A257"/>
-    <mergeCell ref="B256:B257"/>
-    <mergeCell ref="A258:A259"/>
-    <mergeCell ref="B258:B259"/>
-    <mergeCell ref="A260:A261"/>
-    <mergeCell ref="B260:B261"/>
-    <mergeCell ref="A242:A243"/>
-    <mergeCell ref="B242:B243"/>
-    <mergeCell ref="A244:A245"/>
-    <mergeCell ref="B244:B245"/>
-    <mergeCell ref="A246:A247"/>
-    <mergeCell ref="B246:B247"/>
-    <mergeCell ref="A248:A249"/>
-    <mergeCell ref="B248:B249"/>
-    <mergeCell ref="A250:A251"/>
-    <mergeCell ref="B250:B251"/>
-    <mergeCell ref="A232:A233"/>
-    <mergeCell ref="B232:B233"/>
-    <mergeCell ref="A234:A235"/>
-    <mergeCell ref="B234:B235"/>
-    <mergeCell ref="A236:A237"/>
-    <mergeCell ref="B236:B237"/>
-    <mergeCell ref="A238:A239"/>
-    <mergeCell ref="B238:B239"/>
-    <mergeCell ref="A240:A241"/>
-    <mergeCell ref="B240:B241"/>
-    <mergeCell ref="A222:I222"/>
-    <mergeCell ref="A224:A225"/>
-    <mergeCell ref="B224:B225"/>
-    <mergeCell ref="A226:A227"/>
-    <mergeCell ref="B226:B227"/>
-    <mergeCell ref="A228:A229"/>
-    <mergeCell ref="B228:B229"/>
-    <mergeCell ref="A230:A231"/>
-    <mergeCell ref="B230:B231"/>
-    <mergeCell ref="A210:A211"/>
-    <mergeCell ref="B210:B211"/>
-    <mergeCell ref="A212:A213"/>
-    <mergeCell ref="B212:B213"/>
-    <mergeCell ref="A214:A215"/>
-    <mergeCell ref="B214:B215"/>
-    <mergeCell ref="A216:A217"/>
-    <mergeCell ref="B216:B217"/>
-    <mergeCell ref="A218:A219"/>
-    <mergeCell ref="B218:B219"/>
-    <mergeCell ref="A200:A201"/>
-    <mergeCell ref="B200:B201"/>
-    <mergeCell ref="A202:A203"/>
-    <mergeCell ref="B202:B203"/>
-    <mergeCell ref="A204:A205"/>
-    <mergeCell ref="B204:B205"/>
-    <mergeCell ref="A206:A207"/>
-    <mergeCell ref="B206:B207"/>
-    <mergeCell ref="A208:A209"/>
-    <mergeCell ref="B208:B209"/>
-    <mergeCell ref="A190:A191"/>
-    <mergeCell ref="B190:B191"/>
-    <mergeCell ref="A192:A193"/>
-    <mergeCell ref="B192:B193"/>
-    <mergeCell ref="A194:A195"/>
-    <mergeCell ref="B194:B195"/>
-    <mergeCell ref="A196:A197"/>
-    <mergeCell ref="B196:B197"/>
-    <mergeCell ref="A198:A199"/>
-    <mergeCell ref="B198:B199"/>
-    <mergeCell ref="A180:A181"/>
-    <mergeCell ref="B180:B181"/>
-    <mergeCell ref="A182:A183"/>
-    <mergeCell ref="B182:B183"/>
-    <mergeCell ref="A184:A185"/>
-    <mergeCell ref="B184:B185"/>
-    <mergeCell ref="A186:A187"/>
-    <mergeCell ref="B186:B187"/>
-    <mergeCell ref="A188:A189"/>
-    <mergeCell ref="B188:B189"/>
-    <mergeCell ref="A168:A169"/>
-    <mergeCell ref="B168:B169"/>
-    <mergeCell ref="A170:A171"/>
-    <mergeCell ref="B170:B171"/>
-    <mergeCell ref="A172:A173"/>
-    <mergeCell ref="B172:B173"/>
-    <mergeCell ref="A174:A175"/>
-    <mergeCell ref="B174:B175"/>
-    <mergeCell ref="A178:I178"/>
-    <mergeCell ref="A158:A159"/>
-    <mergeCell ref="B158:B159"/>
-    <mergeCell ref="A160:A161"/>
-    <mergeCell ref="B160:B161"/>
-    <mergeCell ref="A162:A163"/>
-    <mergeCell ref="B162:B163"/>
-    <mergeCell ref="A164:A165"/>
-    <mergeCell ref="B164:B165"/>
-    <mergeCell ref="A166:A167"/>
-    <mergeCell ref="B166:B167"/>
-    <mergeCell ref="A148:A149"/>
-    <mergeCell ref="B148:B149"/>
-    <mergeCell ref="A150:A151"/>
-    <mergeCell ref="B150:B151"/>
-    <mergeCell ref="A152:A153"/>
-    <mergeCell ref="B152:B153"/>
-    <mergeCell ref="A154:A155"/>
-    <mergeCell ref="B154:B155"/>
-    <mergeCell ref="A156:A157"/>
-    <mergeCell ref="B156:B157"/>
-    <mergeCell ref="A138:A139"/>
-    <mergeCell ref="B138:B139"/>
-    <mergeCell ref="A140:A141"/>
-    <mergeCell ref="B140:B141"/>
-    <mergeCell ref="A142:A143"/>
-    <mergeCell ref="B142:B143"/>
-    <mergeCell ref="A144:A145"/>
-    <mergeCell ref="B144:B145"/>
-    <mergeCell ref="A146:A147"/>
-    <mergeCell ref="B146:B147"/>
-    <mergeCell ref="A126:A127"/>
-    <mergeCell ref="B126:B127"/>
-    <mergeCell ref="A128:A129"/>
-    <mergeCell ref="B128:B129"/>
-    <mergeCell ref="A130:A131"/>
-    <mergeCell ref="B130:B131"/>
-    <mergeCell ref="A134:I134"/>
-    <mergeCell ref="A136:A137"/>
-    <mergeCell ref="B136:B137"/>
-    <mergeCell ref="A116:A117"/>
-    <mergeCell ref="B116:B117"/>
-    <mergeCell ref="A118:A119"/>
-    <mergeCell ref="B118:B119"/>
-    <mergeCell ref="A120:A121"/>
-    <mergeCell ref="B120:B121"/>
-    <mergeCell ref="A122:A123"/>
-    <mergeCell ref="B122:B123"/>
-    <mergeCell ref="A124:A125"/>
-    <mergeCell ref="B124:B125"/>
-    <mergeCell ref="A106:A107"/>
-    <mergeCell ref="B106:B107"/>
-    <mergeCell ref="A108:A109"/>
-    <mergeCell ref="B108:B109"/>
-    <mergeCell ref="A110:A111"/>
-    <mergeCell ref="B110:B111"/>
-    <mergeCell ref="A112:A113"/>
-    <mergeCell ref="B112:B113"/>
-    <mergeCell ref="A114:A115"/>
-    <mergeCell ref="B114:B115"/>
-    <mergeCell ref="A96:A97"/>
-    <mergeCell ref="B96:B97"/>
-    <mergeCell ref="A98:A99"/>
-    <mergeCell ref="B98:B99"/>
-    <mergeCell ref="A100:A101"/>
-    <mergeCell ref="B100:B101"/>
-    <mergeCell ref="A102:A103"/>
-    <mergeCell ref="B102:B103"/>
-    <mergeCell ref="A104:A105"/>
-    <mergeCell ref="B104:B105"/>
-    <mergeCell ref="A84:A85"/>
-    <mergeCell ref="B84:B85"/>
-    <mergeCell ref="A86:A87"/>
-    <mergeCell ref="B86:B87"/>
-    <mergeCell ref="A90:I90"/>
-    <mergeCell ref="A92:A93"/>
-    <mergeCell ref="B92:B93"/>
-    <mergeCell ref="A94:A95"/>
-    <mergeCell ref="B94:B95"/>
-    <mergeCell ref="A74:A75"/>
-    <mergeCell ref="B74:B75"/>
-    <mergeCell ref="A76:A77"/>
-    <mergeCell ref="B76:B77"/>
-    <mergeCell ref="A78:A79"/>
-    <mergeCell ref="B78:B79"/>
-    <mergeCell ref="A80:A81"/>
-    <mergeCell ref="B80:B81"/>
-    <mergeCell ref="A82:A83"/>
-    <mergeCell ref="B82:B83"/>
-    <mergeCell ref="A64:A65"/>
-    <mergeCell ref="B64:B65"/>
-    <mergeCell ref="A66:A67"/>
-    <mergeCell ref="B66:B67"/>
-    <mergeCell ref="A68:A69"/>
-    <mergeCell ref="B68:B69"/>
-    <mergeCell ref="A70:A71"/>
-    <mergeCell ref="B70:B71"/>
-    <mergeCell ref="A72:A73"/>
-    <mergeCell ref="B72:B73"/>
-    <mergeCell ref="A54:A55"/>
-    <mergeCell ref="B54:B55"/>
-    <mergeCell ref="A56:A57"/>
-    <mergeCell ref="B56:B57"/>
-    <mergeCell ref="A58:A59"/>
-    <mergeCell ref="B58:B59"/>
-    <mergeCell ref="A60:A61"/>
-    <mergeCell ref="B60:B61"/>
-    <mergeCell ref="A62:A63"/>
-    <mergeCell ref="B62:B63"/>
-    <mergeCell ref="A42:A43"/>
-    <mergeCell ref="B42:B43"/>
-    <mergeCell ref="A46:I46"/>
-    <mergeCell ref="A48:A49"/>
-    <mergeCell ref="B48:B49"/>
-    <mergeCell ref="A50:A51"/>
-    <mergeCell ref="B50:B51"/>
-    <mergeCell ref="A52:A53"/>
-    <mergeCell ref="B52:B53"/>
-    <mergeCell ref="A32:A33"/>
-    <mergeCell ref="B32:B33"/>
-    <mergeCell ref="A34:A35"/>
-    <mergeCell ref="B34:B35"/>
-    <mergeCell ref="A36:A37"/>
-    <mergeCell ref="B36:B37"/>
-    <mergeCell ref="A38:A39"/>
-    <mergeCell ref="B38:B39"/>
-    <mergeCell ref="A40:A41"/>
-    <mergeCell ref="B40:B41"/>
-    <mergeCell ref="A22:A23"/>
-    <mergeCell ref="B22:B23"/>
-    <mergeCell ref="A24:A25"/>
-    <mergeCell ref="B24:B25"/>
-    <mergeCell ref="A26:A27"/>
-    <mergeCell ref="B26:B27"/>
-    <mergeCell ref="A28:A29"/>
-    <mergeCell ref="B28:B29"/>
-    <mergeCell ref="A30:A31"/>
-    <mergeCell ref="B30:B31"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="B14:B15"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="A18:A19"/>
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="A20:A21"/>
-    <mergeCell ref="B20:B21"/>
-    <mergeCell ref="A2:I2"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="B10:B11"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
@@ -28840,17 +28840,17 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:9" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="B2" s="9"/>
-      <c r="C2" s="9"/>
-      <c r="D2" s="9"/>
-      <c r="E2" s="9"/>
-      <c r="F2" s="9"/>
-      <c r="G2" s="9"/>
-      <c r="H2" s="9"/>
-      <c r="I2" s="9"/>
+      <c r="A2" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="B2" s="14"/>
+      <c r="C2" s="14"/>
+      <c r="D2" s="14"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="14"/>
+      <c r="G2" s="14"/>
+      <c r="H2" s="14"/>
+      <c r="I2" s="14"/>
     </row>
     <row r="3" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
@@ -29962,17 +29962,17 @@
       </c>
     </row>
     <row r="46" spans="1:9" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="B46" s="9"/>
-      <c r="C46" s="9"/>
-      <c r="D46" s="9"/>
-      <c r="E46" s="9"/>
-      <c r="F46" s="9"/>
-      <c r="G46" s="9"/>
-      <c r="H46" s="9"/>
-      <c r="I46" s="9"/>
+      <c r="A46" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="B46" s="14"/>
+      <c r="C46" s="14"/>
+      <c r="D46" s="14"/>
+      <c r="E46" s="14"/>
+      <c r="F46" s="14"/>
+      <c r="G46" s="14"/>
+      <c r="H46" s="14"/>
+      <c r="I46" s="14"/>
     </row>
     <row r="47" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
@@ -30008,10 +30008,10 @@
         <v>1</v>
       </c>
       <c r="B48" s="11" t="s">
+        <v>159</v>
+      </c>
+      <c r="C48" s="2" t="s">
         <v>160</v>
-      </c>
-      <c r="C48" s="2" t="s">
-        <v>161</v>
       </c>
       <c r="D48" s="3"/>
       <c r="E48" s="3"/>
@@ -30048,10 +30048,10 @@
         <v>2</v>
       </c>
       <c r="B50" s="13" t="s">
+        <v>161</v>
+      </c>
+      <c r="C50" s="5" t="s">
         <v>162</v>
-      </c>
-      <c r="C50" s="5" t="s">
-        <v>163</v>
       </c>
       <c r="D50" s="6"/>
       <c r="E50" s="6"/>
@@ -30088,10 +30088,10 @@
         <v>3</v>
       </c>
       <c r="B52" s="11" t="s">
+        <v>163</v>
+      </c>
+      <c r="C52" s="2" t="s">
         <v>164</v>
-      </c>
-      <c r="C52" s="2" t="s">
-        <v>165</v>
       </c>
       <c r="D52" s="3">
         <v>300</v>
@@ -30117,13 +30117,13 @@
       <c r="B53" s="11"/>
       <c r="C53" s="2"/>
       <c r="D53" s="4" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E53" s="4" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F53" s="4" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="G53" s="4" t="s">
         <v>10</v>
@@ -30140,10 +30140,10 @@
         <v>4</v>
       </c>
       <c r="B54" s="13" t="s">
+        <v>166</v>
+      </c>
+      <c r="C54" s="5" t="s">
         <v>167</v>
-      </c>
-      <c r="C54" s="5" t="s">
-        <v>168</v>
       </c>
       <c r="D54" s="6"/>
       <c r="E54" s="6"/>
@@ -30180,10 +30180,10 @@
         <v>5</v>
       </c>
       <c r="B56" s="11" t="s">
+        <v>168</v>
+      </c>
+      <c r="C56" s="2" t="s">
         <v>169</v>
-      </c>
-      <c r="C56" s="2" t="s">
-        <v>170</v>
       </c>
       <c r="D56" s="3">
         <v>300</v>
@@ -30207,13 +30207,13 @@
       <c r="B57" s="11"/>
       <c r="C57" s="2"/>
       <c r="D57" s="4" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="E57" s="4" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F57" s="4" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="G57" s="4" t="s">
         <v>10</v>
@@ -30230,10 +30230,10 @@
         <v>6</v>
       </c>
       <c r="B58" s="13" t="s">
+        <v>171</v>
+      </c>
+      <c r="C58" s="5" t="s">
         <v>172</v>
-      </c>
-      <c r="C58" s="5" t="s">
-        <v>173</v>
       </c>
       <c r="D58" s="6"/>
       <c r="E58" s="6"/>
@@ -30270,10 +30270,10 @@
         <v>7</v>
       </c>
       <c r="B60" s="11" t="s">
+        <v>173</v>
+      </c>
+      <c r="C60" s="2" t="s">
         <v>174</v>
-      </c>
-      <c r="C60" s="2" t="s">
-        <v>175</v>
       </c>
       <c r="D60" s="3"/>
       <c r="E60" s="3"/>
@@ -30310,10 +30310,10 @@
         <v>8</v>
       </c>
       <c r="B62" s="13" t="s">
+        <v>175</v>
+      </c>
+      <c r="C62" s="5" t="s">
         <v>176</v>
-      </c>
-      <c r="C62" s="5" t="s">
-        <v>177</v>
       </c>
       <c r="D62" s="6"/>
       <c r="E62" s="6"/>
@@ -30350,10 +30350,10 @@
         <v>9</v>
       </c>
       <c r="B64" s="11" t="s">
+        <v>177</v>
+      </c>
+      <c r="C64" s="2" t="s">
         <v>178</v>
-      </c>
-      <c r="C64" s="2" t="s">
-        <v>179</v>
       </c>
       <c r="D64" s="3"/>
       <c r="E64" s="3"/>
@@ -30390,10 +30390,10 @@
         <v>10</v>
       </c>
       <c r="B66" s="13" t="s">
+        <v>179</v>
+      </c>
+      <c r="C66" s="5" t="s">
         <v>180</v>
-      </c>
-      <c r="C66" s="5" t="s">
-        <v>181</v>
       </c>
       <c r="D66" s="6"/>
       <c r="E66" s="6"/>
@@ -30966,17 +30966,17 @@
       </c>
     </row>
     <row r="90" spans="1:9" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A90" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="B90" s="9"/>
-      <c r="C90" s="9"/>
-      <c r="D90" s="9"/>
-      <c r="E90" s="9"/>
-      <c r="F90" s="9"/>
-      <c r="G90" s="9"/>
-      <c r="H90" s="9"/>
-      <c r="I90" s="9"/>
+      <c r="A90" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="B90" s="14"/>
+      <c r="C90" s="14"/>
+      <c r="D90" s="14"/>
+      <c r="E90" s="14"/>
+      <c r="F90" s="14"/>
+      <c r="G90" s="14"/>
+      <c r="H90" s="14"/>
+      <c r="I90" s="14"/>
     </row>
     <row r="91" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
@@ -32088,17 +32088,17 @@
       </c>
     </row>
     <row r="134" spans="1:9" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A134" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="B134" s="9"/>
-      <c r="C134" s="9"/>
-      <c r="D134" s="9"/>
-      <c r="E134" s="9"/>
-      <c r="F134" s="9"/>
-      <c r="G134" s="9"/>
-      <c r="H134" s="9"/>
-      <c r="I134" s="9"/>
+      <c r="A134" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="B134" s="14"/>
+      <c r="C134" s="14"/>
+      <c r="D134" s="14"/>
+      <c r="E134" s="14"/>
+      <c r="F134" s="14"/>
+      <c r="G134" s="14"/>
+      <c r="H134" s="14"/>
+      <c r="I134" s="14"/>
     </row>
     <row r="135" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" s="1" t="s">
@@ -33210,17 +33210,17 @@
       </c>
     </row>
     <row r="178" spans="1:9" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A178" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="B178" s="9"/>
-      <c r="C178" s="9"/>
-      <c r="D178" s="9"/>
-      <c r="E178" s="9"/>
-      <c r="F178" s="9"/>
-      <c r="G178" s="9"/>
-      <c r="H178" s="9"/>
-      <c r="I178" s="9"/>
+      <c r="A178" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="B178" s="14"/>
+      <c r="C178" s="14"/>
+      <c r="D178" s="14"/>
+      <c r="E178" s="14"/>
+      <c r="F178" s="14"/>
+      <c r="G178" s="14"/>
+      <c r="H178" s="14"/>
+      <c r="I178" s="14"/>
     </row>
     <row r="179" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A179" s="1" t="s">
@@ -34332,17 +34332,17 @@
       </c>
     </row>
     <row r="222" spans="1:9" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A222" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="B222" s="9"/>
-      <c r="C222" s="9"/>
-      <c r="D222" s="9"/>
-      <c r="E222" s="9"/>
-      <c r="F222" s="9"/>
-      <c r="G222" s="9"/>
-      <c r="H222" s="9"/>
-      <c r="I222" s="9"/>
+      <c r="A222" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="B222" s="14"/>
+      <c r="C222" s="14"/>
+      <c r="D222" s="14"/>
+      <c r="E222" s="14"/>
+      <c r="F222" s="14"/>
+      <c r="G222" s="14"/>
+      <c r="H222" s="14"/>
+      <c r="I222" s="14"/>
     </row>
     <row r="223" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A223" s="1" t="s">
@@ -35454,17 +35454,17 @@
       </c>
     </row>
     <row r="266" spans="1:9" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A266" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="B266" s="9"/>
-      <c r="C266" s="9"/>
-      <c r="D266" s="9"/>
-      <c r="E266" s="9"/>
-      <c r="F266" s="9"/>
-      <c r="G266" s="9"/>
-      <c r="H266" s="9"/>
-      <c r="I266" s="9"/>
+      <c r="A266" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="B266" s="14"/>
+      <c r="C266" s="14"/>
+      <c r="D266" s="14"/>
+      <c r="E266" s="14"/>
+      <c r="F266" s="14"/>
+      <c r="G266" s="14"/>
+      <c r="H266" s="14"/>
+      <c r="I266" s="14"/>
     </row>
     <row r="267" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A267" s="1" t="s">
@@ -36576,17 +36576,17 @@
       </c>
     </row>
     <row r="310" spans="1:9" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A310" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="B310" s="9"/>
-      <c r="C310" s="9"/>
-      <c r="D310" s="9"/>
-      <c r="E310" s="9"/>
-      <c r="F310" s="9"/>
-      <c r="G310" s="9"/>
-      <c r="H310" s="9"/>
-      <c r="I310" s="9"/>
+      <c r="A310" s="14" t="s">
+        <v>40</v>
+      </c>
+      <c r="B310" s="14"/>
+      <c r="C310" s="14"/>
+      <c r="D310" s="14"/>
+      <c r="E310" s="14"/>
+      <c r="F310" s="14"/>
+      <c r="G310" s="14"/>
+      <c r="H310" s="14"/>
+      <c r="I310" s="14"/>
     </row>
     <row r="311" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A311" s="1" t="s">
@@ -37698,17 +37698,17 @@
       </c>
     </row>
     <row r="354" spans="1:9" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A354" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="B354" s="9"/>
-      <c r="C354" s="9"/>
-      <c r="D354" s="9"/>
-      <c r="E354" s="9"/>
-      <c r="F354" s="9"/>
-      <c r="G354" s="9"/>
-      <c r="H354" s="9"/>
-      <c r="I354" s="9"/>
+      <c r="A354" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="B354" s="14"/>
+      <c r="C354" s="14"/>
+      <c r="D354" s="14"/>
+      <c r="E354" s="14"/>
+      <c r="F354" s="14"/>
+      <c r="G354" s="14"/>
+      <c r="H354" s="14"/>
+      <c r="I354" s="14"/>
     </row>
     <row r="355" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A355" s="1" t="s">
@@ -38820,17 +38820,17 @@
       </c>
     </row>
     <row r="398" spans="1:9" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A398" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="B398" s="9"/>
-      <c r="C398" s="9"/>
-      <c r="D398" s="9"/>
-      <c r="E398" s="9"/>
-      <c r="F398" s="9"/>
-      <c r="G398" s="9"/>
-      <c r="H398" s="9"/>
-      <c r="I398" s="9"/>
+      <c r="A398" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="B398" s="14"/>
+      <c r="C398" s="14"/>
+      <c r="D398" s="14"/>
+      <c r="E398" s="14"/>
+      <c r="F398" s="14"/>
+      <c r="G398" s="14"/>
+      <c r="H398" s="14"/>
+      <c r="I398" s="14"/>
     </row>
     <row r="399" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A399" s="1" t="s">
@@ -39942,17 +39942,17 @@
       </c>
     </row>
     <row r="442" spans="1:9" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A442" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="B442" s="9"/>
-      <c r="C442" s="9"/>
-      <c r="D442" s="9"/>
-      <c r="E442" s="9"/>
-      <c r="F442" s="9"/>
-      <c r="G442" s="9"/>
-      <c r="H442" s="9"/>
-      <c r="I442" s="9"/>
+      <c r="A442" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="B442" s="14"/>
+      <c r="C442" s="14"/>
+      <c r="D442" s="14"/>
+      <c r="E442" s="14"/>
+      <c r="F442" s="14"/>
+      <c r="G442" s="14"/>
+      <c r="H442" s="14"/>
+      <c r="I442" s="14"/>
     </row>
     <row r="443" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A443" s="1" t="s">
@@ -41064,17 +41064,17 @@
       </c>
     </row>
     <row r="486" spans="1:9" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A486" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="B486" s="9"/>
-      <c r="C486" s="9"/>
-      <c r="D486" s="9"/>
-      <c r="E486" s="9"/>
-      <c r="F486" s="9"/>
-      <c r="G486" s="9"/>
-      <c r="H486" s="9"/>
-      <c r="I486" s="9"/>
+      <c r="A486" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="B486" s="14"/>
+      <c r="C486" s="14"/>
+      <c r="D486" s="14"/>
+      <c r="E486" s="14"/>
+      <c r="F486" s="14"/>
+      <c r="G486" s="14"/>
+      <c r="H486" s="14"/>
+      <c r="I486" s="14"/>
     </row>
     <row r="487" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A487" s="1" t="s">
@@ -42187,6 +42187,484 @@
     </row>
   </sheetData>
   <mergeCells count="492">
+    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="A18:A19"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="A20:A21"/>
+    <mergeCell ref="B20:B21"/>
+    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="B22:B23"/>
+    <mergeCell ref="A24:A25"/>
+    <mergeCell ref="B24:B25"/>
+    <mergeCell ref="A26:A27"/>
+    <mergeCell ref="B26:B27"/>
+    <mergeCell ref="A28:A29"/>
+    <mergeCell ref="B28:B29"/>
+    <mergeCell ref="A30:A31"/>
+    <mergeCell ref="B30:B31"/>
+    <mergeCell ref="A32:A33"/>
+    <mergeCell ref="B32:B33"/>
+    <mergeCell ref="A34:A35"/>
+    <mergeCell ref="B34:B35"/>
+    <mergeCell ref="A36:A37"/>
+    <mergeCell ref="B36:B37"/>
+    <mergeCell ref="A38:A39"/>
+    <mergeCell ref="B38:B39"/>
+    <mergeCell ref="A40:A41"/>
+    <mergeCell ref="B40:B41"/>
+    <mergeCell ref="A42:A43"/>
+    <mergeCell ref="B42:B43"/>
+    <mergeCell ref="A46:I46"/>
+    <mergeCell ref="A48:A49"/>
+    <mergeCell ref="B48:B49"/>
+    <mergeCell ref="A50:A51"/>
+    <mergeCell ref="B50:B51"/>
+    <mergeCell ref="A52:A53"/>
+    <mergeCell ref="B52:B53"/>
+    <mergeCell ref="A54:A55"/>
+    <mergeCell ref="B54:B55"/>
+    <mergeCell ref="A56:A57"/>
+    <mergeCell ref="B56:B57"/>
+    <mergeCell ref="A58:A59"/>
+    <mergeCell ref="B58:B59"/>
+    <mergeCell ref="A60:A61"/>
+    <mergeCell ref="B60:B61"/>
+    <mergeCell ref="A62:A63"/>
+    <mergeCell ref="B62:B63"/>
+    <mergeCell ref="A64:A65"/>
+    <mergeCell ref="B64:B65"/>
+    <mergeCell ref="A66:A67"/>
+    <mergeCell ref="B66:B67"/>
+    <mergeCell ref="A68:A69"/>
+    <mergeCell ref="B68:B69"/>
+    <mergeCell ref="A70:A71"/>
+    <mergeCell ref="B70:B71"/>
+    <mergeCell ref="A72:A73"/>
+    <mergeCell ref="B72:B73"/>
+    <mergeCell ref="A74:A75"/>
+    <mergeCell ref="B74:B75"/>
+    <mergeCell ref="A76:A77"/>
+    <mergeCell ref="B76:B77"/>
+    <mergeCell ref="A78:A79"/>
+    <mergeCell ref="B78:B79"/>
+    <mergeCell ref="A80:A81"/>
+    <mergeCell ref="B80:B81"/>
+    <mergeCell ref="A82:A83"/>
+    <mergeCell ref="B82:B83"/>
+    <mergeCell ref="A84:A85"/>
+    <mergeCell ref="B84:B85"/>
+    <mergeCell ref="A86:A87"/>
+    <mergeCell ref="B86:B87"/>
+    <mergeCell ref="A90:I90"/>
+    <mergeCell ref="A92:A93"/>
+    <mergeCell ref="B92:B93"/>
+    <mergeCell ref="A94:A95"/>
+    <mergeCell ref="B94:B95"/>
+    <mergeCell ref="A96:A97"/>
+    <mergeCell ref="B96:B97"/>
+    <mergeCell ref="A98:A99"/>
+    <mergeCell ref="B98:B99"/>
+    <mergeCell ref="A100:A101"/>
+    <mergeCell ref="B100:B101"/>
+    <mergeCell ref="A102:A103"/>
+    <mergeCell ref="B102:B103"/>
+    <mergeCell ref="A104:A105"/>
+    <mergeCell ref="B104:B105"/>
+    <mergeCell ref="A106:A107"/>
+    <mergeCell ref="B106:B107"/>
+    <mergeCell ref="A108:A109"/>
+    <mergeCell ref="B108:B109"/>
+    <mergeCell ref="A110:A111"/>
+    <mergeCell ref="B110:B111"/>
+    <mergeCell ref="A112:A113"/>
+    <mergeCell ref="B112:B113"/>
+    <mergeCell ref="A114:A115"/>
+    <mergeCell ref="B114:B115"/>
+    <mergeCell ref="A116:A117"/>
+    <mergeCell ref="B116:B117"/>
+    <mergeCell ref="A118:A119"/>
+    <mergeCell ref="B118:B119"/>
+    <mergeCell ref="A120:A121"/>
+    <mergeCell ref="B120:B121"/>
+    <mergeCell ref="A122:A123"/>
+    <mergeCell ref="B122:B123"/>
+    <mergeCell ref="A124:A125"/>
+    <mergeCell ref="B124:B125"/>
+    <mergeCell ref="A126:A127"/>
+    <mergeCell ref="B126:B127"/>
+    <mergeCell ref="A128:A129"/>
+    <mergeCell ref="B128:B129"/>
+    <mergeCell ref="A130:A131"/>
+    <mergeCell ref="B130:B131"/>
+    <mergeCell ref="A134:I134"/>
+    <mergeCell ref="A136:A137"/>
+    <mergeCell ref="B136:B137"/>
+    <mergeCell ref="A138:A139"/>
+    <mergeCell ref="B138:B139"/>
+    <mergeCell ref="A140:A141"/>
+    <mergeCell ref="B140:B141"/>
+    <mergeCell ref="A142:A143"/>
+    <mergeCell ref="B142:B143"/>
+    <mergeCell ref="A144:A145"/>
+    <mergeCell ref="B144:B145"/>
+    <mergeCell ref="A146:A147"/>
+    <mergeCell ref="B146:B147"/>
+    <mergeCell ref="A148:A149"/>
+    <mergeCell ref="B148:B149"/>
+    <mergeCell ref="A150:A151"/>
+    <mergeCell ref="B150:B151"/>
+    <mergeCell ref="A152:A153"/>
+    <mergeCell ref="B152:B153"/>
+    <mergeCell ref="A154:A155"/>
+    <mergeCell ref="B154:B155"/>
+    <mergeCell ref="A156:A157"/>
+    <mergeCell ref="B156:B157"/>
+    <mergeCell ref="A158:A159"/>
+    <mergeCell ref="B158:B159"/>
+    <mergeCell ref="A160:A161"/>
+    <mergeCell ref="B160:B161"/>
+    <mergeCell ref="A162:A163"/>
+    <mergeCell ref="B162:B163"/>
+    <mergeCell ref="A164:A165"/>
+    <mergeCell ref="B164:B165"/>
+    <mergeCell ref="A166:A167"/>
+    <mergeCell ref="B166:B167"/>
+    <mergeCell ref="A168:A169"/>
+    <mergeCell ref="B168:B169"/>
+    <mergeCell ref="A170:A171"/>
+    <mergeCell ref="B170:B171"/>
+    <mergeCell ref="A172:A173"/>
+    <mergeCell ref="B172:B173"/>
+    <mergeCell ref="A174:A175"/>
+    <mergeCell ref="B174:B175"/>
+    <mergeCell ref="A178:I178"/>
+    <mergeCell ref="A180:A181"/>
+    <mergeCell ref="B180:B181"/>
+    <mergeCell ref="A182:A183"/>
+    <mergeCell ref="B182:B183"/>
+    <mergeCell ref="A184:A185"/>
+    <mergeCell ref="B184:B185"/>
+    <mergeCell ref="A186:A187"/>
+    <mergeCell ref="B186:B187"/>
+    <mergeCell ref="A188:A189"/>
+    <mergeCell ref="B188:B189"/>
+    <mergeCell ref="A190:A191"/>
+    <mergeCell ref="B190:B191"/>
+    <mergeCell ref="A192:A193"/>
+    <mergeCell ref="B192:B193"/>
+    <mergeCell ref="A194:A195"/>
+    <mergeCell ref="B194:B195"/>
+    <mergeCell ref="A196:A197"/>
+    <mergeCell ref="B196:B197"/>
+    <mergeCell ref="A198:A199"/>
+    <mergeCell ref="B198:B199"/>
+    <mergeCell ref="A200:A201"/>
+    <mergeCell ref="B200:B201"/>
+    <mergeCell ref="A202:A203"/>
+    <mergeCell ref="B202:B203"/>
+    <mergeCell ref="A204:A205"/>
+    <mergeCell ref="B204:B205"/>
+    <mergeCell ref="A206:A207"/>
+    <mergeCell ref="B206:B207"/>
+    <mergeCell ref="A208:A209"/>
+    <mergeCell ref="B208:B209"/>
+    <mergeCell ref="A210:A211"/>
+    <mergeCell ref="B210:B211"/>
+    <mergeCell ref="A212:A213"/>
+    <mergeCell ref="B212:B213"/>
+    <mergeCell ref="A214:A215"/>
+    <mergeCell ref="B214:B215"/>
+    <mergeCell ref="A216:A217"/>
+    <mergeCell ref="B216:B217"/>
+    <mergeCell ref="A218:A219"/>
+    <mergeCell ref="B218:B219"/>
+    <mergeCell ref="A222:I222"/>
+    <mergeCell ref="A224:A225"/>
+    <mergeCell ref="B224:B225"/>
+    <mergeCell ref="A226:A227"/>
+    <mergeCell ref="B226:B227"/>
+    <mergeCell ref="A228:A229"/>
+    <mergeCell ref="B228:B229"/>
+    <mergeCell ref="A230:A231"/>
+    <mergeCell ref="B230:B231"/>
+    <mergeCell ref="A232:A233"/>
+    <mergeCell ref="B232:B233"/>
+    <mergeCell ref="A234:A235"/>
+    <mergeCell ref="B234:B235"/>
+    <mergeCell ref="A236:A237"/>
+    <mergeCell ref="B236:B237"/>
+    <mergeCell ref="A238:A239"/>
+    <mergeCell ref="B238:B239"/>
+    <mergeCell ref="A240:A241"/>
+    <mergeCell ref="B240:B241"/>
+    <mergeCell ref="A242:A243"/>
+    <mergeCell ref="B242:B243"/>
+    <mergeCell ref="A244:A245"/>
+    <mergeCell ref="B244:B245"/>
+    <mergeCell ref="A246:A247"/>
+    <mergeCell ref="B246:B247"/>
+    <mergeCell ref="A248:A249"/>
+    <mergeCell ref="B248:B249"/>
+    <mergeCell ref="A250:A251"/>
+    <mergeCell ref="B250:B251"/>
+    <mergeCell ref="A252:A253"/>
+    <mergeCell ref="B252:B253"/>
+    <mergeCell ref="A254:A255"/>
+    <mergeCell ref="B254:B255"/>
+    <mergeCell ref="A256:A257"/>
+    <mergeCell ref="B256:B257"/>
+    <mergeCell ref="A258:A259"/>
+    <mergeCell ref="B258:B259"/>
+    <mergeCell ref="A260:A261"/>
+    <mergeCell ref="B260:B261"/>
+    <mergeCell ref="A262:A263"/>
+    <mergeCell ref="B262:B263"/>
+    <mergeCell ref="A266:I266"/>
+    <mergeCell ref="A268:A269"/>
+    <mergeCell ref="B268:B269"/>
+    <mergeCell ref="A270:A271"/>
+    <mergeCell ref="B270:B271"/>
+    <mergeCell ref="A272:A273"/>
+    <mergeCell ref="B272:B273"/>
+    <mergeCell ref="A274:A275"/>
+    <mergeCell ref="B274:B275"/>
+    <mergeCell ref="A276:A277"/>
+    <mergeCell ref="B276:B277"/>
+    <mergeCell ref="A278:A279"/>
+    <mergeCell ref="B278:B279"/>
+    <mergeCell ref="A280:A281"/>
+    <mergeCell ref="B280:B281"/>
+    <mergeCell ref="A282:A283"/>
+    <mergeCell ref="B282:B283"/>
+    <mergeCell ref="A284:A285"/>
+    <mergeCell ref="B284:B285"/>
+    <mergeCell ref="A286:A287"/>
+    <mergeCell ref="B286:B287"/>
+    <mergeCell ref="A288:A289"/>
+    <mergeCell ref="B288:B289"/>
+    <mergeCell ref="A290:A291"/>
+    <mergeCell ref="B290:B291"/>
+    <mergeCell ref="A292:A293"/>
+    <mergeCell ref="B292:B293"/>
+    <mergeCell ref="A294:A295"/>
+    <mergeCell ref="B294:B295"/>
+    <mergeCell ref="A296:A297"/>
+    <mergeCell ref="B296:B297"/>
+    <mergeCell ref="A298:A299"/>
+    <mergeCell ref="B298:B299"/>
+    <mergeCell ref="A300:A301"/>
+    <mergeCell ref="B300:B301"/>
+    <mergeCell ref="A302:A303"/>
+    <mergeCell ref="B302:B303"/>
+    <mergeCell ref="A304:A305"/>
+    <mergeCell ref="B304:B305"/>
+    <mergeCell ref="A306:A307"/>
+    <mergeCell ref="B306:B307"/>
+    <mergeCell ref="A310:I310"/>
+    <mergeCell ref="A312:A313"/>
+    <mergeCell ref="B312:B313"/>
+    <mergeCell ref="A314:A315"/>
+    <mergeCell ref="B314:B315"/>
+    <mergeCell ref="A316:A317"/>
+    <mergeCell ref="B316:B317"/>
+    <mergeCell ref="A318:A319"/>
+    <mergeCell ref="B318:B319"/>
+    <mergeCell ref="A320:A321"/>
+    <mergeCell ref="B320:B321"/>
+    <mergeCell ref="A322:A323"/>
+    <mergeCell ref="B322:B323"/>
+    <mergeCell ref="A324:A325"/>
+    <mergeCell ref="B324:B325"/>
+    <mergeCell ref="A326:A327"/>
+    <mergeCell ref="B326:B327"/>
+    <mergeCell ref="A328:A329"/>
+    <mergeCell ref="B328:B329"/>
+    <mergeCell ref="A330:A331"/>
+    <mergeCell ref="B330:B331"/>
+    <mergeCell ref="A332:A333"/>
+    <mergeCell ref="B332:B333"/>
+    <mergeCell ref="A334:A335"/>
+    <mergeCell ref="B334:B335"/>
+    <mergeCell ref="A336:A337"/>
+    <mergeCell ref="B336:B337"/>
+    <mergeCell ref="A338:A339"/>
+    <mergeCell ref="B338:B339"/>
+    <mergeCell ref="A340:A341"/>
+    <mergeCell ref="B340:B341"/>
+    <mergeCell ref="A342:A343"/>
+    <mergeCell ref="B342:B343"/>
+    <mergeCell ref="A344:A345"/>
+    <mergeCell ref="B344:B345"/>
+    <mergeCell ref="A346:A347"/>
+    <mergeCell ref="B346:B347"/>
+    <mergeCell ref="A348:A349"/>
+    <mergeCell ref="B348:B349"/>
+    <mergeCell ref="A350:A351"/>
+    <mergeCell ref="B350:B351"/>
+    <mergeCell ref="A354:I354"/>
+    <mergeCell ref="A356:A357"/>
+    <mergeCell ref="B356:B357"/>
+    <mergeCell ref="A358:A359"/>
+    <mergeCell ref="B358:B359"/>
+    <mergeCell ref="A360:A361"/>
+    <mergeCell ref="B360:B361"/>
+    <mergeCell ref="A362:A363"/>
+    <mergeCell ref="B362:B363"/>
+    <mergeCell ref="A364:A365"/>
+    <mergeCell ref="B364:B365"/>
+    <mergeCell ref="A366:A367"/>
+    <mergeCell ref="B366:B367"/>
+    <mergeCell ref="A368:A369"/>
+    <mergeCell ref="B368:B369"/>
+    <mergeCell ref="A370:A371"/>
+    <mergeCell ref="B370:B371"/>
+    <mergeCell ref="A372:A373"/>
+    <mergeCell ref="B372:B373"/>
+    <mergeCell ref="A374:A375"/>
+    <mergeCell ref="B374:B375"/>
+    <mergeCell ref="A376:A377"/>
+    <mergeCell ref="B376:B377"/>
+    <mergeCell ref="A378:A379"/>
+    <mergeCell ref="B378:B379"/>
+    <mergeCell ref="A380:A381"/>
+    <mergeCell ref="B380:B381"/>
+    <mergeCell ref="A382:A383"/>
+    <mergeCell ref="B382:B383"/>
+    <mergeCell ref="A384:A385"/>
+    <mergeCell ref="B384:B385"/>
+    <mergeCell ref="A386:A387"/>
+    <mergeCell ref="B386:B387"/>
+    <mergeCell ref="A388:A389"/>
+    <mergeCell ref="B388:B389"/>
+    <mergeCell ref="A390:A391"/>
+    <mergeCell ref="B390:B391"/>
+    <mergeCell ref="A392:A393"/>
+    <mergeCell ref="B392:B393"/>
+    <mergeCell ref="A394:A395"/>
+    <mergeCell ref="B394:B395"/>
+    <mergeCell ref="A398:I398"/>
+    <mergeCell ref="A400:A401"/>
+    <mergeCell ref="B400:B401"/>
+    <mergeCell ref="A402:A403"/>
+    <mergeCell ref="B402:B403"/>
+    <mergeCell ref="A404:A405"/>
+    <mergeCell ref="B404:B405"/>
+    <mergeCell ref="A406:A407"/>
+    <mergeCell ref="B406:B407"/>
+    <mergeCell ref="A408:A409"/>
+    <mergeCell ref="B408:B409"/>
+    <mergeCell ref="A410:A411"/>
+    <mergeCell ref="B410:B411"/>
+    <mergeCell ref="A412:A413"/>
+    <mergeCell ref="B412:B413"/>
+    <mergeCell ref="A414:A415"/>
+    <mergeCell ref="B414:B415"/>
+    <mergeCell ref="A416:A417"/>
+    <mergeCell ref="B416:B417"/>
+    <mergeCell ref="A418:A419"/>
+    <mergeCell ref="B418:B419"/>
+    <mergeCell ref="A420:A421"/>
+    <mergeCell ref="B420:B421"/>
+    <mergeCell ref="A422:A423"/>
+    <mergeCell ref="B422:B423"/>
+    <mergeCell ref="A424:A425"/>
+    <mergeCell ref="B424:B425"/>
+    <mergeCell ref="A426:A427"/>
+    <mergeCell ref="B426:B427"/>
+    <mergeCell ref="A428:A429"/>
+    <mergeCell ref="B428:B429"/>
+    <mergeCell ref="A430:A431"/>
+    <mergeCell ref="B430:B431"/>
+    <mergeCell ref="A432:A433"/>
+    <mergeCell ref="B432:B433"/>
+    <mergeCell ref="A434:A435"/>
+    <mergeCell ref="B434:B435"/>
+    <mergeCell ref="A436:A437"/>
+    <mergeCell ref="B436:B437"/>
+    <mergeCell ref="A438:A439"/>
+    <mergeCell ref="B438:B439"/>
+    <mergeCell ref="A442:I442"/>
+    <mergeCell ref="A444:A445"/>
+    <mergeCell ref="B444:B445"/>
+    <mergeCell ref="A446:A447"/>
+    <mergeCell ref="B446:B447"/>
+    <mergeCell ref="A448:A449"/>
+    <mergeCell ref="B448:B449"/>
+    <mergeCell ref="A450:A451"/>
+    <mergeCell ref="B450:B451"/>
+    <mergeCell ref="A452:A453"/>
+    <mergeCell ref="B452:B453"/>
+    <mergeCell ref="A454:A455"/>
+    <mergeCell ref="B454:B455"/>
+    <mergeCell ref="A456:A457"/>
+    <mergeCell ref="B456:B457"/>
+    <mergeCell ref="A458:A459"/>
+    <mergeCell ref="B458:B459"/>
+    <mergeCell ref="A460:A461"/>
+    <mergeCell ref="B460:B461"/>
+    <mergeCell ref="A462:A463"/>
+    <mergeCell ref="B462:B463"/>
+    <mergeCell ref="A464:A465"/>
+    <mergeCell ref="B464:B465"/>
+    <mergeCell ref="A466:A467"/>
+    <mergeCell ref="B466:B467"/>
+    <mergeCell ref="A468:A469"/>
+    <mergeCell ref="B468:B469"/>
+    <mergeCell ref="A470:A471"/>
+    <mergeCell ref="B470:B471"/>
+    <mergeCell ref="A472:A473"/>
+    <mergeCell ref="B472:B473"/>
+    <mergeCell ref="A474:A475"/>
+    <mergeCell ref="B474:B475"/>
+    <mergeCell ref="A476:A477"/>
+    <mergeCell ref="B476:B477"/>
+    <mergeCell ref="A478:A479"/>
+    <mergeCell ref="B478:B479"/>
+    <mergeCell ref="A480:A481"/>
+    <mergeCell ref="B480:B481"/>
+    <mergeCell ref="A482:A483"/>
+    <mergeCell ref="B482:B483"/>
+    <mergeCell ref="A486:I486"/>
+    <mergeCell ref="A488:A489"/>
+    <mergeCell ref="B488:B489"/>
+    <mergeCell ref="A490:A491"/>
+    <mergeCell ref="B490:B491"/>
+    <mergeCell ref="A492:A493"/>
+    <mergeCell ref="B492:B493"/>
+    <mergeCell ref="A494:A495"/>
+    <mergeCell ref="B494:B495"/>
+    <mergeCell ref="A496:A497"/>
+    <mergeCell ref="B496:B497"/>
+    <mergeCell ref="A498:A499"/>
+    <mergeCell ref="B498:B499"/>
+    <mergeCell ref="A500:A501"/>
+    <mergeCell ref="B500:B501"/>
+    <mergeCell ref="A502:A503"/>
+    <mergeCell ref="B502:B503"/>
+    <mergeCell ref="A504:A505"/>
+    <mergeCell ref="B504:B505"/>
+    <mergeCell ref="A506:A507"/>
+    <mergeCell ref="B506:B507"/>
+    <mergeCell ref="A508:A509"/>
+    <mergeCell ref="B508:B509"/>
+    <mergeCell ref="A510:A511"/>
+    <mergeCell ref="B510:B511"/>
+    <mergeCell ref="A512:A513"/>
+    <mergeCell ref="B512:B513"/>
     <mergeCell ref="A524:A525"/>
     <mergeCell ref="B524:B525"/>
     <mergeCell ref="A526:A527"/>
@@ -42201,484 +42679,6 @@
     <mergeCell ref="B520:B521"/>
     <mergeCell ref="A522:A523"/>
     <mergeCell ref="B522:B523"/>
-    <mergeCell ref="A504:A505"/>
-    <mergeCell ref="B504:B505"/>
-    <mergeCell ref="A506:A507"/>
-    <mergeCell ref="B506:B507"/>
-    <mergeCell ref="A508:A509"/>
-    <mergeCell ref="B508:B509"/>
-    <mergeCell ref="A510:A511"/>
-    <mergeCell ref="B510:B511"/>
-    <mergeCell ref="A512:A513"/>
-    <mergeCell ref="B512:B513"/>
-    <mergeCell ref="A494:A495"/>
-    <mergeCell ref="B494:B495"/>
-    <mergeCell ref="A496:A497"/>
-    <mergeCell ref="B496:B497"/>
-    <mergeCell ref="A498:A499"/>
-    <mergeCell ref="B498:B499"/>
-    <mergeCell ref="A500:A501"/>
-    <mergeCell ref="B500:B501"/>
-    <mergeCell ref="A502:A503"/>
-    <mergeCell ref="B502:B503"/>
-    <mergeCell ref="A482:A483"/>
-    <mergeCell ref="B482:B483"/>
-    <mergeCell ref="A486:I486"/>
-    <mergeCell ref="A488:A489"/>
-    <mergeCell ref="B488:B489"/>
-    <mergeCell ref="A490:A491"/>
-    <mergeCell ref="B490:B491"/>
-    <mergeCell ref="A492:A493"/>
-    <mergeCell ref="B492:B493"/>
-    <mergeCell ref="A472:A473"/>
-    <mergeCell ref="B472:B473"/>
-    <mergeCell ref="A474:A475"/>
-    <mergeCell ref="B474:B475"/>
-    <mergeCell ref="A476:A477"/>
-    <mergeCell ref="B476:B477"/>
-    <mergeCell ref="A478:A479"/>
-    <mergeCell ref="B478:B479"/>
-    <mergeCell ref="A480:A481"/>
-    <mergeCell ref="B480:B481"/>
-    <mergeCell ref="A462:A463"/>
-    <mergeCell ref="B462:B463"/>
-    <mergeCell ref="A464:A465"/>
-    <mergeCell ref="B464:B465"/>
-    <mergeCell ref="A466:A467"/>
-    <mergeCell ref="B466:B467"/>
-    <mergeCell ref="A468:A469"/>
-    <mergeCell ref="B468:B469"/>
-    <mergeCell ref="A470:A471"/>
-    <mergeCell ref="B470:B471"/>
-    <mergeCell ref="A452:A453"/>
-    <mergeCell ref="B452:B453"/>
-    <mergeCell ref="A454:A455"/>
-    <mergeCell ref="B454:B455"/>
-    <mergeCell ref="A456:A457"/>
-    <mergeCell ref="B456:B457"/>
-    <mergeCell ref="A458:A459"/>
-    <mergeCell ref="B458:B459"/>
-    <mergeCell ref="A460:A461"/>
-    <mergeCell ref="B460:B461"/>
-    <mergeCell ref="A442:I442"/>
-    <mergeCell ref="A444:A445"/>
-    <mergeCell ref="B444:B445"/>
-    <mergeCell ref="A446:A447"/>
-    <mergeCell ref="B446:B447"/>
-    <mergeCell ref="A448:A449"/>
-    <mergeCell ref="B448:B449"/>
-    <mergeCell ref="A450:A451"/>
-    <mergeCell ref="B450:B451"/>
-    <mergeCell ref="A430:A431"/>
-    <mergeCell ref="B430:B431"/>
-    <mergeCell ref="A432:A433"/>
-    <mergeCell ref="B432:B433"/>
-    <mergeCell ref="A434:A435"/>
-    <mergeCell ref="B434:B435"/>
-    <mergeCell ref="A436:A437"/>
-    <mergeCell ref="B436:B437"/>
-    <mergeCell ref="A438:A439"/>
-    <mergeCell ref="B438:B439"/>
-    <mergeCell ref="A420:A421"/>
-    <mergeCell ref="B420:B421"/>
-    <mergeCell ref="A422:A423"/>
-    <mergeCell ref="B422:B423"/>
-    <mergeCell ref="A424:A425"/>
-    <mergeCell ref="B424:B425"/>
-    <mergeCell ref="A426:A427"/>
-    <mergeCell ref="B426:B427"/>
-    <mergeCell ref="A428:A429"/>
-    <mergeCell ref="B428:B429"/>
-    <mergeCell ref="A410:A411"/>
-    <mergeCell ref="B410:B411"/>
-    <mergeCell ref="A412:A413"/>
-    <mergeCell ref="B412:B413"/>
-    <mergeCell ref="A414:A415"/>
-    <mergeCell ref="B414:B415"/>
-    <mergeCell ref="A416:A417"/>
-    <mergeCell ref="B416:B417"/>
-    <mergeCell ref="A418:A419"/>
-    <mergeCell ref="B418:B419"/>
-    <mergeCell ref="A400:A401"/>
-    <mergeCell ref="B400:B401"/>
-    <mergeCell ref="A402:A403"/>
-    <mergeCell ref="B402:B403"/>
-    <mergeCell ref="A404:A405"/>
-    <mergeCell ref="B404:B405"/>
-    <mergeCell ref="A406:A407"/>
-    <mergeCell ref="B406:B407"/>
-    <mergeCell ref="A408:A409"/>
-    <mergeCell ref="B408:B409"/>
-    <mergeCell ref="A388:A389"/>
-    <mergeCell ref="B388:B389"/>
-    <mergeCell ref="A390:A391"/>
-    <mergeCell ref="B390:B391"/>
-    <mergeCell ref="A392:A393"/>
-    <mergeCell ref="B392:B393"/>
-    <mergeCell ref="A394:A395"/>
-    <mergeCell ref="B394:B395"/>
-    <mergeCell ref="A398:I398"/>
-    <mergeCell ref="A378:A379"/>
-    <mergeCell ref="B378:B379"/>
-    <mergeCell ref="A380:A381"/>
-    <mergeCell ref="B380:B381"/>
-    <mergeCell ref="A382:A383"/>
-    <mergeCell ref="B382:B383"/>
-    <mergeCell ref="A384:A385"/>
-    <mergeCell ref="B384:B385"/>
-    <mergeCell ref="A386:A387"/>
-    <mergeCell ref="B386:B387"/>
-    <mergeCell ref="A368:A369"/>
-    <mergeCell ref="B368:B369"/>
-    <mergeCell ref="A370:A371"/>
-    <mergeCell ref="B370:B371"/>
-    <mergeCell ref="A372:A373"/>
-    <mergeCell ref="B372:B373"/>
-    <mergeCell ref="A374:A375"/>
-    <mergeCell ref="B374:B375"/>
-    <mergeCell ref="A376:A377"/>
-    <mergeCell ref="B376:B377"/>
-    <mergeCell ref="A358:A359"/>
-    <mergeCell ref="B358:B359"/>
-    <mergeCell ref="A360:A361"/>
-    <mergeCell ref="B360:B361"/>
-    <mergeCell ref="A362:A363"/>
-    <mergeCell ref="B362:B363"/>
-    <mergeCell ref="A364:A365"/>
-    <mergeCell ref="B364:B365"/>
-    <mergeCell ref="A366:A367"/>
-    <mergeCell ref="B366:B367"/>
-    <mergeCell ref="A346:A347"/>
-    <mergeCell ref="B346:B347"/>
-    <mergeCell ref="A348:A349"/>
-    <mergeCell ref="B348:B349"/>
-    <mergeCell ref="A350:A351"/>
-    <mergeCell ref="B350:B351"/>
-    <mergeCell ref="A354:I354"/>
-    <mergeCell ref="A356:A357"/>
-    <mergeCell ref="B356:B357"/>
-    <mergeCell ref="A336:A337"/>
-    <mergeCell ref="B336:B337"/>
-    <mergeCell ref="A338:A339"/>
-    <mergeCell ref="B338:B339"/>
-    <mergeCell ref="A340:A341"/>
-    <mergeCell ref="B340:B341"/>
-    <mergeCell ref="A342:A343"/>
-    <mergeCell ref="B342:B343"/>
-    <mergeCell ref="A344:A345"/>
-    <mergeCell ref="B344:B345"/>
-    <mergeCell ref="A326:A327"/>
-    <mergeCell ref="B326:B327"/>
-    <mergeCell ref="A328:A329"/>
-    <mergeCell ref="B328:B329"/>
-    <mergeCell ref="A330:A331"/>
-    <mergeCell ref="B330:B331"/>
-    <mergeCell ref="A332:A333"/>
-    <mergeCell ref="B332:B333"/>
-    <mergeCell ref="A334:A335"/>
-    <mergeCell ref="B334:B335"/>
-    <mergeCell ref="A316:A317"/>
-    <mergeCell ref="B316:B317"/>
-    <mergeCell ref="A318:A319"/>
-    <mergeCell ref="B318:B319"/>
-    <mergeCell ref="A320:A321"/>
-    <mergeCell ref="B320:B321"/>
-    <mergeCell ref="A322:A323"/>
-    <mergeCell ref="B322:B323"/>
-    <mergeCell ref="A324:A325"/>
-    <mergeCell ref="B324:B325"/>
-    <mergeCell ref="A304:A305"/>
-    <mergeCell ref="B304:B305"/>
-    <mergeCell ref="A306:A307"/>
-    <mergeCell ref="B306:B307"/>
-    <mergeCell ref="A310:I310"/>
-    <mergeCell ref="A312:A313"/>
-    <mergeCell ref="B312:B313"/>
-    <mergeCell ref="A314:A315"/>
-    <mergeCell ref="B314:B315"/>
-    <mergeCell ref="A294:A295"/>
-    <mergeCell ref="B294:B295"/>
-    <mergeCell ref="A296:A297"/>
-    <mergeCell ref="B296:B297"/>
-    <mergeCell ref="A298:A299"/>
-    <mergeCell ref="B298:B299"/>
-    <mergeCell ref="A300:A301"/>
-    <mergeCell ref="B300:B301"/>
-    <mergeCell ref="A302:A303"/>
-    <mergeCell ref="B302:B303"/>
-    <mergeCell ref="A284:A285"/>
-    <mergeCell ref="B284:B285"/>
-    <mergeCell ref="A286:A287"/>
-    <mergeCell ref="B286:B287"/>
-    <mergeCell ref="A288:A289"/>
-    <mergeCell ref="B288:B289"/>
-    <mergeCell ref="A290:A291"/>
-    <mergeCell ref="B290:B291"/>
-    <mergeCell ref="A292:A293"/>
-    <mergeCell ref="B292:B293"/>
-    <mergeCell ref="A274:A275"/>
-    <mergeCell ref="B274:B275"/>
-    <mergeCell ref="A276:A277"/>
-    <mergeCell ref="B276:B277"/>
-    <mergeCell ref="A278:A279"/>
-    <mergeCell ref="B278:B279"/>
-    <mergeCell ref="A280:A281"/>
-    <mergeCell ref="B280:B281"/>
-    <mergeCell ref="A282:A283"/>
-    <mergeCell ref="B282:B283"/>
-    <mergeCell ref="A262:A263"/>
-    <mergeCell ref="B262:B263"/>
-    <mergeCell ref="A266:I266"/>
-    <mergeCell ref="A268:A269"/>
-    <mergeCell ref="B268:B269"/>
-    <mergeCell ref="A270:A271"/>
-    <mergeCell ref="B270:B271"/>
-    <mergeCell ref="A272:A273"/>
-    <mergeCell ref="B272:B273"/>
-    <mergeCell ref="A252:A253"/>
-    <mergeCell ref="B252:B253"/>
-    <mergeCell ref="A254:A255"/>
-    <mergeCell ref="B254:B255"/>
-    <mergeCell ref="A256:A257"/>
-    <mergeCell ref="B256:B257"/>
-    <mergeCell ref="A258:A259"/>
-    <mergeCell ref="B258:B259"/>
-    <mergeCell ref="A260:A261"/>
-    <mergeCell ref="B260:B261"/>
-    <mergeCell ref="A242:A243"/>
-    <mergeCell ref="B242:B243"/>
-    <mergeCell ref="A244:A245"/>
-    <mergeCell ref="B244:B245"/>
-    <mergeCell ref="A246:A247"/>
-    <mergeCell ref="B246:B247"/>
-    <mergeCell ref="A248:A249"/>
-    <mergeCell ref="B248:B249"/>
-    <mergeCell ref="A250:A251"/>
-    <mergeCell ref="B250:B251"/>
-    <mergeCell ref="A232:A233"/>
-    <mergeCell ref="B232:B233"/>
-    <mergeCell ref="A234:A235"/>
-    <mergeCell ref="B234:B235"/>
-    <mergeCell ref="A236:A237"/>
-    <mergeCell ref="B236:B237"/>
-    <mergeCell ref="A238:A239"/>
-    <mergeCell ref="B238:B239"/>
-    <mergeCell ref="A240:A241"/>
-    <mergeCell ref="B240:B241"/>
-    <mergeCell ref="A222:I222"/>
-    <mergeCell ref="A224:A225"/>
-    <mergeCell ref="B224:B225"/>
-    <mergeCell ref="A226:A227"/>
-    <mergeCell ref="B226:B227"/>
-    <mergeCell ref="A228:A229"/>
-    <mergeCell ref="B228:B229"/>
-    <mergeCell ref="A230:A231"/>
-    <mergeCell ref="B230:B231"/>
-    <mergeCell ref="A210:A211"/>
-    <mergeCell ref="B210:B211"/>
-    <mergeCell ref="A212:A213"/>
-    <mergeCell ref="B212:B213"/>
-    <mergeCell ref="A214:A215"/>
-    <mergeCell ref="B214:B215"/>
-    <mergeCell ref="A216:A217"/>
-    <mergeCell ref="B216:B217"/>
-    <mergeCell ref="A218:A219"/>
-    <mergeCell ref="B218:B219"/>
-    <mergeCell ref="A200:A201"/>
-    <mergeCell ref="B200:B201"/>
-    <mergeCell ref="A202:A203"/>
-    <mergeCell ref="B202:B203"/>
-    <mergeCell ref="A204:A205"/>
-    <mergeCell ref="B204:B205"/>
-    <mergeCell ref="A206:A207"/>
-    <mergeCell ref="B206:B207"/>
-    <mergeCell ref="A208:A209"/>
-    <mergeCell ref="B208:B209"/>
-    <mergeCell ref="A190:A191"/>
-    <mergeCell ref="B190:B191"/>
-    <mergeCell ref="A192:A193"/>
-    <mergeCell ref="B192:B193"/>
-    <mergeCell ref="A194:A195"/>
-    <mergeCell ref="B194:B195"/>
-    <mergeCell ref="A196:A197"/>
-    <mergeCell ref="B196:B197"/>
-    <mergeCell ref="A198:A199"/>
-    <mergeCell ref="B198:B199"/>
-    <mergeCell ref="A180:A181"/>
-    <mergeCell ref="B180:B181"/>
-    <mergeCell ref="A182:A183"/>
-    <mergeCell ref="B182:B183"/>
-    <mergeCell ref="A184:A185"/>
-    <mergeCell ref="B184:B185"/>
-    <mergeCell ref="A186:A187"/>
-    <mergeCell ref="B186:B187"/>
-    <mergeCell ref="A188:A189"/>
-    <mergeCell ref="B188:B189"/>
-    <mergeCell ref="A168:A169"/>
-    <mergeCell ref="B168:B169"/>
-    <mergeCell ref="A170:A171"/>
-    <mergeCell ref="B170:B171"/>
-    <mergeCell ref="A172:A173"/>
-    <mergeCell ref="B172:B173"/>
-    <mergeCell ref="A174:A175"/>
-    <mergeCell ref="B174:B175"/>
-    <mergeCell ref="A178:I178"/>
-    <mergeCell ref="A158:A159"/>
-    <mergeCell ref="B158:B159"/>
-    <mergeCell ref="A160:A161"/>
-    <mergeCell ref="B160:B161"/>
-    <mergeCell ref="A162:A163"/>
-    <mergeCell ref="B162:B163"/>
-    <mergeCell ref="A164:A165"/>
-    <mergeCell ref="B164:B165"/>
-    <mergeCell ref="A166:A167"/>
-    <mergeCell ref="B166:B167"/>
-    <mergeCell ref="A148:A149"/>
-    <mergeCell ref="B148:B149"/>
-    <mergeCell ref="A150:A151"/>
-    <mergeCell ref="B150:B151"/>
-    <mergeCell ref="A152:A153"/>
-    <mergeCell ref="B152:B153"/>
-    <mergeCell ref="A154:A155"/>
-    <mergeCell ref="B154:B155"/>
-    <mergeCell ref="A156:A157"/>
-    <mergeCell ref="B156:B157"/>
-    <mergeCell ref="A138:A139"/>
-    <mergeCell ref="B138:B139"/>
-    <mergeCell ref="A140:A141"/>
-    <mergeCell ref="B140:B141"/>
-    <mergeCell ref="A142:A143"/>
-    <mergeCell ref="B142:B143"/>
-    <mergeCell ref="A144:A145"/>
-    <mergeCell ref="B144:B145"/>
-    <mergeCell ref="A146:A147"/>
-    <mergeCell ref="B146:B147"/>
-    <mergeCell ref="A126:A127"/>
-    <mergeCell ref="B126:B127"/>
-    <mergeCell ref="A128:A129"/>
-    <mergeCell ref="B128:B129"/>
-    <mergeCell ref="A130:A131"/>
-    <mergeCell ref="B130:B131"/>
-    <mergeCell ref="A134:I134"/>
-    <mergeCell ref="A136:A137"/>
-    <mergeCell ref="B136:B137"/>
-    <mergeCell ref="A116:A117"/>
-    <mergeCell ref="B116:B117"/>
-    <mergeCell ref="A118:A119"/>
-    <mergeCell ref="B118:B119"/>
-    <mergeCell ref="A120:A121"/>
-    <mergeCell ref="B120:B121"/>
-    <mergeCell ref="A122:A123"/>
-    <mergeCell ref="B122:B123"/>
-    <mergeCell ref="A124:A125"/>
-    <mergeCell ref="B124:B125"/>
-    <mergeCell ref="A106:A107"/>
-    <mergeCell ref="B106:B107"/>
-    <mergeCell ref="A108:A109"/>
-    <mergeCell ref="B108:B109"/>
-    <mergeCell ref="A110:A111"/>
-    <mergeCell ref="B110:B111"/>
-    <mergeCell ref="A112:A113"/>
-    <mergeCell ref="B112:B113"/>
-    <mergeCell ref="A114:A115"/>
-    <mergeCell ref="B114:B115"/>
-    <mergeCell ref="A96:A97"/>
-    <mergeCell ref="B96:B97"/>
-    <mergeCell ref="A98:A99"/>
-    <mergeCell ref="B98:B99"/>
-    <mergeCell ref="A100:A101"/>
-    <mergeCell ref="B100:B101"/>
-    <mergeCell ref="A102:A103"/>
-    <mergeCell ref="B102:B103"/>
-    <mergeCell ref="A104:A105"/>
-    <mergeCell ref="B104:B105"/>
-    <mergeCell ref="A84:A85"/>
-    <mergeCell ref="B84:B85"/>
-    <mergeCell ref="A86:A87"/>
-    <mergeCell ref="B86:B87"/>
-    <mergeCell ref="A90:I90"/>
-    <mergeCell ref="A92:A93"/>
-    <mergeCell ref="B92:B93"/>
-    <mergeCell ref="A94:A95"/>
-    <mergeCell ref="B94:B95"/>
-    <mergeCell ref="A74:A75"/>
-    <mergeCell ref="B74:B75"/>
-    <mergeCell ref="A76:A77"/>
-    <mergeCell ref="B76:B77"/>
-    <mergeCell ref="A78:A79"/>
-    <mergeCell ref="B78:B79"/>
-    <mergeCell ref="A80:A81"/>
-    <mergeCell ref="B80:B81"/>
-    <mergeCell ref="A82:A83"/>
-    <mergeCell ref="B82:B83"/>
-    <mergeCell ref="A64:A65"/>
-    <mergeCell ref="B64:B65"/>
-    <mergeCell ref="A66:A67"/>
-    <mergeCell ref="B66:B67"/>
-    <mergeCell ref="A68:A69"/>
-    <mergeCell ref="B68:B69"/>
-    <mergeCell ref="A70:A71"/>
-    <mergeCell ref="B70:B71"/>
-    <mergeCell ref="A72:A73"/>
-    <mergeCell ref="B72:B73"/>
-    <mergeCell ref="A54:A55"/>
-    <mergeCell ref="B54:B55"/>
-    <mergeCell ref="A56:A57"/>
-    <mergeCell ref="B56:B57"/>
-    <mergeCell ref="A58:A59"/>
-    <mergeCell ref="B58:B59"/>
-    <mergeCell ref="A60:A61"/>
-    <mergeCell ref="B60:B61"/>
-    <mergeCell ref="A62:A63"/>
-    <mergeCell ref="B62:B63"/>
-    <mergeCell ref="A42:A43"/>
-    <mergeCell ref="B42:B43"/>
-    <mergeCell ref="A46:I46"/>
-    <mergeCell ref="A48:A49"/>
-    <mergeCell ref="B48:B49"/>
-    <mergeCell ref="A50:A51"/>
-    <mergeCell ref="B50:B51"/>
-    <mergeCell ref="A52:A53"/>
-    <mergeCell ref="B52:B53"/>
-    <mergeCell ref="A32:A33"/>
-    <mergeCell ref="B32:B33"/>
-    <mergeCell ref="A34:A35"/>
-    <mergeCell ref="B34:B35"/>
-    <mergeCell ref="A36:A37"/>
-    <mergeCell ref="B36:B37"/>
-    <mergeCell ref="A38:A39"/>
-    <mergeCell ref="B38:B39"/>
-    <mergeCell ref="A40:A41"/>
-    <mergeCell ref="B40:B41"/>
-    <mergeCell ref="A22:A23"/>
-    <mergeCell ref="B22:B23"/>
-    <mergeCell ref="A24:A25"/>
-    <mergeCell ref="B24:B25"/>
-    <mergeCell ref="A26:A27"/>
-    <mergeCell ref="B26:B27"/>
-    <mergeCell ref="A28:A29"/>
-    <mergeCell ref="B28:B29"/>
-    <mergeCell ref="A30:A31"/>
-    <mergeCell ref="B30:B31"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="B14:B15"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="A18:A19"/>
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="A20:A21"/>
-    <mergeCell ref="B20:B21"/>
-    <mergeCell ref="A2:I2"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="B10:B11"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
@@ -42698,17 +42698,17 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:9" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="B2" s="9"/>
-      <c r="C2" s="9"/>
-      <c r="D2" s="9"/>
-      <c r="E2" s="9"/>
-      <c r="F2" s="9"/>
-      <c r="G2" s="9"/>
-      <c r="H2" s="9"/>
-      <c r="I2" s="9"/>
+      <c r="A2" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="B2" s="14"/>
+      <c r="C2" s="14"/>
+      <c r="D2" s="14"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="14"/>
+      <c r="G2" s="14"/>
+      <c r="H2" s="14"/>
+      <c r="I2" s="14"/>
     </row>
     <row r="3" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
@@ -43820,17 +43820,17 @@
       </c>
     </row>
     <row r="46" spans="1:9" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="B46" s="9"/>
-      <c r="C46" s="9"/>
-      <c r="D46" s="9"/>
-      <c r="E46" s="9"/>
-      <c r="F46" s="9"/>
-      <c r="G46" s="9"/>
-      <c r="H46" s="9"/>
-      <c r="I46" s="9"/>
+      <c r="A46" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="B46" s="14"/>
+      <c r="C46" s="14"/>
+      <c r="D46" s="14"/>
+      <c r="E46" s="14"/>
+      <c r="F46" s="14"/>
+      <c r="G46" s="14"/>
+      <c r="H46" s="14"/>
+      <c r="I46" s="14"/>
     </row>
     <row r="47" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
@@ -44942,17 +44942,17 @@
       </c>
     </row>
     <row r="90" spans="1:9" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A90" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="B90" s="9"/>
-      <c r="C90" s="9"/>
-      <c r="D90" s="9"/>
-      <c r="E90" s="9"/>
-      <c r="F90" s="9"/>
-      <c r="G90" s="9"/>
-      <c r="H90" s="9"/>
-      <c r="I90" s="9"/>
+      <c r="A90" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="B90" s="14"/>
+      <c r="C90" s="14"/>
+      <c r="D90" s="14"/>
+      <c r="E90" s="14"/>
+      <c r="F90" s="14"/>
+      <c r="G90" s="14"/>
+      <c r="H90" s="14"/>
+      <c r="I90" s="14"/>
     </row>
     <row r="91" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
@@ -46064,17 +46064,17 @@
       </c>
     </row>
     <row r="134" spans="1:9" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A134" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="B134" s="9"/>
-      <c r="C134" s="9"/>
-      <c r="D134" s="9"/>
-      <c r="E134" s="9"/>
-      <c r="F134" s="9"/>
-      <c r="G134" s="9"/>
-      <c r="H134" s="9"/>
-      <c r="I134" s="9"/>
+      <c r="A134" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="B134" s="14"/>
+      <c r="C134" s="14"/>
+      <c r="D134" s="14"/>
+      <c r="E134" s="14"/>
+      <c r="F134" s="14"/>
+      <c r="G134" s="14"/>
+      <c r="H134" s="14"/>
+      <c r="I134" s="14"/>
     </row>
     <row r="135" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" s="1" t="s">
@@ -47186,17 +47186,17 @@
       </c>
     </row>
     <row r="178" spans="1:9" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A178" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="B178" s="9"/>
-      <c r="C178" s="9"/>
-      <c r="D178" s="9"/>
-      <c r="E178" s="9"/>
-      <c r="F178" s="9"/>
-      <c r="G178" s="9"/>
-      <c r="H178" s="9"/>
-      <c r="I178" s="9"/>
+      <c r="A178" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="B178" s="14"/>
+      <c r="C178" s="14"/>
+      <c r="D178" s="14"/>
+      <c r="E178" s="14"/>
+      <c r="F178" s="14"/>
+      <c r="G178" s="14"/>
+      <c r="H178" s="14"/>
+      <c r="I178" s="14"/>
     </row>
     <row r="179" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A179" s="1" t="s">
@@ -48308,17 +48308,17 @@
       </c>
     </row>
     <row r="222" spans="1:9" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A222" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="B222" s="9"/>
-      <c r="C222" s="9"/>
-      <c r="D222" s="9"/>
-      <c r="E222" s="9"/>
-      <c r="F222" s="9"/>
-      <c r="G222" s="9"/>
-      <c r="H222" s="9"/>
-      <c r="I222" s="9"/>
+      <c r="A222" s="14" t="s">
+        <v>50</v>
+      </c>
+      <c r="B222" s="14"/>
+      <c r="C222" s="14"/>
+      <c r="D222" s="14"/>
+      <c r="E222" s="14"/>
+      <c r="F222" s="14"/>
+      <c r="G222" s="14"/>
+      <c r="H222" s="14"/>
+      <c r="I222" s="14"/>
     </row>
     <row r="223" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A223" s="1" t="s">
@@ -49430,17 +49430,17 @@
       </c>
     </row>
     <row r="266" spans="1:9" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A266" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="B266" s="9"/>
-      <c r="C266" s="9"/>
-      <c r="D266" s="9"/>
-      <c r="E266" s="9"/>
-      <c r="F266" s="9"/>
-      <c r="G266" s="9"/>
-      <c r="H266" s="9"/>
-      <c r="I266" s="9"/>
+      <c r="A266" s="14" t="s">
+        <v>51</v>
+      </c>
+      <c r="B266" s="14"/>
+      <c r="C266" s="14"/>
+      <c r="D266" s="14"/>
+      <c r="E266" s="14"/>
+      <c r="F266" s="14"/>
+      <c r="G266" s="14"/>
+      <c r="H266" s="14"/>
+      <c r="I266" s="14"/>
     </row>
     <row r="267" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A267" s="1" t="s">
@@ -50552,17 +50552,17 @@
       </c>
     </row>
     <row r="310" spans="1:9" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A310" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="B310" s="9"/>
-      <c r="C310" s="9"/>
-      <c r="D310" s="9"/>
-      <c r="E310" s="9"/>
-      <c r="F310" s="9"/>
-      <c r="G310" s="9"/>
-      <c r="H310" s="9"/>
-      <c r="I310" s="9"/>
+      <c r="A310" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="B310" s="14"/>
+      <c r="C310" s="14"/>
+      <c r="D310" s="14"/>
+      <c r="E310" s="14"/>
+      <c r="F310" s="14"/>
+      <c r="G310" s="14"/>
+      <c r="H310" s="14"/>
+      <c r="I310" s="14"/>
     </row>
     <row r="311" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A311" s="1" t="s">
@@ -51674,17 +51674,17 @@
       </c>
     </row>
     <row r="354" spans="1:9" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A354" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="B354" s="9"/>
-      <c r="C354" s="9"/>
-      <c r="D354" s="9"/>
-      <c r="E354" s="9"/>
-      <c r="F354" s="9"/>
-      <c r="G354" s="9"/>
-      <c r="H354" s="9"/>
-      <c r="I354" s="9"/>
+      <c r="A354" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="B354" s="14"/>
+      <c r="C354" s="14"/>
+      <c r="D354" s="14"/>
+      <c r="E354" s="14"/>
+      <c r="F354" s="14"/>
+      <c r="G354" s="14"/>
+      <c r="H354" s="14"/>
+      <c r="I354" s="14"/>
     </row>
     <row r="355" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A355" s="1" t="s">
@@ -52796,17 +52796,17 @@
       </c>
     </row>
     <row r="398" spans="1:9" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A398" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="B398" s="9"/>
-      <c r="C398" s="9"/>
-      <c r="D398" s="9"/>
-      <c r="E398" s="9"/>
-      <c r="F398" s="9"/>
-      <c r="G398" s="9"/>
-      <c r="H398" s="9"/>
-      <c r="I398" s="9"/>
+      <c r="A398" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="B398" s="14"/>
+      <c r="C398" s="14"/>
+      <c r="D398" s="14"/>
+      <c r="E398" s="14"/>
+      <c r="F398" s="14"/>
+      <c r="G398" s="14"/>
+      <c r="H398" s="14"/>
+      <c r="I398" s="14"/>
     </row>
     <row r="399" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A399" s="1" t="s">
@@ -53918,17 +53918,17 @@
       </c>
     </row>
     <row r="442" spans="1:9" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A442" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="B442" s="9"/>
-      <c r="C442" s="9"/>
-      <c r="D442" s="9"/>
-      <c r="E442" s="9"/>
-      <c r="F442" s="9"/>
-      <c r="G442" s="9"/>
-      <c r="H442" s="9"/>
-      <c r="I442" s="9"/>
+      <c r="A442" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="B442" s="14"/>
+      <c r="C442" s="14"/>
+      <c r="D442" s="14"/>
+      <c r="E442" s="14"/>
+      <c r="F442" s="14"/>
+      <c r="G442" s="14"/>
+      <c r="H442" s="14"/>
+      <c r="I442" s="14"/>
     </row>
     <row r="443" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A443" s="1" t="s">
@@ -55040,17 +55040,17 @@
       </c>
     </row>
     <row r="486" spans="1:9" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A486" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="B486" s="9"/>
-      <c r="C486" s="9"/>
-      <c r="D486" s="9"/>
-      <c r="E486" s="9"/>
-      <c r="F486" s="9"/>
-      <c r="G486" s="9"/>
-      <c r="H486" s="9"/>
-      <c r="I486" s="9"/>
+      <c r="A486" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="B486" s="14"/>
+      <c r="C486" s="14"/>
+      <c r="D486" s="14"/>
+      <c r="E486" s="14"/>
+      <c r="F486" s="14"/>
+      <c r="G486" s="14"/>
+      <c r="H486" s="14"/>
+      <c r="I486" s="14"/>
     </row>
     <row r="487" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A487" s="1" t="s">
@@ -56163,6 +56163,484 @@
     </row>
   </sheetData>
   <mergeCells count="492">
+    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="A18:A19"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="A20:A21"/>
+    <mergeCell ref="B20:B21"/>
+    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="B22:B23"/>
+    <mergeCell ref="A24:A25"/>
+    <mergeCell ref="B24:B25"/>
+    <mergeCell ref="A26:A27"/>
+    <mergeCell ref="B26:B27"/>
+    <mergeCell ref="A28:A29"/>
+    <mergeCell ref="B28:B29"/>
+    <mergeCell ref="A30:A31"/>
+    <mergeCell ref="B30:B31"/>
+    <mergeCell ref="A32:A33"/>
+    <mergeCell ref="B32:B33"/>
+    <mergeCell ref="A34:A35"/>
+    <mergeCell ref="B34:B35"/>
+    <mergeCell ref="A36:A37"/>
+    <mergeCell ref="B36:B37"/>
+    <mergeCell ref="A38:A39"/>
+    <mergeCell ref="B38:B39"/>
+    <mergeCell ref="A40:A41"/>
+    <mergeCell ref="B40:B41"/>
+    <mergeCell ref="A42:A43"/>
+    <mergeCell ref="B42:B43"/>
+    <mergeCell ref="A46:I46"/>
+    <mergeCell ref="A48:A49"/>
+    <mergeCell ref="B48:B49"/>
+    <mergeCell ref="A50:A51"/>
+    <mergeCell ref="B50:B51"/>
+    <mergeCell ref="A52:A53"/>
+    <mergeCell ref="B52:B53"/>
+    <mergeCell ref="A54:A55"/>
+    <mergeCell ref="B54:B55"/>
+    <mergeCell ref="A56:A57"/>
+    <mergeCell ref="B56:B57"/>
+    <mergeCell ref="A58:A59"/>
+    <mergeCell ref="B58:B59"/>
+    <mergeCell ref="A60:A61"/>
+    <mergeCell ref="B60:B61"/>
+    <mergeCell ref="A62:A63"/>
+    <mergeCell ref="B62:B63"/>
+    <mergeCell ref="A64:A65"/>
+    <mergeCell ref="B64:B65"/>
+    <mergeCell ref="A66:A67"/>
+    <mergeCell ref="B66:B67"/>
+    <mergeCell ref="A68:A69"/>
+    <mergeCell ref="B68:B69"/>
+    <mergeCell ref="A70:A71"/>
+    <mergeCell ref="B70:B71"/>
+    <mergeCell ref="A72:A73"/>
+    <mergeCell ref="B72:B73"/>
+    <mergeCell ref="A74:A75"/>
+    <mergeCell ref="B74:B75"/>
+    <mergeCell ref="A76:A77"/>
+    <mergeCell ref="B76:B77"/>
+    <mergeCell ref="A78:A79"/>
+    <mergeCell ref="B78:B79"/>
+    <mergeCell ref="A80:A81"/>
+    <mergeCell ref="B80:B81"/>
+    <mergeCell ref="A82:A83"/>
+    <mergeCell ref="B82:B83"/>
+    <mergeCell ref="A84:A85"/>
+    <mergeCell ref="B84:B85"/>
+    <mergeCell ref="A86:A87"/>
+    <mergeCell ref="B86:B87"/>
+    <mergeCell ref="A90:I90"/>
+    <mergeCell ref="A92:A93"/>
+    <mergeCell ref="B92:B93"/>
+    <mergeCell ref="A94:A95"/>
+    <mergeCell ref="B94:B95"/>
+    <mergeCell ref="A96:A97"/>
+    <mergeCell ref="B96:B97"/>
+    <mergeCell ref="A98:A99"/>
+    <mergeCell ref="B98:B99"/>
+    <mergeCell ref="A100:A101"/>
+    <mergeCell ref="B100:B101"/>
+    <mergeCell ref="A102:A103"/>
+    <mergeCell ref="B102:B103"/>
+    <mergeCell ref="A104:A105"/>
+    <mergeCell ref="B104:B105"/>
+    <mergeCell ref="A106:A107"/>
+    <mergeCell ref="B106:B107"/>
+    <mergeCell ref="A108:A109"/>
+    <mergeCell ref="B108:B109"/>
+    <mergeCell ref="A110:A111"/>
+    <mergeCell ref="B110:B111"/>
+    <mergeCell ref="A112:A113"/>
+    <mergeCell ref="B112:B113"/>
+    <mergeCell ref="A114:A115"/>
+    <mergeCell ref="B114:B115"/>
+    <mergeCell ref="A116:A117"/>
+    <mergeCell ref="B116:B117"/>
+    <mergeCell ref="A118:A119"/>
+    <mergeCell ref="B118:B119"/>
+    <mergeCell ref="A120:A121"/>
+    <mergeCell ref="B120:B121"/>
+    <mergeCell ref="A122:A123"/>
+    <mergeCell ref="B122:B123"/>
+    <mergeCell ref="A124:A125"/>
+    <mergeCell ref="B124:B125"/>
+    <mergeCell ref="A126:A127"/>
+    <mergeCell ref="B126:B127"/>
+    <mergeCell ref="A128:A129"/>
+    <mergeCell ref="B128:B129"/>
+    <mergeCell ref="A130:A131"/>
+    <mergeCell ref="B130:B131"/>
+    <mergeCell ref="A134:I134"/>
+    <mergeCell ref="A136:A137"/>
+    <mergeCell ref="B136:B137"/>
+    <mergeCell ref="A138:A139"/>
+    <mergeCell ref="B138:B139"/>
+    <mergeCell ref="A140:A141"/>
+    <mergeCell ref="B140:B141"/>
+    <mergeCell ref="A142:A143"/>
+    <mergeCell ref="B142:B143"/>
+    <mergeCell ref="A144:A145"/>
+    <mergeCell ref="B144:B145"/>
+    <mergeCell ref="A146:A147"/>
+    <mergeCell ref="B146:B147"/>
+    <mergeCell ref="A148:A149"/>
+    <mergeCell ref="B148:B149"/>
+    <mergeCell ref="A150:A151"/>
+    <mergeCell ref="B150:B151"/>
+    <mergeCell ref="A152:A153"/>
+    <mergeCell ref="B152:B153"/>
+    <mergeCell ref="A154:A155"/>
+    <mergeCell ref="B154:B155"/>
+    <mergeCell ref="A156:A157"/>
+    <mergeCell ref="B156:B157"/>
+    <mergeCell ref="A158:A159"/>
+    <mergeCell ref="B158:B159"/>
+    <mergeCell ref="A160:A161"/>
+    <mergeCell ref="B160:B161"/>
+    <mergeCell ref="A162:A163"/>
+    <mergeCell ref="B162:B163"/>
+    <mergeCell ref="A164:A165"/>
+    <mergeCell ref="B164:B165"/>
+    <mergeCell ref="A166:A167"/>
+    <mergeCell ref="B166:B167"/>
+    <mergeCell ref="A168:A169"/>
+    <mergeCell ref="B168:B169"/>
+    <mergeCell ref="A170:A171"/>
+    <mergeCell ref="B170:B171"/>
+    <mergeCell ref="A172:A173"/>
+    <mergeCell ref="B172:B173"/>
+    <mergeCell ref="A174:A175"/>
+    <mergeCell ref="B174:B175"/>
+    <mergeCell ref="A178:I178"/>
+    <mergeCell ref="A180:A181"/>
+    <mergeCell ref="B180:B181"/>
+    <mergeCell ref="A182:A183"/>
+    <mergeCell ref="B182:B183"/>
+    <mergeCell ref="A184:A185"/>
+    <mergeCell ref="B184:B185"/>
+    <mergeCell ref="A186:A187"/>
+    <mergeCell ref="B186:B187"/>
+    <mergeCell ref="A188:A189"/>
+    <mergeCell ref="B188:B189"/>
+    <mergeCell ref="A190:A191"/>
+    <mergeCell ref="B190:B191"/>
+    <mergeCell ref="A192:A193"/>
+    <mergeCell ref="B192:B193"/>
+    <mergeCell ref="A194:A195"/>
+    <mergeCell ref="B194:B195"/>
+    <mergeCell ref="A196:A197"/>
+    <mergeCell ref="B196:B197"/>
+    <mergeCell ref="A198:A199"/>
+    <mergeCell ref="B198:B199"/>
+    <mergeCell ref="A200:A201"/>
+    <mergeCell ref="B200:B201"/>
+    <mergeCell ref="A202:A203"/>
+    <mergeCell ref="B202:B203"/>
+    <mergeCell ref="A204:A205"/>
+    <mergeCell ref="B204:B205"/>
+    <mergeCell ref="A206:A207"/>
+    <mergeCell ref="B206:B207"/>
+    <mergeCell ref="A208:A209"/>
+    <mergeCell ref="B208:B209"/>
+    <mergeCell ref="A210:A211"/>
+    <mergeCell ref="B210:B211"/>
+    <mergeCell ref="A212:A213"/>
+    <mergeCell ref="B212:B213"/>
+    <mergeCell ref="A214:A215"/>
+    <mergeCell ref="B214:B215"/>
+    <mergeCell ref="A216:A217"/>
+    <mergeCell ref="B216:B217"/>
+    <mergeCell ref="A218:A219"/>
+    <mergeCell ref="B218:B219"/>
+    <mergeCell ref="A222:I222"/>
+    <mergeCell ref="A224:A225"/>
+    <mergeCell ref="B224:B225"/>
+    <mergeCell ref="A226:A227"/>
+    <mergeCell ref="B226:B227"/>
+    <mergeCell ref="A228:A229"/>
+    <mergeCell ref="B228:B229"/>
+    <mergeCell ref="A230:A231"/>
+    <mergeCell ref="B230:B231"/>
+    <mergeCell ref="A232:A233"/>
+    <mergeCell ref="B232:B233"/>
+    <mergeCell ref="A234:A235"/>
+    <mergeCell ref="B234:B235"/>
+    <mergeCell ref="A236:A237"/>
+    <mergeCell ref="B236:B237"/>
+    <mergeCell ref="A238:A239"/>
+    <mergeCell ref="B238:B239"/>
+    <mergeCell ref="A240:A241"/>
+    <mergeCell ref="B240:B241"/>
+    <mergeCell ref="A242:A243"/>
+    <mergeCell ref="B242:B243"/>
+    <mergeCell ref="A244:A245"/>
+    <mergeCell ref="B244:B245"/>
+    <mergeCell ref="A246:A247"/>
+    <mergeCell ref="B246:B247"/>
+    <mergeCell ref="A248:A249"/>
+    <mergeCell ref="B248:B249"/>
+    <mergeCell ref="A250:A251"/>
+    <mergeCell ref="B250:B251"/>
+    <mergeCell ref="A252:A253"/>
+    <mergeCell ref="B252:B253"/>
+    <mergeCell ref="A254:A255"/>
+    <mergeCell ref="B254:B255"/>
+    <mergeCell ref="A256:A257"/>
+    <mergeCell ref="B256:B257"/>
+    <mergeCell ref="A258:A259"/>
+    <mergeCell ref="B258:B259"/>
+    <mergeCell ref="A260:A261"/>
+    <mergeCell ref="B260:B261"/>
+    <mergeCell ref="A262:A263"/>
+    <mergeCell ref="B262:B263"/>
+    <mergeCell ref="A266:I266"/>
+    <mergeCell ref="A268:A269"/>
+    <mergeCell ref="B268:B269"/>
+    <mergeCell ref="A270:A271"/>
+    <mergeCell ref="B270:B271"/>
+    <mergeCell ref="A272:A273"/>
+    <mergeCell ref="B272:B273"/>
+    <mergeCell ref="A274:A275"/>
+    <mergeCell ref="B274:B275"/>
+    <mergeCell ref="A276:A277"/>
+    <mergeCell ref="B276:B277"/>
+    <mergeCell ref="A278:A279"/>
+    <mergeCell ref="B278:B279"/>
+    <mergeCell ref="A280:A281"/>
+    <mergeCell ref="B280:B281"/>
+    <mergeCell ref="A282:A283"/>
+    <mergeCell ref="B282:B283"/>
+    <mergeCell ref="A284:A285"/>
+    <mergeCell ref="B284:B285"/>
+    <mergeCell ref="A286:A287"/>
+    <mergeCell ref="B286:B287"/>
+    <mergeCell ref="A288:A289"/>
+    <mergeCell ref="B288:B289"/>
+    <mergeCell ref="A290:A291"/>
+    <mergeCell ref="B290:B291"/>
+    <mergeCell ref="A292:A293"/>
+    <mergeCell ref="B292:B293"/>
+    <mergeCell ref="A294:A295"/>
+    <mergeCell ref="B294:B295"/>
+    <mergeCell ref="A296:A297"/>
+    <mergeCell ref="B296:B297"/>
+    <mergeCell ref="A298:A299"/>
+    <mergeCell ref="B298:B299"/>
+    <mergeCell ref="A300:A301"/>
+    <mergeCell ref="B300:B301"/>
+    <mergeCell ref="A302:A303"/>
+    <mergeCell ref="B302:B303"/>
+    <mergeCell ref="A304:A305"/>
+    <mergeCell ref="B304:B305"/>
+    <mergeCell ref="A306:A307"/>
+    <mergeCell ref="B306:B307"/>
+    <mergeCell ref="A310:I310"/>
+    <mergeCell ref="A312:A313"/>
+    <mergeCell ref="B312:B313"/>
+    <mergeCell ref="A314:A315"/>
+    <mergeCell ref="B314:B315"/>
+    <mergeCell ref="A316:A317"/>
+    <mergeCell ref="B316:B317"/>
+    <mergeCell ref="A318:A319"/>
+    <mergeCell ref="B318:B319"/>
+    <mergeCell ref="A320:A321"/>
+    <mergeCell ref="B320:B321"/>
+    <mergeCell ref="A322:A323"/>
+    <mergeCell ref="B322:B323"/>
+    <mergeCell ref="A324:A325"/>
+    <mergeCell ref="B324:B325"/>
+    <mergeCell ref="A326:A327"/>
+    <mergeCell ref="B326:B327"/>
+    <mergeCell ref="A328:A329"/>
+    <mergeCell ref="B328:B329"/>
+    <mergeCell ref="A330:A331"/>
+    <mergeCell ref="B330:B331"/>
+    <mergeCell ref="A332:A333"/>
+    <mergeCell ref="B332:B333"/>
+    <mergeCell ref="A334:A335"/>
+    <mergeCell ref="B334:B335"/>
+    <mergeCell ref="A336:A337"/>
+    <mergeCell ref="B336:B337"/>
+    <mergeCell ref="A338:A339"/>
+    <mergeCell ref="B338:B339"/>
+    <mergeCell ref="A340:A341"/>
+    <mergeCell ref="B340:B341"/>
+    <mergeCell ref="A342:A343"/>
+    <mergeCell ref="B342:B343"/>
+    <mergeCell ref="A344:A345"/>
+    <mergeCell ref="B344:B345"/>
+    <mergeCell ref="A346:A347"/>
+    <mergeCell ref="B346:B347"/>
+    <mergeCell ref="A348:A349"/>
+    <mergeCell ref="B348:B349"/>
+    <mergeCell ref="A350:A351"/>
+    <mergeCell ref="B350:B351"/>
+    <mergeCell ref="A354:I354"/>
+    <mergeCell ref="A356:A357"/>
+    <mergeCell ref="B356:B357"/>
+    <mergeCell ref="A358:A359"/>
+    <mergeCell ref="B358:B359"/>
+    <mergeCell ref="A360:A361"/>
+    <mergeCell ref="B360:B361"/>
+    <mergeCell ref="A362:A363"/>
+    <mergeCell ref="B362:B363"/>
+    <mergeCell ref="A364:A365"/>
+    <mergeCell ref="B364:B365"/>
+    <mergeCell ref="A366:A367"/>
+    <mergeCell ref="B366:B367"/>
+    <mergeCell ref="A368:A369"/>
+    <mergeCell ref="B368:B369"/>
+    <mergeCell ref="A370:A371"/>
+    <mergeCell ref="B370:B371"/>
+    <mergeCell ref="A372:A373"/>
+    <mergeCell ref="B372:B373"/>
+    <mergeCell ref="A374:A375"/>
+    <mergeCell ref="B374:B375"/>
+    <mergeCell ref="A376:A377"/>
+    <mergeCell ref="B376:B377"/>
+    <mergeCell ref="A378:A379"/>
+    <mergeCell ref="B378:B379"/>
+    <mergeCell ref="A380:A381"/>
+    <mergeCell ref="B380:B381"/>
+    <mergeCell ref="A382:A383"/>
+    <mergeCell ref="B382:B383"/>
+    <mergeCell ref="A384:A385"/>
+    <mergeCell ref="B384:B385"/>
+    <mergeCell ref="A386:A387"/>
+    <mergeCell ref="B386:B387"/>
+    <mergeCell ref="A388:A389"/>
+    <mergeCell ref="B388:B389"/>
+    <mergeCell ref="A390:A391"/>
+    <mergeCell ref="B390:B391"/>
+    <mergeCell ref="A392:A393"/>
+    <mergeCell ref="B392:B393"/>
+    <mergeCell ref="A394:A395"/>
+    <mergeCell ref="B394:B395"/>
+    <mergeCell ref="A398:I398"/>
+    <mergeCell ref="A400:A401"/>
+    <mergeCell ref="B400:B401"/>
+    <mergeCell ref="A402:A403"/>
+    <mergeCell ref="B402:B403"/>
+    <mergeCell ref="A404:A405"/>
+    <mergeCell ref="B404:B405"/>
+    <mergeCell ref="A406:A407"/>
+    <mergeCell ref="B406:B407"/>
+    <mergeCell ref="A408:A409"/>
+    <mergeCell ref="B408:B409"/>
+    <mergeCell ref="A410:A411"/>
+    <mergeCell ref="B410:B411"/>
+    <mergeCell ref="A412:A413"/>
+    <mergeCell ref="B412:B413"/>
+    <mergeCell ref="A414:A415"/>
+    <mergeCell ref="B414:B415"/>
+    <mergeCell ref="A416:A417"/>
+    <mergeCell ref="B416:B417"/>
+    <mergeCell ref="A418:A419"/>
+    <mergeCell ref="B418:B419"/>
+    <mergeCell ref="A420:A421"/>
+    <mergeCell ref="B420:B421"/>
+    <mergeCell ref="A422:A423"/>
+    <mergeCell ref="B422:B423"/>
+    <mergeCell ref="A424:A425"/>
+    <mergeCell ref="B424:B425"/>
+    <mergeCell ref="A426:A427"/>
+    <mergeCell ref="B426:B427"/>
+    <mergeCell ref="A428:A429"/>
+    <mergeCell ref="B428:B429"/>
+    <mergeCell ref="A430:A431"/>
+    <mergeCell ref="B430:B431"/>
+    <mergeCell ref="A432:A433"/>
+    <mergeCell ref="B432:B433"/>
+    <mergeCell ref="A434:A435"/>
+    <mergeCell ref="B434:B435"/>
+    <mergeCell ref="A436:A437"/>
+    <mergeCell ref="B436:B437"/>
+    <mergeCell ref="A438:A439"/>
+    <mergeCell ref="B438:B439"/>
+    <mergeCell ref="A442:I442"/>
+    <mergeCell ref="A444:A445"/>
+    <mergeCell ref="B444:B445"/>
+    <mergeCell ref="A446:A447"/>
+    <mergeCell ref="B446:B447"/>
+    <mergeCell ref="A448:A449"/>
+    <mergeCell ref="B448:B449"/>
+    <mergeCell ref="A450:A451"/>
+    <mergeCell ref="B450:B451"/>
+    <mergeCell ref="A452:A453"/>
+    <mergeCell ref="B452:B453"/>
+    <mergeCell ref="A454:A455"/>
+    <mergeCell ref="B454:B455"/>
+    <mergeCell ref="A456:A457"/>
+    <mergeCell ref="B456:B457"/>
+    <mergeCell ref="A458:A459"/>
+    <mergeCell ref="B458:B459"/>
+    <mergeCell ref="A460:A461"/>
+    <mergeCell ref="B460:B461"/>
+    <mergeCell ref="A462:A463"/>
+    <mergeCell ref="B462:B463"/>
+    <mergeCell ref="A464:A465"/>
+    <mergeCell ref="B464:B465"/>
+    <mergeCell ref="A466:A467"/>
+    <mergeCell ref="B466:B467"/>
+    <mergeCell ref="A468:A469"/>
+    <mergeCell ref="B468:B469"/>
+    <mergeCell ref="A470:A471"/>
+    <mergeCell ref="B470:B471"/>
+    <mergeCell ref="A472:A473"/>
+    <mergeCell ref="B472:B473"/>
+    <mergeCell ref="A474:A475"/>
+    <mergeCell ref="B474:B475"/>
+    <mergeCell ref="A476:A477"/>
+    <mergeCell ref="B476:B477"/>
+    <mergeCell ref="A478:A479"/>
+    <mergeCell ref="B478:B479"/>
+    <mergeCell ref="A480:A481"/>
+    <mergeCell ref="B480:B481"/>
+    <mergeCell ref="A482:A483"/>
+    <mergeCell ref="B482:B483"/>
+    <mergeCell ref="A486:I486"/>
+    <mergeCell ref="A488:A489"/>
+    <mergeCell ref="B488:B489"/>
+    <mergeCell ref="A490:A491"/>
+    <mergeCell ref="B490:B491"/>
+    <mergeCell ref="A492:A493"/>
+    <mergeCell ref="B492:B493"/>
+    <mergeCell ref="A494:A495"/>
+    <mergeCell ref="B494:B495"/>
+    <mergeCell ref="A496:A497"/>
+    <mergeCell ref="B496:B497"/>
+    <mergeCell ref="A498:A499"/>
+    <mergeCell ref="B498:B499"/>
+    <mergeCell ref="A500:A501"/>
+    <mergeCell ref="B500:B501"/>
+    <mergeCell ref="A502:A503"/>
+    <mergeCell ref="B502:B503"/>
+    <mergeCell ref="A504:A505"/>
+    <mergeCell ref="B504:B505"/>
+    <mergeCell ref="A506:A507"/>
+    <mergeCell ref="B506:B507"/>
+    <mergeCell ref="A508:A509"/>
+    <mergeCell ref="B508:B509"/>
+    <mergeCell ref="A510:A511"/>
+    <mergeCell ref="B510:B511"/>
+    <mergeCell ref="A512:A513"/>
+    <mergeCell ref="B512:B513"/>
     <mergeCell ref="A524:A525"/>
     <mergeCell ref="B524:B525"/>
     <mergeCell ref="A526:A527"/>
@@ -56177,484 +56655,6 @@
     <mergeCell ref="B520:B521"/>
     <mergeCell ref="A522:A523"/>
     <mergeCell ref="B522:B523"/>
-    <mergeCell ref="A504:A505"/>
-    <mergeCell ref="B504:B505"/>
-    <mergeCell ref="A506:A507"/>
-    <mergeCell ref="B506:B507"/>
-    <mergeCell ref="A508:A509"/>
-    <mergeCell ref="B508:B509"/>
-    <mergeCell ref="A510:A511"/>
-    <mergeCell ref="B510:B511"/>
-    <mergeCell ref="A512:A513"/>
-    <mergeCell ref="B512:B513"/>
-    <mergeCell ref="A494:A495"/>
-    <mergeCell ref="B494:B495"/>
-    <mergeCell ref="A496:A497"/>
-    <mergeCell ref="B496:B497"/>
-    <mergeCell ref="A498:A499"/>
-    <mergeCell ref="B498:B499"/>
-    <mergeCell ref="A500:A501"/>
-    <mergeCell ref="B500:B501"/>
-    <mergeCell ref="A502:A503"/>
-    <mergeCell ref="B502:B503"/>
-    <mergeCell ref="A482:A483"/>
-    <mergeCell ref="B482:B483"/>
-    <mergeCell ref="A486:I486"/>
-    <mergeCell ref="A488:A489"/>
-    <mergeCell ref="B488:B489"/>
-    <mergeCell ref="A490:A491"/>
-    <mergeCell ref="B490:B491"/>
-    <mergeCell ref="A492:A493"/>
-    <mergeCell ref="B492:B493"/>
-    <mergeCell ref="A472:A473"/>
-    <mergeCell ref="B472:B473"/>
-    <mergeCell ref="A474:A475"/>
-    <mergeCell ref="B474:B475"/>
-    <mergeCell ref="A476:A477"/>
-    <mergeCell ref="B476:B477"/>
-    <mergeCell ref="A478:A479"/>
-    <mergeCell ref="B478:B479"/>
-    <mergeCell ref="A480:A481"/>
-    <mergeCell ref="B480:B481"/>
-    <mergeCell ref="A462:A463"/>
-    <mergeCell ref="B462:B463"/>
-    <mergeCell ref="A464:A465"/>
-    <mergeCell ref="B464:B465"/>
-    <mergeCell ref="A466:A467"/>
-    <mergeCell ref="B466:B467"/>
-    <mergeCell ref="A468:A469"/>
-    <mergeCell ref="B468:B469"/>
-    <mergeCell ref="A470:A471"/>
-    <mergeCell ref="B470:B471"/>
-    <mergeCell ref="A452:A453"/>
-    <mergeCell ref="B452:B453"/>
-    <mergeCell ref="A454:A455"/>
-    <mergeCell ref="B454:B455"/>
-    <mergeCell ref="A456:A457"/>
-    <mergeCell ref="B456:B457"/>
-    <mergeCell ref="A458:A459"/>
-    <mergeCell ref="B458:B459"/>
-    <mergeCell ref="A460:A461"/>
-    <mergeCell ref="B460:B461"/>
-    <mergeCell ref="A442:I442"/>
-    <mergeCell ref="A444:A445"/>
-    <mergeCell ref="B444:B445"/>
-    <mergeCell ref="A446:A447"/>
-    <mergeCell ref="B446:B447"/>
-    <mergeCell ref="A448:A449"/>
-    <mergeCell ref="B448:B449"/>
-    <mergeCell ref="A450:A451"/>
-    <mergeCell ref="B450:B451"/>
-    <mergeCell ref="A430:A431"/>
-    <mergeCell ref="B430:B431"/>
-    <mergeCell ref="A432:A433"/>
-    <mergeCell ref="B432:B433"/>
-    <mergeCell ref="A434:A435"/>
-    <mergeCell ref="B434:B435"/>
-    <mergeCell ref="A436:A437"/>
-    <mergeCell ref="B436:B437"/>
-    <mergeCell ref="A438:A439"/>
-    <mergeCell ref="B438:B439"/>
-    <mergeCell ref="A420:A421"/>
-    <mergeCell ref="B420:B421"/>
-    <mergeCell ref="A422:A423"/>
-    <mergeCell ref="B422:B423"/>
-    <mergeCell ref="A424:A425"/>
-    <mergeCell ref="B424:B425"/>
-    <mergeCell ref="A426:A427"/>
-    <mergeCell ref="B426:B427"/>
-    <mergeCell ref="A428:A429"/>
-    <mergeCell ref="B428:B429"/>
-    <mergeCell ref="A410:A411"/>
-    <mergeCell ref="B410:B411"/>
-    <mergeCell ref="A412:A413"/>
-    <mergeCell ref="B412:B413"/>
-    <mergeCell ref="A414:A415"/>
-    <mergeCell ref="B414:B415"/>
-    <mergeCell ref="A416:A417"/>
-    <mergeCell ref="B416:B417"/>
-    <mergeCell ref="A418:A419"/>
-    <mergeCell ref="B418:B419"/>
-    <mergeCell ref="A400:A401"/>
-    <mergeCell ref="B400:B401"/>
-    <mergeCell ref="A402:A403"/>
-    <mergeCell ref="B402:B403"/>
-    <mergeCell ref="A404:A405"/>
-    <mergeCell ref="B404:B405"/>
-    <mergeCell ref="A406:A407"/>
-    <mergeCell ref="B406:B407"/>
-    <mergeCell ref="A408:A409"/>
-    <mergeCell ref="B408:B409"/>
-    <mergeCell ref="A388:A389"/>
-    <mergeCell ref="B388:B389"/>
-    <mergeCell ref="A390:A391"/>
-    <mergeCell ref="B390:B391"/>
-    <mergeCell ref="A392:A393"/>
-    <mergeCell ref="B392:B393"/>
-    <mergeCell ref="A394:A395"/>
-    <mergeCell ref="B394:B395"/>
-    <mergeCell ref="A398:I398"/>
-    <mergeCell ref="A378:A379"/>
-    <mergeCell ref="B378:B379"/>
-    <mergeCell ref="A380:A381"/>
-    <mergeCell ref="B380:B381"/>
-    <mergeCell ref="A382:A383"/>
-    <mergeCell ref="B382:B383"/>
-    <mergeCell ref="A384:A385"/>
-    <mergeCell ref="B384:B385"/>
-    <mergeCell ref="A386:A387"/>
-    <mergeCell ref="B386:B387"/>
-    <mergeCell ref="A368:A369"/>
-    <mergeCell ref="B368:B369"/>
-    <mergeCell ref="A370:A371"/>
-    <mergeCell ref="B370:B371"/>
-    <mergeCell ref="A372:A373"/>
-    <mergeCell ref="B372:B373"/>
-    <mergeCell ref="A374:A375"/>
-    <mergeCell ref="B374:B375"/>
-    <mergeCell ref="A376:A377"/>
-    <mergeCell ref="B376:B377"/>
-    <mergeCell ref="A358:A359"/>
-    <mergeCell ref="B358:B359"/>
-    <mergeCell ref="A360:A361"/>
-    <mergeCell ref="B360:B361"/>
-    <mergeCell ref="A362:A363"/>
-    <mergeCell ref="B362:B363"/>
-    <mergeCell ref="A364:A365"/>
-    <mergeCell ref="B364:B365"/>
-    <mergeCell ref="A366:A367"/>
-    <mergeCell ref="B366:B367"/>
-    <mergeCell ref="A346:A347"/>
-    <mergeCell ref="B346:B347"/>
-    <mergeCell ref="A348:A349"/>
-    <mergeCell ref="B348:B349"/>
-    <mergeCell ref="A350:A351"/>
-    <mergeCell ref="B350:B351"/>
-    <mergeCell ref="A354:I354"/>
-    <mergeCell ref="A356:A357"/>
-    <mergeCell ref="B356:B357"/>
-    <mergeCell ref="A336:A337"/>
-    <mergeCell ref="B336:B337"/>
-    <mergeCell ref="A338:A339"/>
-    <mergeCell ref="B338:B339"/>
-    <mergeCell ref="A340:A341"/>
-    <mergeCell ref="B340:B341"/>
-    <mergeCell ref="A342:A343"/>
-    <mergeCell ref="B342:B343"/>
-    <mergeCell ref="A344:A345"/>
-    <mergeCell ref="B344:B345"/>
-    <mergeCell ref="A326:A327"/>
-    <mergeCell ref="B326:B327"/>
-    <mergeCell ref="A328:A329"/>
-    <mergeCell ref="B328:B329"/>
-    <mergeCell ref="A330:A331"/>
-    <mergeCell ref="B330:B331"/>
-    <mergeCell ref="A332:A333"/>
-    <mergeCell ref="B332:B333"/>
-    <mergeCell ref="A334:A335"/>
-    <mergeCell ref="B334:B335"/>
-    <mergeCell ref="A316:A317"/>
-    <mergeCell ref="B316:B317"/>
-    <mergeCell ref="A318:A319"/>
-    <mergeCell ref="B318:B319"/>
-    <mergeCell ref="A320:A321"/>
-    <mergeCell ref="B320:B321"/>
-    <mergeCell ref="A322:A323"/>
-    <mergeCell ref="B322:B323"/>
-    <mergeCell ref="A324:A325"/>
-    <mergeCell ref="B324:B325"/>
-    <mergeCell ref="A304:A305"/>
-    <mergeCell ref="B304:B305"/>
-    <mergeCell ref="A306:A307"/>
-    <mergeCell ref="B306:B307"/>
-    <mergeCell ref="A310:I310"/>
-    <mergeCell ref="A312:A313"/>
-    <mergeCell ref="B312:B313"/>
-    <mergeCell ref="A314:A315"/>
-    <mergeCell ref="B314:B315"/>
-    <mergeCell ref="A294:A295"/>
-    <mergeCell ref="B294:B295"/>
-    <mergeCell ref="A296:A297"/>
-    <mergeCell ref="B296:B297"/>
-    <mergeCell ref="A298:A299"/>
-    <mergeCell ref="B298:B299"/>
-    <mergeCell ref="A300:A301"/>
-    <mergeCell ref="B300:B301"/>
-    <mergeCell ref="A302:A303"/>
-    <mergeCell ref="B302:B303"/>
-    <mergeCell ref="A284:A285"/>
-    <mergeCell ref="B284:B285"/>
-    <mergeCell ref="A286:A287"/>
-    <mergeCell ref="B286:B287"/>
-    <mergeCell ref="A288:A289"/>
-    <mergeCell ref="B288:B289"/>
-    <mergeCell ref="A290:A291"/>
-    <mergeCell ref="B290:B291"/>
-    <mergeCell ref="A292:A293"/>
-    <mergeCell ref="B292:B293"/>
-    <mergeCell ref="A274:A275"/>
-    <mergeCell ref="B274:B275"/>
-    <mergeCell ref="A276:A277"/>
-    <mergeCell ref="B276:B277"/>
-    <mergeCell ref="A278:A279"/>
-    <mergeCell ref="B278:B279"/>
-    <mergeCell ref="A280:A281"/>
-    <mergeCell ref="B280:B281"/>
-    <mergeCell ref="A282:A283"/>
-    <mergeCell ref="B282:B283"/>
-    <mergeCell ref="A262:A263"/>
-    <mergeCell ref="B262:B263"/>
-    <mergeCell ref="A266:I266"/>
-    <mergeCell ref="A268:A269"/>
-    <mergeCell ref="B268:B269"/>
-    <mergeCell ref="A270:A271"/>
-    <mergeCell ref="B270:B271"/>
-    <mergeCell ref="A272:A273"/>
-    <mergeCell ref="B272:B273"/>
-    <mergeCell ref="A252:A253"/>
-    <mergeCell ref="B252:B253"/>
-    <mergeCell ref="A254:A255"/>
-    <mergeCell ref="B254:B255"/>
-    <mergeCell ref="A256:A257"/>
-    <mergeCell ref="B256:B257"/>
-    <mergeCell ref="A258:A259"/>
-    <mergeCell ref="B258:B259"/>
-    <mergeCell ref="A260:A261"/>
-    <mergeCell ref="B260:B261"/>
-    <mergeCell ref="A242:A243"/>
-    <mergeCell ref="B242:B243"/>
-    <mergeCell ref="A244:A245"/>
-    <mergeCell ref="B244:B245"/>
-    <mergeCell ref="A246:A247"/>
-    <mergeCell ref="B246:B247"/>
-    <mergeCell ref="A248:A249"/>
-    <mergeCell ref="B248:B249"/>
-    <mergeCell ref="A250:A251"/>
-    <mergeCell ref="B250:B251"/>
-    <mergeCell ref="A232:A233"/>
-    <mergeCell ref="B232:B233"/>
-    <mergeCell ref="A234:A235"/>
-    <mergeCell ref="B234:B235"/>
-    <mergeCell ref="A236:A237"/>
-    <mergeCell ref="B236:B237"/>
-    <mergeCell ref="A238:A239"/>
-    <mergeCell ref="B238:B239"/>
-    <mergeCell ref="A240:A241"/>
-    <mergeCell ref="B240:B241"/>
-    <mergeCell ref="A222:I222"/>
-    <mergeCell ref="A224:A225"/>
-    <mergeCell ref="B224:B225"/>
-    <mergeCell ref="A226:A227"/>
-    <mergeCell ref="B226:B227"/>
-    <mergeCell ref="A228:A229"/>
-    <mergeCell ref="B228:B229"/>
-    <mergeCell ref="A230:A231"/>
-    <mergeCell ref="B230:B231"/>
-    <mergeCell ref="A210:A211"/>
-    <mergeCell ref="B210:B211"/>
-    <mergeCell ref="A212:A213"/>
-    <mergeCell ref="B212:B213"/>
-    <mergeCell ref="A214:A215"/>
-    <mergeCell ref="B214:B215"/>
-    <mergeCell ref="A216:A217"/>
-    <mergeCell ref="B216:B217"/>
-    <mergeCell ref="A218:A219"/>
-    <mergeCell ref="B218:B219"/>
-    <mergeCell ref="A200:A201"/>
-    <mergeCell ref="B200:B201"/>
-    <mergeCell ref="A202:A203"/>
-    <mergeCell ref="B202:B203"/>
-    <mergeCell ref="A204:A205"/>
-    <mergeCell ref="B204:B205"/>
-    <mergeCell ref="A206:A207"/>
-    <mergeCell ref="B206:B207"/>
-    <mergeCell ref="A208:A209"/>
-    <mergeCell ref="B208:B209"/>
-    <mergeCell ref="A190:A191"/>
-    <mergeCell ref="B190:B191"/>
-    <mergeCell ref="A192:A193"/>
-    <mergeCell ref="B192:B193"/>
-    <mergeCell ref="A194:A195"/>
-    <mergeCell ref="B194:B195"/>
-    <mergeCell ref="A196:A197"/>
-    <mergeCell ref="B196:B197"/>
-    <mergeCell ref="A198:A199"/>
-    <mergeCell ref="B198:B199"/>
-    <mergeCell ref="A180:A181"/>
-    <mergeCell ref="B180:B181"/>
-    <mergeCell ref="A182:A183"/>
-    <mergeCell ref="B182:B183"/>
-    <mergeCell ref="A184:A185"/>
-    <mergeCell ref="B184:B185"/>
-    <mergeCell ref="A186:A187"/>
-    <mergeCell ref="B186:B187"/>
-    <mergeCell ref="A188:A189"/>
-    <mergeCell ref="B188:B189"/>
-    <mergeCell ref="A168:A169"/>
-    <mergeCell ref="B168:B169"/>
-    <mergeCell ref="A170:A171"/>
-    <mergeCell ref="B170:B171"/>
-    <mergeCell ref="A172:A173"/>
-    <mergeCell ref="B172:B173"/>
-    <mergeCell ref="A174:A175"/>
-    <mergeCell ref="B174:B175"/>
-    <mergeCell ref="A178:I178"/>
-    <mergeCell ref="A158:A159"/>
-    <mergeCell ref="B158:B159"/>
-    <mergeCell ref="A160:A161"/>
-    <mergeCell ref="B160:B161"/>
-    <mergeCell ref="A162:A163"/>
-    <mergeCell ref="B162:B163"/>
-    <mergeCell ref="A164:A165"/>
-    <mergeCell ref="B164:B165"/>
-    <mergeCell ref="A166:A167"/>
-    <mergeCell ref="B166:B167"/>
-    <mergeCell ref="A148:A149"/>
-    <mergeCell ref="B148:B149"/>
-    <mergeCell ref="A150:A151"/>
-    <mergeCell ref="B150:B151"/>
-    <mergeCell ref="A152:A153"/>
-    <mergeCell ref="B152:B153"/>
-    <mergeCell ref="A154:A155"/>
-    <mergeCell ref="B154:B155"/>
-    <mergeCell ref="A156:A157"/>
-    <mergeCell ref="B156:B157"/>
-    <mergeCell ref="A138:A139"/>
-    <mergeCell ref="B138:B139"/>
-    <mergeCell ref="A140:A141"/>
-    <mergeCell ref="B140:B141"/>
-    <mergeCell ref="A142:A143"/>
-    <mergeCell ref="B142:B143"/>
-    <mergeCell ref="A144:A145"/>
-    <mergeCell ref="B144:B145"/>
-    <mergeCell ref="A146:A147"/>
-    <mergeCell ref="B146:B147"/>
-    <mergeCell ref="A126:A127"/>
-    <mergeCell ref="B126:B127"/>
-    <mergeCell ref="A128:A129"/>
-    <mergeCell ref="B128:B129"/>
-    <mergeCell ref="A130:A131"/>
-    <mergeCell ref="B130:B131"/>
-    <mergeCell ref="A134:I134"/>
-    <mergeCell ref="A136:A137"/>
-    <mergeCell ref="B136:B137"/>
-    <mergeCell ref="A116:A117"/>
-    <mergeCell ref="B116:B117"/>
-    <mergeCell ref="A118:A119"/>
-    <mergeCell ref="B118:B119"/>
-    <mergeCell ref="A120:A121"/>
-    <mergeCell ref="B120:B121"/>
-    <mergeCell ref="A122:A123"/>
-    <mergeCell ref="B122:B123"/>
-    <mergeCell ref="A124:A125"/>
-    <mergeCell ref="B124:B125"/>
-    <mergeCell ref="A106:A107"/>
-    <mergeCell ref="B106:B107"/>
-    <mergeCell ref="A108:A109"/>
-    <mergeCell ref="B108:B109"/>
-    <mergeCell ref="A110:A111"/>
-    <mergeCell ref="B110:B111"/>
-    <mergeCell ref="A112:A113"/>
-    <mergeCell ref="B112:B113"/>
-    <mergeCell ref="A114:A115"/>
-    <mergeCell ref="B114:B115"/>
-    <mergeCell ref="A96:A97"/>
-    <mergeCell ref="B96:B97"/>
-    <mergeCell ref="A98:A99"/>
-    <mergeCell ref="B98:B99"/>
-    <mergeCell ref="A100:A101"/>
-    <mergeCell ref="B100:B101"/>
-    <mergeCell ref="A102:A103"/>
-    <mergeCell ref="B102:B103"/>
-    <mergeCell ref="A104:A105"/>
-    <mergeCell ref="B104:B105"/>
-    <mergeCell ref="A84:A85"/>
-    <mergeCell ref="B84:B85"/>
-    <mergeCell ref="A86:A87"/>
-    <mergeCell ref="B86:B87"/>
-    <mergeCell ref="A90:I90"/>
-    <mergeCell ref="A92:A93"/>
-    <mergeCell ref="B92:B93"/>
-    <mergeCell ref="A94:A95"/>
-    <mergeCell ref="B94:B95"/>
-    <mergeCell ref="A74:A75"/>
-    <mergeCell ref="B74:B75"/>
-    <mergeCell ref="A76:A77"/>
-    <mergeCell ref="B76:B77"/>
-    <mergeCell ref="A78:A79"/>
-    <mergeCell ref="B78:B79"/>
-    <mergeCell ref="A80:A81"/>
-    <mergeCell ref="B80:B81"/>
-    <mergeCell ref="A82:A83"/>
-    <mergeCell ref="B82:B83"/>
-    <mergeCell ref="A64:A65"/>
-    <mergeCell ref="B64:B65"/>
-    <mergeCell ref="A66:A67"/>
-    <mergeCell ref="B66:B67"/>
-    <mergeCell ref="A68:A69"/>
-    <mergeCell ref="B68:B69"/>
-    <mergeCell ref="A70:A71"/>
-    <mergeCell ref="B70:B71"/>
-    <mergeCell ref="A72:A73"/>
-    <mergeCell ref="B72:B73"/>
-    <mergeCell ref="A54:A55"/>
-    <mergeCell ref="B54:B55"/>
-    <mergeCell ref="A56:A57"/>
-    <mergeCell ref="B56:B57"/>
-    <mergeCell ref="A58:A59"/>
-    <mergeCell ref="B58:B59"/>
-    <mergeCell ref="A60:A61"/>
-    <mergeCell ref="B60:B61"/>
-    <mergeCell ref="A62:A63"/>
-    <mergeCell ref="B62:B63"/>
-    <mergeCell ref="A42:A43"/>
-    <mergeCell ref="B42:B43"/>
-    <mergeCell ref="A46:I46"/>
-    <mergeCell ref="A48:A49"/>
-    <mergeCell ref="B48:B49"/>
-    <mergeCell ref="A50:A51"/>
-    <mergeCell ref="B50:B51"/>
-    <mergeCell ref="A52:A53"/>
-    <mergeCell ref="B52:B53"/>
-    <mergeCell ref="A32:A33"/>
-    <mergeCell ref="B32:B33"/>
-    <mergeCell ref="A34:A35"/>
-    <mergeCell ref="B34:B35"/>
-    <mergeCell ref="A36:A37"/>
-    <mergeCell ref="B36:B37"/>
-    <mergeCell ref="A38:A39"/>
-    <mergeCell ref="B38:B39"/>
-    <mergeCell ref="A40:A41"/>
-    <mergeCell ref="B40:B41"/>
-    <mergeCell ref="A22:A23"/>
-    <mergeCell ref="B22:B23"/>
-    <mergeCell ref="A24:A25"/>
-    <mergeCell ref="B24:B25"/>
-    <mergeCell ref="A26:A27"/>
-    <mergeCell ref="B26:B27"/>
-    <mergeCell ref="A28:A29"/>
-    <mergeCell ref="B28:B29"/>
-    <mergeCell ref="A30:A31"/>
-    <mergeCell ref="B30:B31"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="B14:B15"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="A18:A19"/>
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="A20:A21"/>
-    <mergeCell ref="B20:B21"/>
-    <mergeCell ref="A2:I2"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="B10:B11"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
@@ -56671,7 +56671,7 @@
   <sheetData>
     <row r="1" spans="1:1" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A1" s="8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
@@ -56681,7 +56681,7 @@
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
@@ -56691,17 +56691,17 @@
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
@@ -56711,17 +56711,17 @@
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
@@ -56731,17 +56731,17 @@
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
@@ -56751,12 +56751,12 @@
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
@@ -56766,12 +56766,12 @@
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
   </sheetData>
